--- a/docs/blue_wolf/blue_wolf_darajalar.xlsx
+++ b/docs/blue_wolf/blue_wolf_darajalar.xlsx
@@ -1,33 +1,33 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Darajalar" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Oziqlanish" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Binolar" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Umumiy bogʻlanish" sheetId="4" state="visible" r:id="rId4"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Rollar" sheetId="5" state="visible" r:id="rId5"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="PvP oʻlja" sheetId="6" state="visible" r:id="rId6"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Razvedka" sheetId="7" state="visible" r:id="rId7"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Lager va oazis" sheetId="8" state="visible" r:id="rId8"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Profil" sheetId="9" state="visible" r:id="rId9"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Vaqt va narx" sheetId="10" state="visible" r:id="rId10"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Mukofot va mavsum" sheetId="11" state="visible" r:id="rId11"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Adolat nazorati" sheetId="12" state="visible" r:id="rId12"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Tanishtiruv" sheetId="13" state="visible" r:id="rId13"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Vazifalar" sheetId="14" state="visible" r:id="rId14"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Askar iqtisodi" sheetId="15" state="visible" r:id="rId15"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="PvP mexanikasi" sheetId="16" state="visible" r:id="rId16"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Toʻda jangi" sheetId="17" state="visible" r:id="rId17"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Oflayn hisob" sheetId="18" state="visible" r:id="rId18"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Monetizatsiya" sheetId="19" state="visible" r:id="rId19"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Ochilish" sheetId="20" state="visible" r:id="rId20"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sozlamalar" sheetId="21" state="visible" r:id="rId21"/>
+    <sheet name="Darajalar" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Oziqlanish" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="Binolar" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet name="Umumiy bogʻlanish" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet name="Rollar" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet name="PvP oʻlja" sheetId="6" state="visible" r:id="rId6"/>
+    <sheet name="Razvedka" sheetId="7" state="visible" r:id="rId7"/>
+    <sheet name="Lager va oazis" sheetId="8" state="visible" r:id="rId8"/>
+    <sheet name="Profil" sheetId="9" state="visible" r:id="rId9"/>
+    <sheet name="Vaqt va narx" sheetId="10" state="visible" r:id="rId10"/>
+    <sheet name="Mukofot va mavsum" sheetId="11" state="visible" r:id="rId11"/>
+    <sheet name="Adolat nazorati" sheetId="12" state="visible" r:id="rId12"/>
+    <sheet name="Tanishtiruv" sheetId="13" state="visible" r:id="rId13"/>
+    <sheet name="Vazifalar" sheetId="14" state="visible" r:id="rId14"/>
+    <sheet name="Askar iqtisodi" sheetId="15" state="visible" r:id="rId15"/>
+    <sheet name="PvP mexanikasi" sheetId="16" state="visible" r:id="rId16"/>
+    <sheet name="Toʻda jangi" sheetId="17" state="visible" r:id="rId17"/>
+    <sheet name="Oflayn hisob" sheetId="18" state="visible" r:id="rId18"/>
+    <sheet name="Monetizatsiya" sheetId="19" state="visible" r:id="rId19"/>
+    <sheet name="Ochilish" sheetId="20" state="visible" r:id="rId20"/>
+    <sheet name="Sozlamalar" sheetId="21" state="visible" r:id="rId21"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -617,7 +617,7 @@
       </c>
       <c r="Q6" s="1" t="inlineStr">
         <is>
-          <t>Yolgʻiz ov: kemiruvchi va qush; birinchi in</t>
+          <t>Yolgʻiz ov (alfa): kemiruvchi va qush; In</t>
         </is>
       </c>
     </row>
@@ -678,7 +678,7 @@
       </c>
       <c r="Q7" s="1" t="inlineStr">
         <is>
-          <t>Oziq gʻori va Ustaxona qoyasi ochiladi</t>
+          <t>Oziq gʻori va Ustaxona qoyasi</t>
         </is>
       </c>
     </row>
@@ -739,7 +739,7 @@
       </c>
       <c r="Q8" s="1" t="inlineStr">
         <is>
-          <t>Yolgʻiz bosqichning soʻnggi darajasi; toʻdaga tayyorgarlik</t>
+          <t>Ov soʻqmogʻi, birinchi ovchi, quyon ovi</t>
         </is>
       </c>
     </row>
@@ -800,7 +800,7 @@
       </c>
       <c r="Q9" s="1" t="inlineStr">
         <is>
-          <t>🔓 TOʻDA OCHILADI: toʻda bilan ov · toʻda (klan) yaratish yoki qoʻshilish · PvP arena · toʻda janglari</t>
+          <t>🔓 TOʻDA: qoʻshin 10 askar · Jang maydoni, Razvedka qoyasi, Himoya devori · yovvoyi toʻdalarga (bot) hujum · ov guruhi · klan va lager (v2)</t>
         </is>
       </c>
     </row>
@@ -861,7 +861,7 @@
       </c>
       <c r="Q10" s="1" t="inlineStr">
         <is>
-          <t>Toʻda ovi: yirik oʻlja · toʻda umumiy ombori</t>
+          <t>Yirik oʻlja — jayron (kamida 2 boʻri)</t>
         </is>
       </c>
     </row>
@@ -922,7 +922,7 @@
       </c>
       <c r="Q11" s="1" t="inlineStr">
         <is>
-          <t>Toʻda reydi: raqib omboriga hujum</t>
+          <t>🏥 Shifo gʻori · suv oazisi (v2)</t>
         </is>
       </c>
     </row>
@@ -983,7 +983,7 @@
       </c>
       <c r="Q12" s="1" t="inlineStr">
         <is>
-          <t>PvP reytingi va liga tizimi</t>
+          <t>🔓 Haqiqiy oʻyinchilarga hujum (qalqon tugaydi) · reyting va liga (v2)</t>
         </is>
       </c>
     </row>
@@ -1044,7 +1044,7 @@
       </c>
       <c r="Q13" s="1" t="inlineStr">
         <is>
-          <t>Toʻda urushi: toʻda vs toʻda sessiyasi</t>
+          <t>Toʻda urushi (v2) · oʻt oazisi (v2)</t>
         </is>
       </c>
     </row>
@@ -1105,7 +1105,7 @@
       </c>
       <c r="Q14" s="1" t="inlineStr">
         <is>
-          <t>Toʻda lavozimlari: alfa, beta, ovchi, qorovul</t>
+          <t>🛒 Bozor · toʻda lavozimlari (v2)</t>
         </is>
       </c>
     </row>
@@ -1166,7 +1166,7 @@
       </c>
       <c r="Q15" s="1" t="inlineStr">
         <is>
-          <t>Hudud egallash: dasht zonasi toʻda nomiga yoziladi</t>
+          <t>Ikkinchi qurilish navbati — hammaga bepul</t>
         </is>
       </c>
     </row>
@@ -1227,7 +1227,7 @@
       </c>
       <c r="Q16" s="1" t="inlineStr">
         <is>
-          <t>Toʻda birgalikda ovi (co-op boss: togʻ ayigʻi)</t>
+          <t>Co-op boss: togʻ ayigʻi (v3)</t>
         </is>
       </c>
     </row>
@@ -1288,7 +1288,7 @@
       </c>
       <c r="Q17" s="1" t="inlineStr">
         <is>
-          <t>Toʻda xazinasi va aʼzolarga ulush taqsimoti</t>
+          <t>Toʻda xazinasi (v2) · tosh koni (v2)</t>
         </is>
       </c>
     </row>
@@ -1349,7 +1349,7 @@
       </c>
       <c r="Q18" s="1" t="inlineStr">
         <is>
-          <t>Himoya urushi: inni toʻda bilan qoʻriqlash</t>
+          <t>Himoya urushi (v3)</t>
         </is>
       </c>
     </row>
@@ -1410,7 +1410,7 @@
       </c>
       <c r="Q19" s="1" t="inlineStr">
         <is>
-          <t>Mavsumiy PvP turniri (haftalik)</t>
+          <t>Haftalik turnir (v3)</t>
         </is>
       </c>
     </row>
@@ -1471,7 +1471,7 @@
       </c>
       <c r="Q20" s="1" t="inlineStr">
         <is>
-          <t>Toʻda taktikasi: qurshab olish, chekinish, tuzoq</t>
+          <t>Toʻda taktikasi (v3)</t>
         </is>
       </c>
     </row>
@@ -1532,7 +1532,7 @@
       </c>
       <c r="Q21" s="1" t="inlineStr">
         <is>
-          <t>Katta toʻda urushi: 20v20 xarita jangi</t>
+          <t>Suyak dalasi (v2) · 20v20 urush (v3)</t>
         </is>
       </c>
     </row>
@@ -1593,7 +1593,7 @@
       </c>
       <c r="Q22" s="1" t="inlineStr">
         <is>
-          <t>Toʻdalar ittifoqi (2–3 toʻda birlashuvi)</t>
+          <t>Toʻdalar ittifoqi (v3)</t>
         </is>
       </c>
     </row>
@@ -1654,7 +1654,7 @@
       </c>
       <c r="Q23" s="1" t="inlineStr">
         <is>
-          <t>Elite reyd: raqib hududini bosib olish</t>
+          <t>Elite reyd (v3)</t>
         </is>
       </c>
     </row>
@@ -1715,7 +1715,7 @@
       </c>
       <c r="Q24" s="1" t="inlineStr">
         <is>
-          <t>Alfa unvoni: server reytingi va toʻda darajasi</t>
+          <t>Alfa unvoni, server reytingi (v2)</t>
         </is>
       </c>
     </row>
@@ -1776,7 +1776,7 @@
       </c>
       <c r="Q25" s="1" t="inlineStr">
         <is>
-          <t>Muz davri zonasi · qadimgi toʻda janglari</t>
+          <t>🌙 Oy nuri ehtiyoji va passivi · Oy mehrobi (v2) · muz davri zonasi (v3)</t>
         </is>
       </c>
     </row>
@@ -1837,7 +1837,7 @@
       </c>
       <c r="Q26" s="1" t="inlineStr">
         <is>
-          <t>Afsona darvozasi: toʻda bilan boss jangi</t>
+          <t>Afsona bossi (v3)</t>
         </is>
       </c>
     </row>
@@ -1896,7 +1896,7 @@
       </c>
       <c r="Q27" s="1" t="inlineStr">
         <is>
-          <t>Tungi reyd: toʻda hujumi kuchi x2</t>
+          <t>Tungi reyd: 22:00–06:00 yurish tezligi +25%</t>
         </is>
       </c>
     </row>
@@ -1955,7 +1955,7 @@
       </c>
       <c r="Q28" s="1" t="inlineStr">
         <is>
-          <t>Juft hujum: ikki toʻda bir vaqtda urishadi</t>
+          <t>Juft hujum (v3)</t>
         </is>
       </c>
     </row>
@@ -2014,7 +2014,7 @@
       </c>
       <c r="Q29" s="1" t="inlineStr">
         <is>
-          <t>Zanjirni uzish: urushda toʻliq tiklanish</t>
+          <t>Zanjirni uzish: urushdan keyin jarohatlanganlar 2× tez davolanadi</t>
         </is>
       </c>
     </row>
@@ -2073,7 +2073,7 @@
       </c>
       <c r="Q30" s="1" t="inlineStr">
         <is>
-          <t>Yakuniy daraja: butun ittifoqqa +10% doimiy bonus</t>
+          <t>Koʻk Boʻri unvoni · klanga +10% ishlab chiqarish (kuch emas)</t>
         </is>
       </c>
     </row>
@@ -6152,7 +6152,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A3:G40"/>
+  <dimension ref="A3:H40"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="28" customWidth="1" min="1" max="1"/>
@@ -6217,6 +6217,11 @@
           <t>Turi</t>
         </is>
       </c>
+      <c r="H5" s="1" t="inlineStr">
+        <is>
+          <t>XP</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" s="1" t="n">
@@ -6248,6 +6253,9 @@
           <t>Majburiy</t>
         </is>
       </c>
+      <c r="H6" s="1" t="n">
+        <v>5</v>
+      </c>
     </row>
     <row r="7">
       <c r="A7" s="1" t="n">
@@ -6279,6 +6287,9 @@
           <t>Majburiy</t>
         </is>
       </c>
+      <c r="H7" s="1" t="n">
+        <v>10</v>
+      </c>
     </row>
     <row r="8">
       <c r="A8" s="1" t="n">
@@ -6310,6 +6321,9 @@
           <t>Majburiy</t>
         </is>
       </c>
+      <c r="H8" s="1" t="n">
+        <v>15</v>
+      </c>
     </row>
     <row r="9">
       <c r="A9" s="1" t="n">
@@ -6325,12 +6339,12 @@
       </c>
       <c r="D9" s="1" t="inlineStr">
         <is>
-          <t>Oziq gʻori qurish</t>
+          <t>Oziq gʻorini ochish</t>
         </is>
       </c>
       <c r="E9" s="1" t="inlineStr">
         <is>
-          <t>Bepul tezlashtirish</t>
+          <t>Oziq gʻori 1-daraja</t>
         </is>
       </c>
       <c r="F9" s="1" t="n">
@@ -6340,6 +6354,9 @@
         <is>
           <t>Majburiy</t>
         </is>
+      </c>
+      <c r="H9" s="1" t="n">
+        <v>10</v>
       </c>
     </row>
     <row r="10">
@@ -6372,6 +6389,9 @@
           <t>Majburiy</t>
         </is>
       </c>
+      <c r="H10" s="1" t="n">
+        <v>10</v>
+      </c>
     </row>
     <row r="11">
       <c r="A11" s="1" t="n">
@@ -6387,12 +6407,12 @@
       </c>
       <c r="D11" s="1" t="inlineStr">
         <is>
-          <t>Ustaxona qurish</t>
+          <t>Ustaxonani ochish</t>
         </is>
       </c>
       <c r="E11" s="1" t="inlineStr">
         <is>
-          <t>Bepul tezlashtirish</t>
+          <t>Ustaxona 1-daraja</t>
         </is>
       </c>
       <c r="F11" s="1" t="n">
@@ -6402,6 +6422,9 @@
         <is>
           <t>Majburiy</t>
         </is>
+      </c>
+      <c r="H11" s="1" t="n">
+        <v>10</v>
       </c>
     </row>
     <row r="12">
@@ -6413,12 +6436,12 @@
       </c>
       <c r="C12" s="1" t="inlineStr">
         <is>
-          <t>Ustaxonaga boʻri qoʻy — u sen uchun tosh yigʻadi.</t>
+          <t>Ustaxona resursni oʻzi yigʻadi. Qaysi biri koʻproq kerakligini tanla.</t>
         </is>
       </c>
       <c r="D12" s="1" t="inlineStr">
         <is>
-          <t>Yigʻuvchi tayinlash</t>
+          <t>Taqsimotni sozlash</t>
         </is>
       </c>
       <c r="E12" s="1" t="inlineStr">
@@ -6433,6 +6456,9 @@
         <is>
           <t>Majburiy</t>
         </is>
+      </c>
+      <c r="H12" s="1" t="n">
+        <v>10</v>
       </c>
     </row>
     <row r="13">
@@ -6449,12 +6475,12 @@
       </c>
       <c r="D13" s="1" t="inlineStr">
         <is>
-          <t>Ov soʻqmogʻi qurish</t>
+          <t>Ov soʻqmogʻini ochish</t>
         </is>
       </c>
       <c r="E13" s="1" t="inlineStr">
         <is>
-          <t>Bepul tezlashtirish</t>
+          <t>Ov soʻqmogʻi 1-daraja</t>
         </is>
       </c>
       <c r="F13" s="1" t="n">
@@ -6464,6 +6490,9 @@
         <is>
           <t>Majburiy</t>
         </is>
+      </c>
+      <c r="H13" s="1" t="n">
+        <v>20</v>
       </c>
     </row>
     <row r="14">
@@ -6496,6 +6525,9 @@
           <t>Majburiy</t>
         </is>
       </c>
+      <c r="H14" s="1" t="n">
+        <v>20</v>
+      </c>
     </row>
     <row r="15">
       <c r="A15" s="1" t="n">
@@ -6516,7 +6548,7 @@
       </c>
       <c r="E15" s="1" t="inlineStr">
         <is>
-          <t>Bepul tezlashtirish</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F15" s="1" t="n">
@@ -6526,6 +6558,9 @@
         <is>
           <t>Majburiy</t>
         </is>
+      </c>
+      <c r="H15" s="1" t="n">
+        <v>20</v>
       </c>
     </row>
     <row r="16">
@@ -6547,7 +6582,7 @@
       </c>
       <c r="E16" s="1" t="inlineStr">
         <is>
-          <t>3 boʻri</t>
+          <t>2 ovchi</t>
         </is>
       </c>
       <c r="F16" s="1" t="n">
@@ -6557,6 +6592,9 @@
         <is>
           <t>Majburiy</t>
         </is>
+      </c>
+      <c r="H16" s="1" t="n">
+        <v>20</v>
       </c>
     </row>
     <row r="17">
@@ -6573,7 +6611,7 @@
       </c>
       <c r="D17" s="1" t="inlineStr">
         <is>
-          <t>Toʻda ovi</t>
+          <t>Ovchilarni ovga yuborish (sugʻur)</t>
         </is>
       </c>
       <c r="E17" s="1" t="inlineStr">
@@ -6588,6 +6626,9 @@
         <is>
           <t>Majburiy</t>
         </is>
+      </c>
+      <c r="H17" s="1" t="n">
+        <v>25</v>
       </c>
     </row>
     <row r="18">
@@ -6604,12 +6645,12 @@
       </c>
       <c r="D18" s="1" t="inlineStr">
         <is>
-          <t>Jang maydoni qurish</t>
+          <t>Jang maydonini ochish</t>
         </is>
       </c>
       <c r="E18" s="1" t="inlineStr">
         <is>
-          <t>Bepul tezlashtirish</t>
+          <t>Jang maydoni 1-daraja</t>
         </is>
       </c>
       <c r="F18" s="1" t="n">
@@ -6619,6 +6660,9 @@
         <is>
           <t>Tavsiya</t>
         </is>
+      </c>
+      <c r="H18" s="1" t="n">
+        <v>25</v>
       </c>
     </row>
     <row r="19">
@@ -6651,6 +6695,9 @@
           <t>Tavsiya</t>
         </is>
       </c>
+      <c r="H19" s="1" t="n">
+        <v>25</v>
+      </c>
     </row>
     <row r="20">
       <c r="A20" s="1" t="n">
@@ -6661,17 +6708,17 @@
       </c>
       <c r="C20" s="1" t="inlineStr">
         <is>
-          <t>Yolgʻiz boʻri omon qolmaydi. Toʻdaga qoʻshil yoki oʻzingniki yarat.</t>
+          <t>Yolgʻiz boʻri omon qolmaydi. Ov guruhiga qoʻshil.</t>
         </is>
       </c>
       <c r="D20" s="1" t="inlineStr">
         <is>
-          <t>Klanga qoʻshilish</t>
+          <t>Ov guruhiga qoʻshilish</t>
         </is>
       </c>
       <c r="E20" s="1" t="inlineStr">
         <is>
-          <t>Klan bonusi</t>
+          <t>Ov +10% (24 soat)</t>
         </is>
       </c>
       <c r="F20" s="1" t="n">
@@ -6681,6 +6728,9 @@
         <is>
           <t>Tavsiya</t>
         </is>
+      </c>
+      <c r="H20" s="1" t="n">
+        <v>25</v>
       </c>
     </row>
     <row r="21">
@@ -6692,12 +6742,12 @@
       </c>
       <c r="C21" s="1" t="inlineStr">
         <is>
-          <t>Endi birinchi jang. Qoʻrqma — bu mashq jangi.</t>
+          <t>Endi birinchi jang. Qoʻrqma — bu yovvoyi toʻda.</t>
         </is>
       </c>
       <c r="D21" s="1" t="inlineStr">
         <is>
-          <t>PvP (bot raqib)</t>
+          <t>Botga hujum (yovvoyi toʻda)</t>
         </is>
       </c>
       <c r="E21" s="1" t="inlineStr">
@@ -6712,6 +6762,9 @@
         <is>
           <t>Majburiy</t>
         </is>
+      </c>
+      <c r="H21" s="1" t="n">
+        <v>30</v>
       </c>
     </row>
     <row r="22">
@@ -6728,12 +6781,12 @@
       </c>
       <c r="D22" s="1" t="inlineStr">
         <is>
-          <t>Razvedka qoyasi qurish</t>
+          <t>Razvedka qoyasini ochish</t>
         </is>
       </c>
       <c r="E22" s="1" t="inlineStr">
         <is>
-          <t>Bepul tezlashtirish</t>
+          <t>1 razvedkachi</t>
         </is>
       </c>
       <c r="F22" s="1" t="n">
@@ -6743,6 +6796,9 @@
         <is>
           <t>Tavsiya</t>
         </is>
+      </c>
+      <c r="H22" s="1" t="n">
+        <v>10</v>
       </c>
     </row>
     <row r="23">
@@ -6759,7 +6815,7 @@
       </c>
       <c r="D23" s="1" t="inlineStr">
         <is>
-          <t>Razvedka yuborish</t>
+          <t>Razvedka yuborish (botga)</t>
         </is>
       </c>
       <c r="E23" s="1" t="inlineStr">
@@ -6774,6 +6830,9 @@
         <is>
           <t>Tavsiya</t>
         </is>
+      </c>
+      <c r="H23" s="1" t="n">
+        <v>10</v>
       </c>
     </row>
     <row r="24">
@@ -6785,17 +6844,17 @@
       </c>
       <c r="C24" s="1" t="inlineStr">
         <is>
-          <t>Sening iningga ham hujum qilishadi. Himoya devorini qur.</t>
+          <t>Ustaxona buferi toʻldi — resursni omborga ol.</t>
         </is>
       </c>
       <c r="D24" s="1" t="inlineStr">
         <is>
-          <t>Himoya devori qurish</t>
+          <t>Yigʻib olish</t>
         </is>
       </c>
       <c r="E24" s="1" t="inlineStr">
         <is>
-          <t>Bepul tezlashtirish</t>
+          <t>100 shox-shabba</t>
         </is>
       </c>
       <c r="F24" s="1" t="n">
@@ -6805,6 +6864,9 @@
         <is>
           <t>Tavsiya</t>
         </is>
+      </c>
+      <c r="H24" s="1" t="n">
+        <v>10</v>
       </c>
     </row>
     <row r="25">
@@ -6836,6 +6898,9 @@
         <is>
           <t>Majburiy</t>
         </is>
+      </c>
+      <c r="H25" s="1" t="n">
+        <v>20</v>
       </c>
     </row>
     <row r="26">
@@ -6856,6 +6921,9 @@
           <t>✅ Maqsadga mos</t>
         </is>
       </c>
+      <c r="H26" t="n">
+        <v>330</v>
+      </c>
     </row>
     <row r="27">
       <c r="A27" s="1" t="inlineStr">
@@ -6867,13 +6935,13 @@
     <row r="28">
       <c r="A28" s="1" t="inlineStr">
         <is>
-          <t>Bepul tezlashtirish</t>
+          <t>Navbatlar darhol</t>
         </is>
       </c>
       <c r="B28" s="1" t="inlineStr"/>
       <c r="C28" s="1" t="inlineStr">
         <is>
-          <t>Tanishtiruvdagi har qurilish darhol tugaydi — 5 marta bepul. Yangi oʻyinchi hech narsa kutmaydi</t>
+          <t>Tanishtiruv davomida barcha qurilish va mashq navbatlari darhol tugaydi. Yakunda keyin ishlatish uchun 5 ta bepul tezlashtirish (har biri 1 soatgacha) beriladi</t>
         </is>
       </c>
     </row>
@@ -6938,7 +7006,7 @@
       <c r="B33" s="1" t="inlineStr"/>
       <c r="C33" s="1" t="inlineStr">
         <is>
-          <t>Tanishtiruv davomida va 6-darajagacha hujum qilib boʻlmaydi</t>
+          <t>Tanishtiruv davomida va 6-darajagacha oʻyinchilar hujum qila olmaydi; 4-darajadan faqat botlarga hujum</t>
         </is>
       </c>
     </row>
@@ -6951,7 +7019,7 @@
       <c r="B34" s="1" t="inlineStr"/>
       <c r="C34" s="1" t="inlineStr">
         <is>
-          <t>500 goʻsht, 300 tosh, 200 shox-shabba, 1 ta bepul tier mashqi</t>
+          <t>Oziq gʻorini toʻliq toʻldiradigan goʻsht, 300 tosh, 200 shox-shabba, 100 teri, 100 suyak, 1 ta bepul tier mashqi</t>
         </is>
       </c>
     </row>
@@ -7004,14 +7072,14 @@
     <row r="39">
       <c r="A39" s="1" t="inlineStr">
         <is>
-          <t>Eng muhim qadam — 11-qadam: yolgʻizlikdan toʻdaga oʻtish. Bu yerda musiqa va animatsiya oʻzgarsin, oʻyinchi farqni his qilsin.</t>
+          <t>Eng muhim qadam — 11-qadam: yolgʻizlikdan toʻdaga oʻtish. Bu yerda musiqa va animatsiya oʻzgarsin, oʻyinchi farqni his qilsin. v2 da: 15-qadam → Klanga qoʻshilish, 19-qadam → Himoya devori.</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" s="1" t="inlineStr">
         <is>
-          <t>Tanishtiruv XP si bosqich koeffitsientiga (×0.40) mos: 5-darajagacha atigi 280 XP kerak, shuning uchun 15 daqiqa realistik.</t>
+          <t>Tanishtiruv XP si faqat qadam mukofotidan keladi (H ustuni, jami 330): 3-qadamdan keyin 2-daraja, 7-dan keyin 3-daraja, 10-dan keyin 4-daraja, 16-dan keyin 5-daraja. Oʻtkazib yuborilgan qadam XP si ham beriladi.</t>
         </is>
       </c>
     </row>
@@ -7943,7 +8011,7 @@
       </c>
       <c r="B37" s="1" t="inlineStr">
         <is>
-          <t>1 ta PvP jangida qatnashish</t>
+          <t>1 ta hujum (botlar ham hisoblanadi)</t>
         </is>
       </c>
       <c r="C37" s="1" t="inlineStr">
@@ -8121,7 +8189,7 @@
       </c>
       <c r="B43" s="1" t="inlineStr">
         <is>
-          <t>3 marta lager yuborish</t>
+          <t>3 marta lager yuborish (MVP da: 3 razvedka)</t>
         </is>
       </c>
       <c r="C43" s="1" t="inlineStr">
@@ -8154,7 +8222,7 @@
       </c>
       <c r="B44" s="1" t="inlineStr">
         <is>
-          <t>10 ta PvP jangi</t>
+          <t>10 ta hujum (botlar ham hisoblanadi)</t>
         </is>
       </c>
       <c r="C44" s="1" t="inlineStr">
@@ -8171,7 +8239,7 @@
       </c>
       <c r="B45" s="1" t="inlineStr">
         <is>
-          <t>Toʻda jangida 3 marta qatnashish</t>
+          <t>3 marta guruh ovi yoki toʻda jangi</t>
         </is>
       </c>
       <c r="C45" s="1" t="inlineStr">
@@ -8815,7 +8883,7 @@
         <v>1</v>
       </c>
       <c r="G24" s="1" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H24" s="1" t="n">
         <v>1</v>
@@ -8841,7 +8909,7 @@
         <v>1</v>
       </c>
       <c r="G25" s="1" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H25" s="1" t="n">
         <v>1</v>
@@ -8867,7 +8935,7 @@
         <v>1</v>
       </c>
       <c r="G26" s="1" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H26" s="1" t="n">
         <v>1</v>
@@ -9560,7 +9628,7 @@
     <row r="60">
       <c r="A60" s="1" t="inlineStr">
         <is>
-          <t>Koeffitsient = (toʻlganlik / normal toʻlganlik) ^ 1.8, 0.50x va 3.00x orasida. Normal toʻlganlik 60%.</t>
+          <t>Koeffitsient = MAX(0.50, (toʻlganlik / normal toʻlganlik) ^ 1.8). Normal toʻlganlik 60%; 100% da 2.51x.</t>
         </is>
       </c>
     </row>
@@ -11621,7 +11689,7 @@
       </c>
       <c r="B19" s="1" t="inlineStr">
         <is>
-          <t>Raqib klanga 30 daqiqa beriladi; rad etsa reytingdan ball yoʻqotadi</t>
+          <t>Raqib klanga 30 daqiqa beriladi; rad etsa yoki javob bermasa klan reytingidan 50 ball yoʻqotadi, garov qaytariladi</t>
         </is>
       </c>
       <c r="C19" s="1" t="inlineStr"/>
@@ -12116,7 +12184,7 @@
     <row r="48">
       <c r="A48" s="1" t="inlineStr">
         <is>
-          <t>Aʼzo mukofot shifti 15%: bitta aʼzo urush fondining 15% idan koʻp ololmaydi - alfa hamma narsani olib ketmaydi.</t>
+          <t>Aʼzo mukofot shifti 15%: bitta aʼzo urush fondining 15% idan koʻp ololmaydi. Shiftdan ortgan qism (misolda 20,779 tanga) klan xazinasiga tushadi.</t>
         </is>
       </c>
     </row>
@@ -12218,12 +12286,12 @@
     <row r="7">
       <c r="A7" s="1" t="inlineStr">
         <is>
-          <t>0 - 8 soat</t>
+          <t>0 - 20 soat</t>
         </is>
       </c>
       <c r="B7" s="1" t="inlineStr">
         <is>
-          <t>Toʻliq (70% oflayn stavka)</t>
+          <t>70% oflayn stavka, Ustaxona buferi toʻlguncha (oflaynda 2× = 20 soat)</t>
         </is>
       </c>
       <c r="C7" s="1" t="inlineStr">
@@ -12245,17 +12313,17 @@
     <row r="8">
       <c r="A8" s="1" t="inlineStr">
         <is>
-          <t>8 - 24 soat</t>
+          <t>20 soat - 3 kun</t>
         </is>
       </c>
       <c r="B8" s="1" t="inlineStr">
         <is>
-          <t>Ombor toʻlguncha davom etadi</t>
+          <t>Bufer toʻlgan - toʻxtaydi</t>
         </is>
       </c>
       <c r="C8" s="1" t="inlineStr">
         <is>
-          <t>Ombordan yeydi</t>
+          <t>Zaxira kamayadi</t>
         </is>
       </c>
       <c r="D8" s="1" t="inlineStr">
@@ -12265,24 +12333,24 @@
       </c>
       <c r="E8" s="1" t="inlineStr">
         <is>
-          <t>Hujum qilinadi</t>
+          <t>Hujum qilinadi; 24 soatdan keyin oʻlja 0.5x</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="1" t="inlineStr">
         <is>
-          <t>1 - 3 kun</t>
+          <t>3 - ~7 kun</t>
         </is>
       </c>
       <c r="B9" s="1" t="inlineStr">
         <is>
-          <t>Ombor toʻlgan - toʻxtaydi</t>
+          <t>Toʻxtagan</t>
         </is>
       </c>
       <c r="C9" s="1" t="inlineStr">
         <is>
-          <t>Zaxira tugay boshlaydi</t>
+          <t>Zaxira kamayadi (oflayn ombor ~6-7 kunga yetadi)</t>
         </is>
       </c>
       <c r="D9" s="1" t="inlineStr">
@@ -12292,14 +12360,14 @@
       </c>
       <c r="E9" s="1" t="inlineStr">
         <is>
-          <t>Oʻlja koeff. 0.5x</t>
+          <t>Uyqu qalqoni (72 soatdan)</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="1" t="inlineStr">
         <is>
-          <t>3 - 7 kun</t>
+          <t>Zaxira tugagach</t>
         </is>
       </c>
       <c r="B10" s="1" t="inlineStr">
@@ -12309,7 +12377,7 @@
       </c>
       <c r="C10" s="1" t="inlineStr">
         <is>
-          <t>Ochlik rejimi</t>
+          <t>Ochlik</t>
         </is>
       </c>
       <c r="D10" s="1" t="inlineStr">
@@ -12319,14 +12387,14 @@
       </c>
       <c r="E10" s="1" t="inlineStr">
         <is>
-          <t>Uyqu qalqoni yoqiladi</t>
+          <t>Uyqu qalqoni</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="1" t="inlineStr">
         <is>
-          <t>7+ kun</t>
+          <t>Ochlikning 7-kunidan</t>
         </is>
       </c>
       <c r="B11" s="1" t="inlineStr">
@@ -12336,7 +12404,7 @@
       </c>
       <c r="C11" s="1" t="inlineStr">
         <is>
-          <t>Ochlik davom etadi</t>
+          <t>Ochlik</t>
         </is>
       </c>
       <c r="D11" s="1" t="inlineStr">
@@ -12360,7 +12428,7 @@
     <row r="13">
       <c r="A13" s="1" t="inlineStr">
         <is>
-          <t>Oʻyinchi yoʻqligida ombor sigʻimi 2x ga kengayadi - bu 3 kunlik yoʻqlikni qoplash uchun ataylab qilingan.</t>
+          <t>Oʻyinchi yoʻqligida (oxirgi soʻrovdan 5 daqiqadan koʻp) Oziq gʻori sigʻimi va Ustaxona buferi 2x ga kengayadi (“Oflayn ombor +50%” xaridi bilan 2.5x).</t>
         </is>
       </c>
     </row>
@@ -13484,7 +13552,7 @@
     <row r="8">
       <c r="A8" s="1" t="inlineStr">
         <is>
-          <t>Ikkinchi qurilish navbati</t>
+          <t>Ikkinchi qurilish navbati (erta ochish)</t>
         </is>
       </c>
       <c r="B8" s="1" t="inlineStr">
@@ -14464,7 +14532,7 @@
       </c>
       <c r="D52" s="1" t="inlineStr">
         <is>
-          <t>Ikkinchi qurilish navbati</t>
+          <t>Ikkinchi navbat — erta ochish</t>
         </is>
       </c>
       <c r="E52" s="1" t="inlineStr">
@@ -14474,7 +14542,7 @@
       </c>
       <c r="F52" s="1" t="inlineStr">
         <is>
-          <t>Bir martalik. Ikki bino parallel quriladi</t>
+          <t>4–9 darajada ochadi; 10-darajadan hammaga bepul — uzoq muddatda ustunlik bermaydi</t>
         </is>
       </c>
     </row>
@@ -14530,7 +14598,7 @@
       </c>
       <c r="F54" s="1" t="inlineStr">
         <is>
-          <t>Bir martalik. Uzoq yoʻqlikni qoplaydi</t>
+          <t>Oflayn koeff. 2.0 → 2.5. Uzoq yoʻqlikni qoplaydi</t>
         </is>
       </c>
     </row>
@@ -14708,7 +14776,7 @@
     <row r="67">
       <c r="A67" s="1" t="inlineStr">
         <is>
-          <t>Natija: eng koʻp toʻlagan oʻyinchi bepul oʻynagandan 1.25x tez rivojlanadi - 5x emas. Bir oyda farq sezilarli, lekin yengib boʻlmaydigan emas.</t>
+          <t>Natija: eng koʻp toʻlagan oʻyinchi bepul oʻynagandan koʻpi bilan 1.25x tez rivojlanadi - 5x emas. Ikkinchi navbat 10-darajada hammaga bepul boʻlgani uchun bu hisobni buzmaydi.</t>
         </is>
       </c>
       <c r="B67" s="1" t="inlineStr">
@@ -14828,10 +14896,10 @@
         <v>1.5</v>
       </c>
       <c r="D75" s="1" t="n">
-        <v>10</v>
+        <v>16</v>
       </c>
       <c r="E75" s="1" t="n">
-        <v>0.1</v>
+        <v>0.16</v>
       </c>
       <c r="F75" s="1" t="n">
         <v>1.5</v>
@@ -14848,10 +14916,10 @@
         <v>3</v>
       </c>
       <c r="D76" s="1" t="n">
-        <v>15</v>
+        <v>32</v>
       </c>
       <c r="E76" s="1" t="n">
-        <v>0.15</v>
+        <v>0.32</v>
       </c>
       <c r="F76" s="1" t="n">
         <v>3</v>
@@ -14868,10 +14936,10 @@
         <v>5</v>
       </c>
       <c r="D77" s="1" t="n">
-        <v>39</v>
+        <v>96</v>
       </c>
       <c r="E77" s="1" t="n">
-        <v>0.39</v>
+        <v>0.96</v>
       </c>
       <c r="F77" s="1" t="n">
         <v>5</v>
@@ -14880,7 +14948,7 @@
     <row r="78">
       <c r="A78" s="1" t="inlineStr">
         <is>
-          <t>Narx odatdagi tezlashtirish shkalasiga 0.60 koeffitsient bilan bogʻlangan - qaytish arzonroq, chunki qiymati kamroq.</t>
+          <t>Narx = yuqoriga yaxlitlangan(0.60 × Σ blok narxlari), bloklar soni = yuqoriga yaxlitlangan(qaytish soati). Bloklar progressiv jadvaldan (10, 16, 26, ...).</t>
         </is>
       </c>
     </row>
@@ -16545,7 +16613,7 @@
     <row r="4">
       <c r="A4" s="1" t="inlineStr">
         <is>
-          <t>1–3 daraja yolgʻiz bosqich. 4-darajada toʻda, klan, PvP va toʻda janglari birdaniga ochiladi.</t>
+          <t>1–3 daraja yolgʻiz bosqich. 4-darajada toʻda, botlarga hujum va ov guruhi ochiladi; haqiqiy PvP — 7-darajadan. (v2) — MVP dan keyin, (v3) — dizayni hali yozilmagan.</t>
         </is>
       </c>
     </row>
@@ -16592,7 +16660,7 @@
       </c>
       <c r="D6" s="1" t="inlineStr">
         <is>
-          <t>Yolgʻiz ov: kemiruvchi, qush</t>
+          <t>Yolgʻiz ov (alfa): kemiruvchi, qush</t>
         </is>
       </c>
       <c r="E6" s="1" t="inlineStr">
@@ -16617,7 +16685,7 @@
       </c>
       <c r="D7" s="1" t="inlineStr">
         <is>
-          <t>Birinchi in (Bosh in 1-daraja)</t>
+          <t>In — oʻyinchi darajasi bilan avtomatik</t>
         </is>
       </c>
       <c r="E7" s="1" t="inlineStr">
@@ -16667,12 +16735,12 @@
       </c>
       <c r="D9" s="1" t="inlineStr">
         <is>
-          <t>Quyon ovi; yolgʻiz bosqich yakuni</t>
+          <t>Ov soʻqmogʻi, birinchi ovchi, quyon ovi</t>
         </is>
       </c>
       <c r="E9" s="1" t="inlineStr">
         <is>
-          <t>Toʻda ochilishiga qiziqish uygʻotish</t>
+          <t>Toʻda ovi tayyorgarligi</t>
         </is>
       </c>
     </row>
@@ -16692,7 +16760,7 @@
       </c>
       <c r="D10" s="1" t="inlineStr">
         <is>
-          <t>🔓 Toʻda bilan ov (2–3 boʻri birga)</t>
+          <t>🔓 Toʻda (qoʻshin 10), toʻda ovi, ov guruhi (2–4 oʻyinchi)</t>
         </is>
       </c>
       <c r="E10" s="1" t="inlineStr">
@@ -16712,17 +16780,17 @@
       </c>
       <c r="C11" s="1" t="inlineStr">
         <is>
-          <t>Klan</t>
+          <t>PvP</t>
         </is>
       </c>
       <c r="D11" s="1" t="inlineStr">
         <is>
-          <t>🔓 Toʻda (klan) yaratish yoki qoʻshilish</t>
+          <t>🔓 Jang maydoni, Razvedka qoyasi, Himoya devori · yovvoyi toʻdalar (bot)</t>
         </is>
       </c>
       <c r="E11" s="1" t="inlineStr">
         <is>
-          <t>Ijtimoiy yadro; retention sakrashi</t>
+          <t>Xavfsiz birinchi jang tajribasi</t>
         </is>
       </c>
     </row>
@@ -16737,277 +16805,277 @@
       </c>
       <c r="C12" s="1" t="inlineStr">
         <is>
-          <t>PvP</t>
+          <t>Klan</t>
         </is>
       </c>
       <c r="D12" s="1" t="inlineStr">
         <is>
-          <t>🔓 PvP arena: 1v1 boʻri jangi</t>
+          <t>Klan yaratish yoki qoʻshilish (v2) · lager (v2)</t>
         </is>
       </c>
       <c r="E12" s="1" t="inlineStr">
         <is>
-          <t>Birinchi raqobat tajribasi</t>
+          <t>Ijtimoiy yadro</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="1" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="B13" s="1" t="inlineStr">
         <is>
-          <t>Hind boʻrisi</t>
+          <t>Qizil boʻri</t>
         </is>
       </c>
       <c r="C13" s="1" t="inlineStr">
         <is>
-          <t>PvP</t>
+          <t>Ov</t>
         </is>
       </c>
       <c r="D13" s="1" t="inlineStr">
         <is>
-          <t>🔓 Toʻda janglari: toʻda vs toʻda</t>
+          <t>Yirik oʻlja (jayron) — kamida 2 boʻri</t>
         </is>
       </c>
       <c r="E13" s="1" t="inlineStr">
         <is>
-          <t>Asosiy PvP rejimi</t>
+          <t>Toʻdasiz oʻtib boʻlmaydi</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="1" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="B14" s="1" t="inlineStr">
         <is>
-          <t>Qizil boʻri</t>
+          <t>Italyan boʻrisi</t>
         </is>
       </c>
       <c r="C14" s="1" t="inlineStr">
         <is>
-          <t>Toʻda</t>
+          <t>Iqtisod</t>
         </is>
       </c>
       <c r="D14" s="1" t="inlineStr">
         <is>
-          <t>Toʻdaning umumiy ombori</t>
+          <t>🏥 Shifo gʻori · suv oazisi (v2)</t>
         </is>
       </c>
       <c r="E14" s="1" t="inlineStr">
         <is>
-          <t>Aʼzolar resurs ulashadi</t>
+          <t>Jarohatlarni davolash</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="1" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="B15" s="1" t="inlineStr">
         <is>
-          <t>Italyan boʻrisi</t>
+          <t>Meksika boʻrisi</t>
         </is>
       </c>
       <c r="C15" s="1" t="inlineStr">
         <is>
-          <t>Iqtisod</t>
+          <t>PvP</t>
         </is>
       </c>
       <c r="D15" s="1" t="inlineStr">
         <is>
-          <t>🏥 Shifo gʻori — jarohatlangan boʻrilarni davolaydi</t>
+          <t>🔓 Haqiqiy oʻyinchilarga hujum (qalqon tugaydi) · reyting va liga (v2)</t>
         </is>
       </c>
       <c r="E15" s="1" t="inlineStr">
         <is>
-          <t>Reyd boshlangani uchun zarur</t>
+          <t>Birinchi raqobat tajribasi</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="1" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="B16" s="1" t="inlineStr">
         <is>
-          <t>Iberiya boʻrisi</t>
+          <t>Sharqiy boʻri</t>
         </is>
       </c>
       <c r="C16" s="1" t="inlineStr">
         <is>
-          <t>Iqtisod</t>
+          <t>PvP</t>
         </is>
       </c>
       <c r="D16" s="1" t="inlineStr">
         <is>
-          <t>🛒 Bozor — resurs almashtirish va toʻda savdosi</t>
+          <t>Toʻda urushi (v2) · oʻt oazisi (v2)</t>
         </is>
       </c>
       <c r="E16" s="1" t="inlineStr">
         <is>
-          <t>4 resurs nomutanosibligini hal qiladi</t>
+          <t>Rejalashtirilgan sessiya</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="1" t="n">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="B17" s="1" t="inlineStr">
         <is>
-          <t>Qizil boʻri</t>
+          <t>Iberiya boʻrisi</t>
         </is>
       </c>
       <c r="C17" s="1" t="inlineStr">
         <is>
-          <t>Ov</t>
+          <t>Iqtisod</t>
         </is>
       </c>
       <c r="D17" s="1" t="inlineStr">
         <is>
-          <t>Yirik oʻlja (jayron) — faqat toʻda bilan</t>
+          <t>🛒 Bozor · toʻda lavozimlari (v2)</t>
         </is>
       </c>
       <c r="E17" s="1" t="inlineStr">
         <is>
-          <t>Toʻdasiz oʻtib boʻlmaydi</t>
+          <t>Resurs nomutanosibligini hal qiladi</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="1" t="n">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="B18" s="1" t="inlineStr">
         <is>
-          <t>Italyan boʻrisi</t>
+          <t>Dasht boʻrisi</t>
         </is>
       </c>
       <c r="C18" s="1" t="inlineStr">
         <is>
-          <t>PvP</t>
+          <t>Iqtisod</t>
         </is>
       </c>
       <c r="D18" s="1" t="inlineStr">
         <is>
-          <t>Toʻda reydi: raqib omboriga hujum</t>
+          <t>Ikkinchi qurilish navbati — hammaga bepul</t>
         </is>
       </c>
       <c r="E18" s="1" t="inlineStr">
         <is>
-          <t>Resurs oʻgʻirlash sikli</t>
+          <t>Parallel qurilish</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="1" t="n">
-        <v>7</v>
+        <v>11</v>
       </c>
       <c r="B19" s="1" t="inlineStr">
         <is>
-          <t>Meksika boʻrisi</t>
+          <t>Himolay boʻrisi</t>
         </is>
       </c>
       <c r="C19" s="1" t="inlineStr">
         <is>
-          <t>PvP</t>
+          <t>Toʻda</t>
         </is>
       </c>
       <c r="D19" s="1" t="inlineStr">
         <is>
-          <t>Reyting va liga tizimi</t>
+          <t>Co-op boss: togʻ ayigʻi (v3)</t>
         </is>
       </c>
       <c r="E19" s="1" t="inlineStr">
         <is>
-          <t>Haftalik mukofot</t>
+          <t>Birgalikda ov</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="1" t="n">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="B20" s="1" t="inlineStr">
         <is>
-          <t>Sharqiy boʻri</t>
+          <t>Ezo boʻrisi</t>
         </is>
       </c>
       <c r="C20" s="1" t="inlineStr">
         <is>
-          <t>PvP</t>
+          <t>Klan</t>
         </is>
       </c>
       <c r="D20" s="1" t="inlineStr">
         <is>
-          <t>Toʻda urushi: rejalashtirilgan sessiya</t>
+          <t>Toʻda xazinasi (v2) · tosh koni (v2)</t>
         </is>
       </c>
       <c r="E20" s="1" t="inlineStr">
         <is>
-          <t>15 daqiqalik jang</t>
+          <t>Iqtisodiy boshqaruv</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="1" t="n">
-        <v>9</v>
+        <v>13</v>
       </c>
       <c r="B21" s="1" t="inlineStr">
         <is>
-          <t>Iberiya boʻrisi</t>
+          <t>Tibet boʻrisi</t>
         </is>
       </c>
       <c r="C21" s="1" t="inlineStr">
         <is>
-          <t>Klan</t>
+          <t>PvP</t>
         </is>
       </c>
       <c r="D21" s="1" t="inlineStr">
         <is>
-          <t>Toʻda lavozimlari: alfa, beta, ovchi, qorovul</t>
+          <t>Himoya urushi (v3)</t>
         </is>
       </c>
       <c r="E21" s="1" t="inlineStr">
         <is>
-          <t>Rol va boshqaruv</t>
+          <t>Mudofaa taraf</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="1" t="n">
-        <v>10</v>
+        <v>14</v>
       </c>
       <c r="B22" s="1" t="inlineStr">
         <is>
-          <t>Dasht boʻrisi</t>
+          <t>Arktika boʻrisi</t>
         </is>
       </c>
       <c r="C22" s="1" t="inlineStr">
         <is>
-          <t>Klan</t>
+          <t>PvP</t>
         </is>
       </c>
       <c r="D22" s="1" t="inlineStr">
         <is>
-          <t>Hudud egallash (dasht zonasi)</t>
+          <t>Haftalik turnir (v3)</t>
         </is>
       </c>
       <c r="E22" s="1" t="inlineStr">
         <is>
-          <t>Xaritada toʻda nomi</t>
+          <t>Doimiy takrorlanuvchi voqea</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="1" t="n">
-        <v>11</v>
+        <v>15</v>
       </c>
       <c r="B23" s="1" t="inlineStr">
         <is>
-          <t>Himolay boʻrisi</t>
+          <t>Buyuk tekislik boʻrisi</t>
         </is>
       </c>
       <c r="C23" s="1" t="inlineStr">
@@ -17017,72 +17085,72 @@
       </c>
       <c r="D23" s="1" t="inlineStr">
         <is>
-          <t>Co-op boss: togʻ ayigʻi</t>
+          <t>Taktika: qurshab olish, chekinish, tuzoq (v3)</t>
         </is>
       </c>
       <c r="E23" s="1" t="inlineStr">
         <is>
-          <t>Birgalikda ov</t>
+          <t>Chuqurroq jang tanlovi</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="1" t="n">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="B24" s="1" t="inlineStr">
         <is>
-          <t>Ezo boʻrisi</t>
+          <t>Yevroosiyo kulrang boʻrisi</t>
         </is>
       </c>
       <c r="C24" s="1" t="inlineStr">
         <is>
-          <t>Klan</t>
+          <t>PvP</t>
         </is>
       </c>
       <c r="D24" s="1" t="inlineStr">
         <is>
-          <t>Toʻda xazinasi va ulush taqsimoti</t>
+          <t>Suyak dalasi (v2) · 20v20 urush (v3)</t>
         </is>
       </c>
       <c r="E24" s="1" t="inlineStr">
         <is>
-          <t>Iqtisodiy boshqaruv</t>
+          <t>Yirik format</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="1" t="n">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="B25" s="1" t="inlineStr">
         <is>
-          <t>Tibet boʻrisi</t>
+          <t>Tundra boʻrisi</t>
         </is>
       </c>
       <c r="C25" s="1" t="inlineStr">
         <is>
-          <t>PvP</t>
+          <t>Klan</t>
         </is>
       </c>
       <c r="D25" s="1" t="inlineStr">
         <is>
-          <t>Himoya urushi: inni qoʻriqlash</t>
+          <t>Toʻdalar ittifoqi (v3)</t>
         </is>
       </c>
       <c r="E25" s="1" t="inlineStr">
         <is>
-          <t>Mudofaa taraf</t>
+          <t>Meta-qatlam</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="1" t="n">
-        <v>14</v>
+        <v>18</v>
       </c>
       <c r="B26" s="1" t="inlineStr">
         <is>
-          <t>Arktika boʻrisi</t>
+          <t>Alyaska ichki boʻrisi</t>
         </is>
       </c>
       <c r="C26" s="1" t="inlineStr">
@@ -17092,97 +17160,97 @@
       </c>
       <c r="D26" s="1" t="inlineStr">
         <is>
-          <t>Haftalik mavsumiy turnir</t>
+          <t>Elite reyd (v3)</t>
         </is>
       </c>
       <c r="E26" s="1" t="inlineStr">
         <is>
-          <t>Doimiy takrorlanuvchi voqea</t>
+          <t>Yuqori stavka</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" s="1" t="n">
-        <v>15</v>
+        <v>19</v>
       </c>
       <c r="B27" s="1" t="inlineStr">
         <is>
-          <t>Buyuk tekislik boʻrisi</t>
+          <t>Makkenzi vodiysi boʻrisi</t>
         </is>
       </c>
       <c r="C27" s="1" t="inlineStr">
         <is>
-          <t>Toʻda</t>
+          <t>Klan</t>
         </is>
       </c>
       <c r="D27" s="1" t="inlineStr">
         <is>
-          <t>Taktika: qurshab olish, chekinish, tuzoq</t>
+          <t>Alfa unvoni va server reytingi (v2)</t>
         </is>
       </c>
       <c r="E27" s="1" t="inlineStr">
         <is>
-          <t>Chuqurroq jang tanlovi</t>
+          <t>Prestij</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="1" t="n">
-        <v>16</v>
+        <v>20</v>
       </c>
       <c r="B28" s="1" t="inlineStr">
         <is>
-          <t>Yevroosiyo kulrang boʻrisi</t>
+          <t>Beringiya boʻrisi</t>
         </is>
       </c>
       <c r="C28" s="1" t="inlineStr">
         <is>
-          <t>PvP</t>
+          <t>Iqtisod</t>
         </is>
       </c>
       <c r="D28" s="1" t="inlineStr">
         <is>
-          <t>Katta toʻda urushi: 20v20</t>
+          <t>🌙 Oy nuri ehtiyoji va passivi · Oy mehrobi (v2) · muz davri zonasi (v3)</t>
         </is>
       </c>
       <c r="E28" s="1" t="inlineStr">
         <is>
-          <t>Yirik format</t>
+          <t>Mifologik bosqich iqtisodi</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" s="1" t="n">
-        <v>17</v>
+        <v>21</v>
       </c>
       <c r="B29" s="1" t="inlineStr">
         <is>
-          <t>Tundra boʻrisi</t>
+          <t>Dahshatli boʻri</t>
         </is>
       </c>
       <c r="C29" s="1" t="inlineStr">
         <is>
-          <t>Klan</t>
+          <t>PvP</t>
         </is>
       </c>
       <c r="D29" s="1" t="inlineStr">
         <is>
-          <t>Toʻdalar ittifoqi (2–3 toʻda)</t>
+          <t>Afsona bossi (v3)</t>
         </is>
       </c>
       <c r="E29" s="1" t="inlineStr">
         <is>
-          <t>Meta-qatlam</t>
+          <t>Mifologik bosqich darvozasi</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" s="1" t="n">
-        <v>18</v>
+        <v>22</v>
       </c>
       <c r="B30" s="1" t="inlineStr">
         <is>
-          <t>Alyaska ichki boʻrisi</t>
+          <t>Amarok</t>
         </is>
       </c>
       <c r="C30" s="1" t="inlineStr">
@@ -17192,189 +17260,117 @@
       </c>
       <c r="D30" s="1" t="inlineStr">
         <is>
-          <t>Elite reyd: hudud bosib olish</t>
+          <t>Tungi reyd: 22:00–06:00 yurish tezligi +25%</t>
         </is>
       </c>
       <c r="E30" s="1" t="inlineStr">
         <is>
-          <t>Yuqori stavka</t>
+          <t>Vaqtga bogʻliq mexanika (kuch emas)</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="1" t="n">
-        <v>19</v>
+        <v>23</v>
       </c>
       <c r="B31" s="1" t="inlineStr">
         <is>
-          <t>Makkenzi vodiysi boʻrisi</t>
+          <t>Geri va Freki</t>
         </is>
       </c>
       <c r="C31" s="1" t="inlineStr">
         <is>
-          <t>Klan</t>
+          <t>Toʻda</t>
         </is>
       </c>
       <c r="D31" s="1" t="inlineStr">
         <is>
-          <t>Alfa unvoni va server reytingi</t>
+          <t>Juft hujum (v3)</t>
         </is>
       </c>
       <c r="E31" s="1" t="inlineStr">
         <is>
-          <t>Prestij</t>
+          <t>Koordinatsiya sinovi</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" s="1" t="n">
-        <v>20</v>
+        <v>24</v>
       </c>
       <c r="B32" s="1" t="inlineStr">
         <is>
-          <t>Beringiya boʻrisi</t>
+          <t>Fenrir</t>
         </is>
       </c>
       <c r="C32" s="1" t="inlineStr">
         <is>
-          <t>Toʻda</t>
+          <t>PvP</t>
         </is>
       </c>
       <c r="D32" s="1" t="inlineStr">
         <is>
-          <t>Muz davri zonasi va qadimgi janglar</t>
+          <t>Zanjirni uzish: urushdan keyin jarohatlanganlar 2× tez davolanadi</t>
         </is>
       </c>
       <c r="E32" s="1" t="inlineStr">
         <is>
-          <t>Yangi kontent bloki</t>
+          <t>Yakuniy qobiliyat (kuch emas)</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" s="1" t="n">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="B33" s="1" t="inlineStr">
         <is>
-          <t>Dahshatli boʻri</t>
+          <t>Koʻk Boʻri</t>
         </is>
       </c>
       <c r="C33" s="1" t="inlineStr">
         <is>
-          <t>PvP</t>
+          <t>Klan</t>
         </is>
       </c>
       <c r="D33" s="1" t="inlineStr">
         <is>
-          <t>Afsona bossi (toʻda bilan)</t>
+          <t>Koʻk Boʻri unvoni · klanga +10% ishlab chiqarish</t>
         </is>
       </c>
       <c r="E33" s="1" t="inlineStr">
         <is>
-          <t>Mifologik bosqich darvozasi</t>
+          <t>Server yetakchisi (kuch emas)</t>
         </is>
       </c>
     </row>
     <row r="34">
-      <c r="A34" s="1" t="n">
-        <v>22</v>
-      </c>
-      <c r="B34" s="1" t="inlineStr">
-        <is>
-          <t>Amarok</t>
-        </is>
-      </c>
-      <c r="C34" s="1" t="inlineStr">
-        <is>
-          <t>PvP</t>
-        </is>
-      </c>
-      <c r="D34" s="1" t="inlineStr">
-        <is>
-          <t>Tungi reyd: hujum kuchi x2</t>
-        </is>
-      </c>
-      <c r="E34" s="1" t="inlineStr">
-        <is>
-          <t>Vaqtga bogʻliq mexanika</t>
-        </is>
-      </c>
+      <c r="A34" s="1" t="n"/>
+      <c r="B34" s="1" t="n"/>
+      <c r="C34" s="1" t="n"/>
+      <c r="D34" s="1" t="n"/>
+      <c r="E34" s="1" t="n"/>
     </row>
     <row r="35">
-      <c r="A35" s="1" t="n">
-        <v>23</v>
-      </c>
-      <c r="B35" s="1" t="inlineStr">
-        <is>
-          <t>Geri va Freki</t>
-        </is>
-      </c>
-      <c r="C35" s="1" t="inlineStr">
-        <is>
-          <t>Toʻda</t>
-        </is>
-      </c>
-      <c r="D35" s="1" t="inlineStr">
-        <is>
-          <t>Juft hujum: ikki toʻda bir vaqtda</t>
-        </is>
-      </c>
-      <c r="E35" s="1" t="inlineStr">
-        <is>
-          <t>Koordinatsiya sinovi</t>
-        </is>
-      </c>
+      <c r="A35" s="1" t="n"/>
+      <c r="B35" s="1" t="n"/>
+      <c r="C35" s="1" t="n"/>
+      <c r="D35" s="1" t="n"/>
+      <c r="E35" s="1" t="n"/>
     </row>
     <row r="36">
-      <c r="A36" s="1" t="n">
-        <v>24</v>
-      </c>
-      <c r="B36" s="1" t="inlineStr">
-        <is>
-          <t>Fenrir</t>
-        </is>
-      </c>
-      <c r="C36" s="1" t="inlineStr">
-        <is>
-          <t>PvP</t>
-        </is>
-      </c>
-      <c r="D36" s="1" t="inlineStr">
-        <is>
-          <t>Zanjirni uzish: urushda toʻliq tiklanish</t>
-        </is>
-      </c>
-      <c r="E36" s="1" t="inlineStr">
-        <is>
-          <t>Yakuniy qobiliyat</t>
-        </is>
-      </c>
+      <c r="A36" s="1" t="n"/>
+      <c r="B36" s="1" t="n"/>
+      <c r="C36" s="1" t="n"/>
+      <c r="D36" s="1" t="n"/>
+      <c r="E36" s="1" t="n"/>
     </row>
     <row r="37">
-      <c r="A37" s="1" t="n">
-        <v>25</v>
-      </c>
-      <c r="B37" s="1" t="inlineStr">
-        <is>
-          <t>Koʻk Boʻri</t>
-        </is>
-      </c>
-      <c r="C37" s="1" t="inlineStr">
-        <is>
-          <t>Klan</t>
-        </is>
-      </c>
-      <c r="D37" s="1" t="inlineStr">
-        <is>
-          <t>Koʻk Boʻri: ittifoqqa +10% doimiy bonus</t>
-        </is>
-      </c>
-      <c r="E37" s="1" t="inlineStr">
-        <is>
-          <t>Server yetakchisi</t>
-        </is>
-      </c>
+      <c r="A37" s="1" t="n"/>
+      <c r="B37" s="1" t="n"/>
+      <c r="C37" s="1" t="n"/>
+      <c r="D37" s="1" t="n"/>
+      <c r="E37" s="1" t="n"/>
     </row>
     <row r="38">
       <c r="A38" s="1" t="inlineStr">
@@ -17386,7 +17382,7 @@
     <row r="39">
       <c r="A39" s="1" t="inlineStr">
         <is>
-          <t>4-daraja oʻyinning eng muhim nuqtasi: oʻyinchi bu yerda yolgʻiz oʻyindan ijtimoiy oʻyinga oʻtadi. Onboarding shu darajagacha 10 daqiqadan oshmasligi kerak.</t>
+          <t>4-daraja oʻyinning eng muhim nuqtasi: oʻyinchi bu yerda yolgʻiz oʻyindan toʻda oʻyiniga oʻtadi. Tanishtiruv shu darajagacha ~10 daqiqa (jami 15 daqiqa) davom etadi.</t>
         </is>
       </c>
     </row>
@@ -17408,7 +17404,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A3:D246"/>
+  <dimension ref="A1:D313"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="28" customWidth="1" min="1" max="1"/>
@@ -17423,6 +17419,8 @@
     <col width="16" customWidth="1" min="10" max="10"/>
   </cols>
   <sheetData>
+    <row r="1"/>
+    <row r="2"/>
     <row r="3">
       <c r="A3" s="1" t="inlineStr">
         <is>
@@ -17433,7 +17431,7 @@
     <row r="4">
       <c r="A4" s="1" t="inlineStr">
         <is>
-          <t>Faqat koʻk rangdagi kataklarni oʻzgartiring. Qolgan hamma narsa formula bilan qayta hisoblanadi.</t>
+          <t>Faqat koʻk rangdagi kataklarni oʻzgartiring. Faylda Excel formulalari yoʻq: oʻzgartirgach `python3 tools/blue_wolf_config.py` ni ishga tushiring — u game_config SQL ni yaratadi va balans tekshiruvlarini bajaradi.</t>
         </is>
       </c>
     </row>
@@ -17775,11 +17773,11 @@
     <row r="25">
       <c r="A25" s="1" t="inlineStr">
         <is>
-          <t>Kech bosqich koeffitsienti</t>
+          <t>Oddiy bosqich koeffitsienti</t>
         </is>
       </c>
       <c r="B25" s="1" t="n">
-        <v>1.25</v>
+        <v>1</v>
       </c>
       <c r="C25" s="1" t="inlineStr">
         <is>
@@ -17788,152 +17786,152 @@
       </c>
       <c r="D25" s="1" t="inlineStr">
         <is>
-          <t>16+ daraja: ataylab qiyinlashadi</t>
+          <t>11–15 daraja</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="1" t="inlineStr">
         <is>
-          <t>Kech bosqich chegarasi</t>
+          <t>Kech bosqich koeffitsienti</t>
         </is>
       </c>
       <c r="B26" s="1" t="n">
-        <v>15</v>
+        <v>1.25</v>
       </c>
       <c r="C26" s="1" t="inlineStr">
         <is>
-          <t>daraja</t>
+          <t>x</t>
         </is>
       </c>
       <c r="D26" s="1" t="inlineStr">
         <is>
-          <t>Shundan keyin kech bosqich</t>
+          <t>16+ daraja: ataylab qiyinlashadi</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" s="1" t="inlineStr">
         <is>
-          <t>Tanishtiruv</t>
+          <t>Kech bosqich chegarasi</t>
+        </is>
+      </c>
+      <c r="B27" s="1" t="n">
+        <v>15</v>
+      </c>
+      <c r="C27" s="1" t="inlineStr">
+        <is>
+          <t>daraja</t>
+        </is>
+      </c>
+      <c r="D27" s="1" t="inlineStr">
+        <is>
+          <t>Shundan keyin kech bosqich</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="1" t="inlineStr">
         <is>
-          <t>Tanishtiruv tugash darajasi</t>
-        </is>
-      </c>
-      <c r="B28" s="1" t="n">
-        <v>5</v>
-      </c>
-      <c r="C28" s="1" t="inlineStr">
-        <is>
-          <t>daraja</t>
-        </is>
-      </c>
-      <c r="D28" s="1" t="inlineStr">
-        <is>
-          <t>Shu darajada qoʻllanma tugaydi</t>
+          <t>Tanishtiruv</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" s="1" t="inlineStr">
         <is>
-          <t>Tanishtiruv maqsadi (daqiqa)</t>
+          <t>Tanishtiruv tugash darajasi</t>
         </is>
       </c>
       <c r="B29" s="1" t="n">
-        <v>15</v>
+        <v>5</v>
       </c>
       <c r="C29" s="1" t="inlineStr">
         <is>
-          <t>daqiqa</t>
+          <t>daraja</t>
         </is>
       </c>
       <c r="D29" s="1" t="inlineStr">
         <is>
-          <t>Boshidan tugashigacha</t>
+          <t>Shu darajada qoʻllanma tugaydi</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" s="1" t="inlineStr">
         <is>
-          <t>Bepul tezlashtirish</t>
+          <t>Tanishtiruv maqsadi (daqiqa)</t>
         </is>
       </c>
       <c r="B30" s="1" t="n">
-        <v>5</v>
+        <v>15</v>
       </c>
       <c r="C30" s="1" t="inlineStr">
         <is>
-          <t>marta</t>
+          <t>daqiqa</t>
         </is>
       </c>
       <c r="D30" s="1" t="inlineStr">
         <is>
-          <t>Tanishtiruvda qurilish darhol tugaydi</t>
+          <t>Boshidan tugashigacha</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="1" t="inlineStr">
         <is>
-          <t>Oʻtkazib yuborish qadami</t>
+          <t>Bepul tezlashtirish</t>
         </is>
       </c>
       <c r="B31" s="1" t="n">
-        <v>12</v>
+        <v>5</v>
       </c>
       <c r="C31" s="1" t="inlineStr">
         <is>
-          <t>qadam</t>
+          <t>marta</t>
         </is>
       </c>
       <c r="D31" s="1" t="inlineStr">
         <is>
-          <t>Shundan keyin «Oʻtkazib yuborish» tugmasi chiqadi</t>
+          <t>Tanishtiruvda qurilish darhol tugaydi</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" s="1" t="inlineStr">
         <is>
-          <t>Vazifalar</t>
+          <t>Oʻtkazib yuborish qadami</t>
+        </is>
+      </c>
+      <c r="B32" s="1" t="n">
+        <v>12</v>
+      </c>
+      <c r="C32" s="1" t="inlineStr">
+        <is>
+          <t>qadam</t>
+        </is>
+      </c>
+      <c r="D32" s="1" t="inlineStr">
+        <is>
+          <t>Shundan keyin «Oʻtkazib yuborish» tugmasi chiqadi</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" s="1" t="inlineStr">
         <is>
-          <t>Kundalik vazifa soni</t>
-        </is>
-      </c>
-      <c r="B33" s="1" t="n">
-        <v>4</v>
-      </c>
-      <c r="C33" s="1" t="inlineStr">
-        <is>
-          <t>ta</t>
-        </is>
-      </c>
-      <c r="D33" s="1" t="inlineStr">
-        <is>
-          <t>Har kuni yangilanadi</t>
+          <t>Vazifalar</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" s="1" t="inlineStr">
         <is>
-          <t>Haftalik vazifa soni</t>
+          <t>Kundalik vazifa soni</t>
         </is>
       </c>
       <c r="B34" s="1" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="C34" s="1" t="inlineStr">
         <is>
@@ -17942,38 +17940,38 @@
       </c>
       <c r="D34" s="1" t="inlineStr">
         <is>
-          <t>Har dushanba yangilanadi</t>
+          <t>Har kuni yangilanadi</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" s="1" t="inlineStr">
         <is>
-          <t>Kundalik mukofot chegarasi</t>
+          <t>Haftalik vazifa soni</t>
         </is>
       </c>
       <c r="B35" s="1" t="n">
-        <v>0.15</v>
+        <v>4</v>
       </c>
       <c r="C35" s="1" t="inlineStr">
         <is>
-          <t>ulush</t>
+          <t>ta</t>
         </is>
       </c>
       <c r="D35" s="1" t="inlineStr">
         <is>
-          <t>Kunlik ishlab chiqarishdan — hammasi qoʻshib</t>
+          <t>Har dushanba yangilanadi</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" s="1" t="inlineStr">
         <is>
-          <t>Haftalik mukofot chegarasi</t>
+          <t>Kundalik mukofot chegarasi</t>
         </is>
       </c>
       <c r="B36" s="1" t="n">
-        <v>0.4</v>
+        <v>0.15</v>
       </c>
       <c r="C36" s="1" t="inlineStr">
         <is>
@@ -17982,18 +17980,18 @@
       </c>
       <c r="D36" s="1" t="inlineStr">
         <is>
-          <t>Bir kunlik ishlab chiqarishdan</t>
+          <t>Kunlik ishlab chiqarishdan — hammasi qoʻshib</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" s="1" t="inlineStr">
         <is>
-          <t>Bosqichli mukofot chegarasi</t>
+          <t>Haftalik mukofot chegarasi</t>
         </is>
       </c>
       <c r="B37" s="1" t="n">
-        <v>0.5</v>
+        <v>0.4</v>
       </c>
       <c r="C37" s="1" t="inlineStr">
         <is>
@@ -18002,89 +18000,89 @@
       </c>
       <c r="D37" s="1" t="inlineStr">
         <is>
-          <t>Bir martalik, kunlik ishlab chiqarishdan</t>
+          <t>Bir kunlik ishlab chiqarishdan</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" s="1" t="inlineStr">
         <is>
-          <t>Tezlashtirish mukofoti</t>
+          <t>Bosqichli mukofot chegarasi</t>
         </is>
       </c>
       <c r="B38" s="1" t="n">
-        <v>10</v>
+        <v>0.5</v>
       </c>
       <c r="C38" s="1" t="inlineStr">
         <is>
-          <t>daqiqa</t>
+          <t>ulush</t>
         </is>
       </c>
       <c r="D38" s="1" t="inlineStr">
         <is>
-          <t>Vazifa uchun beriladigan tezlashtirish</t>
+          <t>Bir martalik, kunlik ishlab chiqarishdan</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" s="1" t="inlineStr">
         <is>
-          <t>Xavfsiz chegara</t>
+          <t>Tezlashtirish mukofoti</t>
         </is>
       </c>
       <c r="B39" s="1" t="n">
-        <v>0.6</v>
+        <v>10</v>
       </c>
       <c r="C39" s="1" t="inlineStr">
         <is>
-          <t>ulush</t>
+          <t>daqiqa</t>
         </is>
       </c>
       <c r="D39" s="1" t="inlineStr">
         <is>
-          <t>Barcha vazifa mukofoti kunlik ishlab chiqarishdan oshmasin</t>
+          <t>Vazifa uchun beriladigan tezlashtirish</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" s="1" t="inlineStr">
         <is>
-          <t>Askar iqtisodi</t>
+          <t>Xavfsiz chegara</t>
+        </is>
+      </c>
+      <c r="B40" s="1" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="C40" s="1" t="inlineStr">
+        <is>
+          <t>ulush</t>
+        </is>
+      </c>
+      <c r="D40" s="1" t="inlineStr">
+        <is>
+          <t>Barcha vazifa mukofoti kunlik ishlab chiqarishdan oshmasin</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" s="1" t="inlineStr">
         <is>
-          <t>Yangi askar: bazaviy goʻsht</t>
-        </is>
-      </c>
-      <c r="B41" s="1" t="n">
-        <v>20</v>
-      </c>
-      <c r="C41" s="1" t="inlineStr">
-        <is>
-          <t>kg</t>
-        </is>
-      </c>
-      <c r="D41" s="1" t="inlineStr">
-        <is>
-          <t>1-tier askar yigʻish</t>
+          <t>Askar iqtisodi</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" s="1" t="inlineStr">
         <is>
-          <t>Yangi askar: bazaviy suyak</t>
+          <t>Yangi askar: bazaviy goʻsht</t>
         </is>
       </c>
       <c r="B42" s="1" t="n">
-        <v>8</v>
+        <v>20</v>
       </c>
       <c r="C42" s="1" t="inlineStr">
         <is>
-          <t>birlik</t>
+          <t>kg</t>
         </is>
       </c>
       <c r="D42" s="1" t="inlineStr">
@@ -18096,15 +18094,15 @@
     <row r="43">
       <c r="A43" s="1" t="inlineStr">
         <is>
-          <t>Yangi askar: bazaviy vaqt</t>
+          <t>Yangi askar: bazaviy suyak</t>
         </is>
       </c>
       <c r="B43" s="1" t="n">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="C43" s="1" t="inlineStr">
         <is>
-          <t>daqiqa</t>
+          <t>birlik</t>
         </is>
       </c>
       <c r="D43" s="1" t="inlineStr">
@@ -18116,51 +18114,51 @@
     <row r="44">
       <c r="A44" s="1" t="inlineStr">
         <is>
-          <t>Almashtirish yoʻqotishi</t>
+          <t>Yangi askar: bazaviy vaqt</t>
         </is>
       </c>
       <c r="B44" s="1" t="n">
-        <v>0.1</v>
+        <v>4</v>
       </c>
       <c r="C44" s="1" t="inlineStr">
         <is>
-          <t>ulush</t>
+          <t>daqiqa</t>
         </is>
       </c>
       <c r="D44" s="1" t="inlineStr">
         <is>
-          <t>Kuch konversiyasida yoʻqoladigan ulush</t>
+          <t>1-tier askar yigʻish</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" s="1" t="inlineStr">
         <is>
-          <t>Almashtirish narx ulushi</t>
+          <t>Almashtirish yoʻqotishi</t>
         </is>
       </c>
       <c r="B45" s="1" t="n">
-        <v>0.6</v>
+        <v>0.1</v>
       </c>
       <c r="C45" s="1" t="inlineStr">
         <is>
-          <t>x</t>
+          <t>ulush</t>
         </is>
       </c>
       <c r="D45" s="1" t="inlineStr">
         <is>
-          <t>Yangi askar narxiga nisbatan</t>
+          <t>Kuch konversiyasida yoʻqoladigan ulush</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" s="1" t="inlineStr">
         <is>
-          <t>Almashtirish vaqt ulushi</t>
+          <t>Almashtirish narx ulushi</t>
         </is>
       </c>
       <c r="B46" s="1" t="n">
-        <v>0.5</v>
+        <v>0.6</v>
       </c>
       <c r="C46" s="1" t="inlineStr">
         <is>
@@ -18169,85 +18167,85 @@
       </c>
       <c r="D46" s="1" t="inlineStr">
         <is>
-          <t>Yangi askar vaqtiga nisbatan</t>
+          <t>Yangi askar narxiga nisbatan</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" s="1" t="inlineStr">
         <is>
-          <t>Qoʻshin toʻlganligi</t>
+          <t>Almashtirish vaqt ulushi</t>
+        </is>
+      </c>
+      <c r="B47" s="1" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="C47" s="1" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
+      <c r="D47" s="1" t="inlineStr">
+        <is>
+          <t>Yangi askar vaqtiga nisbatan</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" s="1" t="inlineStr">
         <is>
-          <t>Normal toʻlganlik</t>
-        </is>
-      </c>
-      <c r="B48" s="1" t="n">
-        <v>0.6</v>
-      </c>
-      <c r="C48" s="1" t="inlineStr">
-        <is>
-          <t>ulush</t>
-        </is>
-      </c>
-      <c r="D48" s="1" t="inlineStr">
-        <is>
-          <t>Shu nuqtada vaqt koeffitsienti 1.00</t>
+          <t>Qoʻshin toʻlganligi</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" s="1" t="inlineStr">
         <is>
-          <t>Toʻlganlik eksponenti</t>
+          <t>Normal toʻlganlik</t>
         </is>
       </c>
       <c r="B49" s="1" t="n">
-        <v>1.8</v>
+        <v>0.6</v>
       </c>
       <c r="C49" s="1" t="inlineStr">
         <is>
-          <t>daraja</t>
+          <t>ulush</t>
         </is>
       </c>
       <c r="D49" s="1" t="inlineStr">
         <is>
-          <t>Qanchalik keskin oʻzgarishi</t>
+          <t>Shu nuqtada vaqt koeffitsienti 1.00</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" s="1" t="inlineStr">
         <is>
-          <t>Minimal vaqt koeffitsienti</t>
+          <t>Toʻlganlik eksponenti</t>
         </is>
       </c>
       <c r="B50" s="1" t="n">
-        <v>0.5</v>
+        <v>1.8</v>
       </c>
       <c r="C50" s="1" t="inlineStr">
         <is>
-          <t>x</t>
+          <t>daraja</t>
         </is>
       </c>
       <c r="D50" s="1" t="inlineStr">
         <is>
-          <t>Qoʻshin juda kam boʻlganda chegirma</t>
+          <t>Qanchalik keskin oʻzgarishi</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" s="1" t="inlineStr">
         <is>
-          <t>Maksimal vaqt koeffitsienti</t>
+          <t>Minimal vaqt koeffitsienti</t>
         </is>
       </c>
       <c r="B51" s="1" t="n">
-        <v>3</v>
+        <v>0.5</v>
       </c>
       <c r="C51" s="1" t="inlineStr">
         <is>
@@ -18256,7 +18254,7 @@
       </c>
       <c r="D51" s="1" t="inlineStr">
         <is>
-          <t>Qoʻshin toʻlganda jazo</t>
+          <t>Qoʻshin juda kam boʻlganda chegirma</t>
         </is>
       </c>
     </row>
@@ -18610,7 +18608,7 @@
       </c>
       <c r="D70" s="1" t="inlineStr">
         <is>
-          <t>Bir martalik, doimiy</t>
+          <t>4–9 darajada erta ochish; 10-darajadan bepul</t>
         </is>
       </c>
     </row>
@@ -19505,75 +19503,75 @@
     <row r="118">
       <c r="A118" s="1" t="inlineStr">
         <is>
-          <t>Bazaviy chirish vaqti</t>
+          <t>Bazaviy passiv suv</t>
         </is>
       </c>
       <c r="B118" s="1" t="n">
-        <v>12</v>
+        <v>0.25</v>
       </c>
       <c r="C118" s="1" t="inlineStr">
         <is>
-          <t>soat</t>
+          <t>birlik/soat</t>
         </is>
       </c>
       <c r="D118" s="1" t="inlineStr">
         <is>
-          <t>Goʻsht buzilmasdan turadi</t>
+          <t>Gʻor oʻzi yigʻadi</t>
         </is>
       </c>
     </row>
     <row r="119">
       <c r="A119" s="1" t="inlineStr">
         <is>
-          <t>Chirish oʻsishi</t>
+          <t>Passiv suv oʻsishi</t>
         </is>
       </c>
       <c r="B119" s="1" t="n">
-        <v>0.12</v>
+        <v>1.25</v>
       </c>
       <c r="C119" s="1" t="inlineStr">
         <is>
-          <t>ulush/daraja</t>
+          <t>x</t>
         </is>
       </c>
       <c r="D119" s="1" t="inlineStr">
         <is>
-          <t>Har darajada +12%</t>
+          <t>Har darajada — suv ehtiyojiga moslangan (~2×)</t>
         </is>
       </c>
     </row>
     <row r="120">
       <c r="A120" s="1" t="inlineStr">
         <is>
-          <t>Bazaviy passiv suv</t>
+          <t>Bazaviy himoya</t>
         </is>
       </c>
       <c r="B120" s="1" t="n">
-        <v>5</v>
+        <v>0.3</v>
       </c>
       <c r="C120" s="1" t="inlineStr">
         <is>
-          <t>birlik/soat</t>
+          <t>ulush</t>
         </is>
       </c>
       <c r="D120" s="1" t="inlineStr">
         <is>
-          <t>Gʻor oʻzi yigʻadi</t>
+          <t>Reyddan saqlanadigan zaxira</t>
         </is>
       </c>
     </row>
     <row r="121">
       <c r="A121" s="1" t="inlineStr">
         <is>
-          <t>Passiv suv oʻsishi</t>
+          <t>Himoya oʻsishi</t>
         </is>
       </c>
       <c r="B121" s="1" t="n">
-        <v>1.2</v>
+        <v>0.02</v>
       </c>
       <c r="C121" s="1" t="inlineStr">
         <is>
-          <t>x</t>
+          <t>ulush/daraja</t>
         </is>
       </c>
       <c r="D121" s="1" t="inlineStr">
@@ -19585,492 +19583,479 @@
     <row r="122">
       <c r="A122" s="1" t="inlineStr">
         <is>
-          <t>Bazaviy himoya</t>
+          <t>Gʻor narxi: tosh</t>
         </is>
       </c>
       <c r="B122" s="1" t="n">
-        <v>0.3</v>
+        <v>100</v>
       </c>
       <c r="C122" s="1" t="inlineStr">
         <is>
-          <t>ulush</t>
+          <t>birlik</t>
         </is>
       </c>
       <c r="D122" s="1" t="inlineStr">
         <is>
-          <t>Reyddan saqlanadigan zaxira</t>
+          <t>1→2 daraja uchun</t>
         </is>
       </c>
     </row>
     <row r="123">
       <c r="A123" s="1" t="inlineStr">
         <is>
-          <t>Himoya oʻsishi</t>
+          <t>Gʻor narxi: shox-shabba</t>
         </is>
       </c>
       <c r="B123" s="1" t="n">
-        <v>0.02</v>
+        <v>60</v>
       </c>
       <c r="C123" s="1" t="inlineStr">
         <is>
-          <t>ulush/daraja</t>
+          <t>birlik</t>
         </is>
       </c>
       <c r="D123" s="1" t="inlineStr">
         <is>
-          <t>Har darajada</t>
+          <t>1→2 daraja uchun</t>
         </is>
       </c>
     </row>
     <row r="124">
       <c r="A124" s="1" t="inlineStr">
         <is>
-          <t>Gʻor narxi: tosh</t>
-        </is>
-      </c>
-      <c r="B124" s="1" t="n">
-        <v>100</v>
-      </c>
-      <c r="C124" s="1" t="inlineStr">
-        <is>
-          <t>birlik</t>
-        </is>
-      </c>
-      <c r="D124" s="1" t="inlineStr">
-        <is>
-          <t>1→2 daraja uchun</t>
+          <t>Ustaxona qoyasi</t>
         </is>
       </c>
     </row>
     <row r="125">
       <c r="A125" s="1" t="inlineStr">
         <is>
-          <t>Gʻor narxi: shox-shabba</t>
+          <t>Bazaviy ishlab chiqarish</t>
         </is>
       </c>
       <c r="B125" s="1" t="n">
-        <v>60</v>
+        <v>20</v>
       </c>
       <c r="C125" s="1" t="inlineStr">
         <is>
-          <t>birlik</t>
+          <t>birlik/soat</t>
         </is>
       </c>
       <c r="D125" s="1" t="inlineStr">
         <is>
-          <t>1→2 daraja uchun</t>
+          <t>Jami qurilish resursi</t>
         </is>
       </c>
     </row>
     <row r="126">
       <c r="A126" s="1" t="inlineStr">
         <is>
-          <t>Ustaxona qoyasi</t>
+          <t>Ishlab chiqarish oʻsishi</t>
+        </is>
+      </c>
+      <c r="B126" s="1" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="C126" s="1" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
+      <c r="D126" s="1" t="inlineStr">
+        <is>
+          <t>Har darajada — narx oʻsishidan (1.30) past boʻlishi shart</t>
         </is>
       </c>
     </row>
     <row r="127">
       <c r="A127" s="1" t="inlineStr">
         <is>
-          <t>Bazaviy ishlab chiqarish</t>
+          <t>Ustaxona buferi</t>
         </is>
       </c>
       <c r="B127" s="1" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="C127" s="1" t="inlineStr">
         <is>
-          <t>birlik/soat</t>
+          <t>soat</t>
         </is>
       </c>
       <c r="D127" s="1" t="inlineStr">
         <is>
-          <t>Jami qurilish resursi</t>
+          <t>Bufer = soatlik ishlab chiqarish × shu; qurilish resurslari ombori cheklanmagan</t>
         </is>
       </c>
     </row>
     <row r="128">
       <c r="A128" s="1" t="inlineStr">
         <is>
-          <t>Ishlab chiqarish oʻsishi</t>
+          <t>Ustaxona narxi: tosh</t>
         </is>
       </c>
       <c r="B128" s="1" t="n">
-        <v>1.22</v>
+        <v>150</v>
       </c>
       <c r="C128" s="1" t="inlineStr">
         <is>
-          <t>x</t>
+          <t>birlik</t>
         </is>
       </c>
       <c r="D128" s="1" t="inlineStr">
         <is>
-          <t>Har darajada — narx oʻsishidan (1.30) past boʻlishi shart</t>
+          <t>1→2 daraja uchun</t>
         </is>
       </c>
     </row>
     <row r="129">
       <c r="A129" s="1" t="inlineStr">
         <is>
-          <t>Ombor koeffitsienti</t>
+          <t>Ustaxona narxi: shox-shabba</t>
         </is>
       </c>
       <c r="B129" s="1" t="n">
-        <v>10</v>
+        <v>100</v>
       </c>
       <c r="C129" s="1" t="inlineStr">
         <is>
-          <t>soat</t>
+          <t>birlik</t>
         </is>
       </c>
       <c r="D129" s="1" t="inlineStr">
         <is>
-          <t>Sigʻim = soatlik ishlab chiqarish × shu</t>
+          <t>1→2 daraja uchun</t>
         </is>
       </c>
     </row>
     <row r="130">
       <c r="A130" s="1" t="inlineStr">
         <is>
-          <t>Bazaviy yigʻuvchi slot</t>
+          <t>Ustaxona narxi: suyak</t>
         </is>
       </c>
       <c r="B130" s="1" t="n">
-        <v>2</v>
+        <v>40</v>
       </c>
       <c r="C130" s="1" t="inlineStr">
         <is>
-          <t>ta</t>
+          <t>birlik</t>
         </is>
       </c>
       <c r="D130" s="1" t="inlineStr">
         <is>
-          <t>Slot = shu + butun(daraja/3)</t>
+          <t>1→2 daraja uchun</t>
         </is>
       </c>
     </row>
     <row r="131">
       <c r="A131" s="1" t="inlineStr">
         <is>
-          <t>Ustaxona narxi: tosh</t>
-        </is>
-      </c>
-      <c r="B131" s="1" t="n">
-        <v>150</v>
-      </c>
-      <c r="C131" s="1" t="inlineStr">
-        <is>
-          <t>birlik</t>
-        </is>
-      </c>
-      <c r="D131" s="1" t="inlineStr">
-        <is>
-          <t>1→2 daraja uchun</t>
+          <t>Binolar — umumiy</t>
         </is>
       </c>
     </row>
     <row r="132">
       <c r="A132" s="1" t="inlineStr">
         <is>
-          <t>Ustaxona narxi: shox-shabba</t>
+          <t>Bino narx oʻsishi</t>
         </is>
       </c>
       <c r="B132" s="1" t="n">
-        <v>100</v>
+        <v>1.3</v>
       </c>
       <c r="C132" s="1" t="inlineStr">
         <is>
-          <t>birlik</t>
+          <t>x</t>
         </is>
       </c>
       <c r="D132" s="1" t="inlineStr">
         <is>
-          <t>1→2 daraja uchun</t>
+          <t>Har darajada (25 daraja uchun moslangan)</t>
         </is>
       </c>
     </row>
     <row r="133">
       <c r="A133" s="1" t="inlineStr">
         <is>
-          <t>Ustaxona narxi: suyak</t>
+          <t>Bino vaqt oʻsishi</t>
         </is>
       </c>
       <c r="B133" s="1" t="n">
-        <v>40</v>
+        <v>1.25</v>
       </c>
       <c r="C133" s="1" t="inlineStr">
         <is>
-          <t>birlik</t>
+          <t>x</t>
         </is>
       </c>
       <c r="D133" s="1" t="inlineStr">
         <is>
-          <t>1→2 daraja uchun</t>
+          <t>Har darajada (25 daraja uchun moslangan)</t>
         </is>
       </c>
     </row>
     <row r="134">
       <c r="A134" s="1" t="inlineStr">
         <is>
-          <t>Binolar — umumiy</t>
+          <t>Bazaviy qurilish vaqti</t>
+        </is>
+      </c>
+      <c r="B134" s="1" t="n">
+        <v>10</v>
+      </c>
+      <c r="C134" s="1" t="inlineStr">
+        <is>
+          <t>daqiqa</t>
+        </is>
+      </c>
+      <c r="D134" s="1" t="inlineStr">
+        <is>
+          <t>1→2 daraja uchun</t>
         </is>
       </c>
     </row>
     <row r="135">
       <c r="A135" s="1" t="inlineStr">
         <is>
-          <t>Bino narx oʻsishi</t>
+          <t>Kuchaytirish rejasi</t>
         </is>
       </c>
       <c r="B135" s="1" t="n">
-        <v>1.3</v>
+        <v>7</v>
       </c>
       <c r="C135" s="1" t="inlineStr">
         <is>
-          <t>x</t>
+          <t>kun</t>
         </is>
       </c>
       <c r="D135" s="1" t="inlineStr">
         <is>
-          <t>Har darajada (25 daraja uchun moslangan)</t>
+          <t>Keyingi darajaga resurs toʻplash muddati</t>
         </is>
       </c>
     </row>
     <row r="136">
       <c r="A136" s="1" t="inlineStr">
         <is>
-          <t>Bino vaqt oʻsishi</t>
-        </is>
-      </c>
-      <c r="B136" s="1" t="n">
-        <v>1.25</v>
-      </c>
-      <c r="C136" s="1" t="inlineStr">
-        <is>
-          <t>x</t>
-        </is>
-      </c>
-      <c r="D136" s="1" t="inlineStr">
-        <is>
-          <t>Har darajada (25 daraja uchun moslangan)</t>
+          <t>Rollar va tierlar</t>
         </is>
       </c>
     </row>
     <row r="137">
       <c r="A137" s="1" t="inlineStr">
         <is>
-          <t>Bazaviy qurilish vaqti</t>
+          <t>Alfa bonusi</t>
         </is>
       </c>
       <c r="B137" s="1" t="n">
-        <v>10</v>
+        <v>0.03</v>
       </c>
       <c r="C137" s="1" t="inlineStr">
         <is>
-          <t>daqiqa</t>
+          <t>ulush/daraja</t>
         </is>
       </c>
       <c r="D137" s="1" t="inlineStr">
         <is>
-          <t>1→2 daraja uchun</t>
+          <t>Askar statiga qoʻshiladi (25-darajada +75%)</t>
         </is>
       </c>
     </row>
     <row r="138">
       <c r="A138" s="1" t="inlineStr">
         <is>
-          <t>Kuchaytirish rejasi</t>
+          <t>Tier koeffitsienti</t>
         </is>
       </c>
       <c r="B138" s="1" t="n">
-        <v>7</v>
+        <v>1.45</v>
       </c>
       <c r="C138" s="1" t="inlineStr">
         <is>
-          <t>kun</t>
+          <t>x</t>
         </is>
       </c>
       <c r="D138" s="1" t="inlineStr">
         <is>
-          <t>Keyingi darajaga resurs toʻplash muddati</t>
+          <t>Har tierda stat shuncha oshadi</t>
         </is>
       </c>
     </row>
     <row r="139">
       <c r="A139" s="1" t="inlineStr">
         <is>
-          <t>Rollar va tierlar</t>
+          <t>Tier ochilish qadami</t>
+        </is>
+      </c>
+      <c r="B139" s="1" t="n">
+        <v>4</v>
+      </c>
+      <c r="C139" s="1" t="inlineStr">
+        <is>
+          <t>daraja</t>
+        </is>
+      </c>
+      <c r="D139" s="1" t="inlineStr">
+        <is>
+          <t>Maks tier = MAX(1, MIN(6, alfa darajasi ÷ shu, bino ÷ shu))</t>
         </is>
       </c>
     </row>
     <row r="140">
       <c r="A140" s="1" t="inlineStr">
         <is>
-          <t>Alfa bonusi</t>
+          <t>Qarshi-kuch bonusi</t>
         </is>
       </c>
       <c r="B140" s="1" t="n">
-        <v>0.03</v>
+        <v>1.3</v>
       </c>
       <c r="C140" s="1" t="inlineStr">
         <is>
-          <t>ulush/daraja</t>
+          <t>x</t>
         </is>
       </c>
       <c r="D140" s="1" t="inlineStr">
         <is>
-          <t>Askar statiga qoʻshiladi (25-darajada +75%)</t>
+          <t>Uchburchakda ustunlik</t>
         </is>
       </c>
     </row>
     <row r="141">
       <c r="A141" s="1" t="inlineStr">
         <is>
-          <t>Tier koeffitsienti</t>
+          <t>Namuna alfa darajasi</t>
         </is>
       </c>
       <c r="B141" s="1" t="n">
-        <v>1.45</v>
+        <v>19</v>
       </c>
       <c r="C141" s="1" t="inlineStr">
         <is>
-          <t>x</t>
+          <t>daraja</t>
         </is>
       </c>
       <c r="D141" s="1" t="inlineStr">
         <is>
-          <t>Har tierda stat shuncha oshadi</t>
+          <t>Quyidagi CP jadvali shu darajaga hisoblangan</t>
         </is>
       </c>
     </row>
     <row r="142">
       <c r="A142" s="1" t="inlineStr">
         <is>
-          <t>Tier ochilish qadami</t>
+          <t>Taqsimot: razvedkachi</t>
         </is>
       </c>
       <c r="B142" s="1" t="n">
-        <v>4</v>
+        <v>0.2</v>
       </c>
       <c r="C142" s="1" t="inlineStr">
         <is>
-          <t>daraja</t>
+          <t>ulush</t>
         </is>
       </c>
       <c r="D142" s="1" t="inlineStr">
         <is>
-          <t>Maks tier = alfa darajasi ÷ shu</t>
+          <t>Tavsiya etilgan slot ulushi</t>
         </is>
       </c>
     </row>
     <row r="143">
       <c r="A143" s="1" t="inlineStr">
         <is>
-          <t>Qarshi-kuch bonusi</t>
+          <t>Taqsimot: hujumchi</t>
         </is>
       </c>
       <c r="B143" s="1" t="n">
-        <v>1.3</v>
+        <v>0.45</v>
       </c>
       <c r="C143" s="1" t="inlineStr">
         <is>
-          <t>x</t>
+          <t>ulush</t>
         </is>
       </c>
       <c r="D143" s="1" t="inlineStr">
         <is>
-          <t>Uchburchakda ustunlik</t>
+          <t>Tavsiya etilgan slot ulushi</t>
         </is>
       </c>
     </row>
     <row r="144">
       <c r="A144" s="1" t="inlineStr">
         <is>
-          <t>Mashq narxi: goʻsht</t>
+          <t>Taqsimot: himoyachi</t>
         </is>
       </c>
       <c r="B144" s="1" t="n">
-        <v>200</v>
+        <v>0.2</v>
       </c>
       <c r="C144" s="1" t="inlineStr">
         <is>
-          <t>kg</t>
+          <t>ulush</t>
         </is>
       </c>
       <c r="D144" s="1" t="inlineStr">
         <is>
-          <t>1→2 tier</t>
+          <t>Tavsiya etilgan slot ulushi</t>
         </is>
       </c>
     </row>
     <row r="145">
       <c r="A145" s="1" t="inlineStr">
         <is>
-          <t>Mashq narxi: suyak</t>
+          <t>Taqsimot: ovchi</t>
         </is>
       </c>
       <c r="B145" s="1" t="n">
-        <v>80</v>
+        <v>0.15</v>
       </c>
       <c r="C145" s="1" t="inlineStr">
         <is>
-          <t>birlik</t>
+          <t>ulush</t>
         </is>
       </c>
       <c r="D145" s="1" t="inlineStr">
         <is>
-          <t>1→2 tier</t>
+          <t>Eng kamida 1 ta ovchi doim boʻladi</t>
         </is>
       </c>
     </row>
     <row r="146">
       <c r="A146" s="1" t="inlineStr">
         <is>
-          <t>Mashq narx oʻsishi</t>
-        </is>
-      </c>
-      <c r="B146" s="1" t="n">
-        <v>2.2</v>
-      </c>
-      <c r="C146" s="1" t="inlineStr">
-        <is>
-          <t>x</t>
-        </is>
-      </c>
-      <c r="D146" s="1" t="inlineStr">
-        <is>
-          <t>Har tierda</t>
+          <t>Mashq maydoni</t>
         </is>
       </c>
     </row>
     <row r="147">
       <c r="A147" s="1" t="inlineStr">
         <is>
-          <t>Mashq vaqti</t>
+          <t>Tier qadami (bino)</t>
         </is>
       </c>
       <c r="B147" s="1" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="C147" s="1" t="inlineStr">
         <is>
-          <t>soat</t>
+          <t>daraja</t>
         </is>
       </c>
       <c r="D147" s="1" t="inlineStr">
         <is>
-          <t>1→2 tier</t>
+          <t>Har 4 daraja = 1 tier ochiladi</t>
         </is>
       </c>
     </row>
     <row r="148">
       <c r="A148" s="1" t="inlineStr">
         <is>
-          <t>Namuna alfa darajasi</t>
+          <t>Bino cheklovi</t>
         </is>
       </c>
       <c r="B148" s="1" t="n">
-        <v>19</v>
+        <v>0</v>
       </c>
       <c r="C148" s="1" t="inlineStr">
         <is>
@@ -20079,479 +20064,479 @@
       </c>
       <c r="D148" s="1" t="inlineStr">
         <is>
-          <t>Quyidagi CP jadvali shu darajaga hisoblangan</t>
+          <t>Bino alfa darajasidan oshmaydi — maks daraja = oʻyinchi darajasi</t>
         </is>
       </c>
     </row>
     <row r="149">
       <c r="A149" s="1" t="inlineStr">
         <is>
-          <t>Taqsimot: razvedkachi</t>
+          <t>Maydon narxi: tosh</t>
         </is>
       </c>
       <c r="B149" s="1" t="n">
-        <v>0.2</v>
+        <v>180</v>
       </c>
       <c r="C149" s="1" t="inlineStr">
         <is>
-          <t>ulush</t>
+          <t>birlik</t>
         </is>
       </c>
       <c r="D149" s="1" t="inlineStr">
         <is>
-          <t>Tavsiya etilgan slot ulushi</t>
+          <t>1→2 daraja</t>
         </is>
       </c>
     </row>
     <row r="150">
       <c r="A150" s="1" t="inlineStr">
         <is>
-          <t>Taqsimot: hujumchi</t>
+          <t>Maydon narxi: suyak</t>
         </is>
       </c>
       <c r="B150" s="1" t="n">
-        <v>0.45</v>
+        <v>90</v>
       </c>
       <c r="C150" s="1" t="inlineStr">
         <is>
-          <t>ulush</t>
+          <t>birlik</t>
         </is>
       </c>
       <c r="D150" s="1" t="inlineStr">
         <is>
-          <t>Tavsiya etilgan slot ulushi</t>
+          <t>1→2 daraja</t>
         </is>
       </c>
     </row>
     <row r="151">
       <c r="A151" s="1" t="inlineStr">
         <is>
-          <t>Taqsimot: himoyachi</t>
+          <t>Maydon narxi: teri</t>
         </is>
       </c>
       <c r="B151" s="1" t="n">
-        <v>0.2</v>
+        <v>150</v>
       </c>
       <c r="C151" s="1" t="inlineStr">
         <is>
-          <t>ulush</t>
+          <t>birlik</t>
         </is>
       </c>
       <c r="D151" s="1" t="inlineStr">
         <is>
-          <t>Tavsiya etilgan slot ulushi</t>
+          <t>1→2 daraja</t>
         </is>
       </c>
     </row>
     <row r="152">
       <c r="A152" s="1" t="inlineStr">
         <is>
-          <t>Taqsimot: ovchi</t>
+          <t>Mashq tezligi bonusi</t>
         </is>
       </c>
       <c r="B152" s="1" t="n">
-        <v>0.15</v>
+        <v>0.04</v>
       </c>
       <c r="C152" s="1" t="inlineStr">
         <is>
-          <t>ulush</t>
+          <t>ulush/daraja</t>
         </is>
       </c>
       <c r="D152" s="1" t="inlineStr">
         <is>
-          <t>Eng kamida 1 ta ovchi doim boʻladi</t>
+          <t>Mashq vaqtini qisqartiradi</t>
         </is>
       </c>
     </row>
     <row r="153">
       <c r="A153" s="1" t="inlineStr">
         <is>
-          <t>Mashq maydoni</t>
+          <t>Bino narxi: Razvedka qoyasi</t>
+        </is>
+      </c>
+      <c r="B153" s="1" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="C153" s="1" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
+      <c r="D153" s="1" t="inlineStr">
+        <is>
+          <t>Bazaviy maydon narxiga nisbatan</t>
         </is>
       </c>
     </row>
     <row r="154">
       <c r="A154" s="1" t="inlineStr">
         <is>
-          <t>Tier qadami (bino)</t>
+          <t>Bino narxi: Jang maydoni</t>
         </is>
       </c>
       <c r="B154" s="1" t="n">
-        <v>4</v>
+        <v>0.7</v>
       </c>
       <c r="C154" s="1" t="inlineStr">
         <is>
-          <t>daraja</t>
+          <t>x</t>
         </is>
       </c>
       <c r="D154" s="1" t="inlineStr">
         <is>
-          <t>Har 4 daraja = 1 tier ochiladi</t>
+          <t>Eng qimmat — hujumchi asosiy rol</t>
         </is>
       </c>
     </row>
     <row r="155">
       <c r="A155" s="1" t="inlineStr">
         <is>
-          <t>Bino cheklovi</t>
+          <t>Bino narxi: Himoya devori</t>
         </is>
       </c>
       <c r="B155" s="1" t="n">
-        <v>0</v>
+        <v>0.6</v>
       </c>
       <c r="C155" s="1" t="inlineStr">
         <is>
-          <t>daraja</t>
+          <t>x</t>
         </is>
       </c>
       <c r="D155" s="1" t="inlineStr">
         <is>
-          <t>Bino alfa darajasidan oshmaydi — maks daraja = oʻyinchi darajasi</t>
+          <t>Bazaviy maydon narxiga nisbatan</t>
         </is>
       </c>
     </row>
     <row r="156">
       <c r="A156" s="1" t="inlineStr">
         <is>
-          <t>Maydon narxi: tosh</t>
+          <t>Bino narxi: Ov soʻqmogʻi</t>
         </is>
       </c>
       <c r="B156" s="1" t="n">
-        <v>180</v>
+        <v>0.45</v>
       </c>
       <c r="C156" s="1" t="inlineStr">
         <is>
-          <t>birlik</t>
+          <t>x</t>
         </is>
       </c>
       <c r="D156" s="1" t="inlineStr">
         <is>
-          <t>1→2 daraja</t>
+          <t>Eng arzon — boshidan kerak boʻladi</t>
         </is>
       </c>
     </row>
     <row r="157">
       <c r="A157" s="1" t="inlineStr">
         <is>
-          <t>Maydon narxi: suyak</t>
-        </is>
-      </c>
-      <c r="B157" s="1" t="n">
-        <v>90</v>
-      </c>
-      <c r="C157" s="1" t="inlineStr">
-        <is>
-          <t>birlik</t>
-        </is>
-      </c>
-      <c r="D157" s="1" t="inlineStr">
-        <is>
-          <t>1→2 daraja</t>
+          <t>Lager va oazis</t>
         </is>
       </c>
     </row>
     <row r="158">
       <c r="A158" s="1" t="inlineStr">
         <is>
-          <t>Maydon narxi: goʻsht</t>
+          <t>Lager yigʻim koeffitsienti</t>
         </is>
       </c>
       <c r="B158" s="1" t="n">
-        <v>150</v>
+        <v>0.1</v>
       </c>
       <c r="C158" s="1" t="inlineStr">
         <is>
-          <t>kg</t>
+          <t>x</t>
         </is>
       </c>
       <c r="D158" s="1" t="inlineStr">
         <is>
-          <t>1→2 daraja</t>
+          <t>Bir boʻri = Ustaxona soatlik ishlab chiqarishining shuncha qismi</t>
         </is>
       </c>
     </row>
     <row r="159">
       <c r="A159" s="1" t="inlineStr">
         <is>
-          <t>Mashq tezligi bonusi</t>
+          <t>Lager tier bonusi</t>
         </is>
       </c>
       <c r="B159" s="1" t="n">
-        <v>0.04</v>
+        <v>0.05</v>
       </c>
       <c r="C159" s="1" t="inlineStr">
         <is>
-          <t>ulush/daraja</t>
+          <t>ulush/tier</t>
         </is>
       </c>
       <c r="D159" s="1" t="inlineStr">
         <is>
-          <t>Mashq vaqtini qisqartiradi</t>
+          <t>Yuqori tier tezroq yigʻadi</t>
         </is>
       </c>
     </row>
     <row r="160">
       <c r="A160" s="1" t="inlineStr">
         <is>
-          <t>Bino narxi: Razvedka qoyasi</t>
+          <t>Lager muddati</t>
         </is>
       </c>
       <c r="B160" s="1" t="n">
-        <v>0.5</v>
+        <v>8</v>
       </c>
       <c r="C160" s="1" t="inlineStr">
         <is>
-          <t>x</t>
+          <t>soat</t>
         </is>
       </c>
       <c r="D160" s="1" t="inlineStr">
         <is>
-          <t>Bazaviy maydon narxiga nisbatan</t>
+          <t>Shundan keyin toʻda inga qaytadi</t>
         </is>
       </c>
     </row>
     <row r="161">
       <c r="A161" s="1" t="inlineStr">
         <is>
-          <t>Bino narxi: Jang maydoni</t>
+          <t>Lagerga yuborish ulushi</t>
         </is>
       </c>
       <c r="B161" s="1" t="n">
-        <v>0.7</v>
+        <v>0.5</v>
       </c>
       <c r="C161" s="1" t="inlineStr">
         <is>
-          <t>x</t>
+          <t>ulush</t>
         </is>
       </c>
       <c r="D161" s="1" t="inlineStr">
         <is>
-          <t>Eng qimmat — hujumchi asosiy rol</t>
+          <t>Toʻdaning eng koʻpi shuncha qismi</t>
         </is>
       </c>
     </row>
     <row r="162">
       <c r="A162" s="1" t="inlineStr">
         <is>
-          <t>Bino narxi: Himoya devori</t>
+          <t>Oazis soni (server)</t>
         </is>
       </c>
       <c r="B162" s="1" t="n">
-        <v>0.6</v>
+        <v>20</v>
       </c>
       <c r="C162" s="1" t="inlineStr">
         <is>
-          <t>x</t>
+          <t>ta</t>
         </is>
       </c>
       <c r="D162" s="1" t="inlineStr">
         <is>
-          <t>Bazaviy maydon narxiga nisbatan</t>
+          <t>Cheklangan — shuning uchun urush sababi</t>
         </is>
       </c>
     </row>
     <row r="163">
       <c r="A163" s="1" t="inlineStr">
         <is>
-          <t>Bino narxi: Ov soʻqmogʻi</t>
+          <t>Oazis bonusi</t>
         </is>
       </c>
       <c r="B163" s="1" t="n">
-        <v>0.45</v>
+        <v>0.12</v>
       </c>
       <c r="C163" s="1" t="inlineStr">
         <is>
-          <t>x</t>
+          <t>ulush</t>
         </is>
       </c>
       <c r="D163" s="1" t="inlineStr">
         <is>
-          <t>Eng arzon — boshidan kerak boʻladi</t>
+          <t>Suv oazisi; boshqa oazislar bonusi oazis jadvalida</t>
         </is>
       </c>
     </row>
     <row r="164">
       <c r="A164" s="1" t="inlineStr">
         <is>
-          <t>Lager va oazis</t>
+          <t>Oazis ushlab turish</t>
+        </is>
+      </c>
+      <c r="B164" s="1" t="n">
+        <v>24</v>
+      </c>
+      <c r="C164" s="1" t="inlineStr">
+        <is>
+          <t>soat</t>
+        </is>
+      </c>
+      <c r="D164" s="1" t="inlineStr">
+        <is>
+          <t>Egallangandan keyin hujum qilib boʻlmaydi</t>
         </is>
       </c>
     </row>
     <row r="165">
       <c r="A165" s="1" t="inlineStr">
         <is>
-          <t>Lager yigʻim koeffitsienti</t>
-        </is>
-      </c>
-      <c r="B165" s="1" t="n">
-        <v>0.1</v>
-      </c>
-      <c r="C165" s="1" t="inlineStr">
-        <is>
-          <t>x</t>
-        </is>
-      </c>
-      <c r="D165" s="1" t="inlineStr">
-        <is>
-          <t>Bir boʻri = Ustaxona soatlik ishlab chiqarishining shuncha qismi</t>
+          <t>Bino askar sigʻimi</t>
         </is>
       </c>
     </row>
     <row r="166">
       <c r="A166" s="1" t="inlineStr">
         <is>
-          <t>Lager tier bonusi</t>
+          <t>Bazaviy askar sigʻimi</t>
         </is>
       </c>
       <c r="B166" s="1" t="n">
-        <v>0.05</v>
+        <v>6</v>
       </c>
       <c r="C166" s="1" t="inlineStr">
         <is>
-          <t>ulush/tier</t>
+          <t>ta</t>
         </is>
       </c>
       <c r="D166" s="1" t="inlineStr">
         <is>
-          <t>Yuqori tier tezroq yigʻadi</t>
+          <t>Bino 1-darajada nechta askar sigʻadi</t>
         </is>
       </c>
     </row>
     <row r="167">
       <c r="A167" s="1" t="inlineStr">
         <is>
-          <t>Lager muddati</t>
+          <t>Sigʻim oʻsish koeffitsienti</t>
         </is>
       </c>
       <c r="B167" s="1" t="n">
-        <v>8</v>
+        <v>1.2</v>
       </c>
       <c r="C167" s="1" t="inlineStr">
         <is>
-          <t>soat</t>
+          <t>x</t>
         </is>
       </c>
       <c r="D167" s="1" t="inlineStr">
         <is>
-          <t>Shundan keyin toʻda inga qaytadi</t>
+          <t>Har bino darajasida koʻpaytiriladi</t>
         </is>
       </c>
     </row>
     <row r="168">
       <c r="A168" s="1" t="inlineStr">
         <is>
-          <t>Lagerga yuborish ulushi</t>
+          <t>Ortiqcha jazo darajasi</t>
         </is>
       </c>
       <c r="B168" s="1" t="n">
-        <v>0.5</v>
+        <v>2</v>
       </c>
       <c r="C168" s="1" t="inlineStr">
         <is>
-          <t>ulush</t>
+          <t>daraja</t>
         </is>
       </c>
       <c r="D168" s="1" t="inlineStr">
         <is>
-          <t>Toʻdaning eng koʻpi shuncha qismi</t>
+          <t>Vaqt koeffitsienti = toʻlganlik ^ shu</t>
         </is>
       </c>
     </row>
     <row r="169">
       <c r="A169" s="1" t="inlineStr">
         <is>
-          <t>Oazis soni (server)</t>
+          <t>Maksimal jazo</t>
         </is>
       </c>
       <c r="B169" s="1" t="n">
-        <v>20</v>
+        <v>5</v>
       </c>
       <c r="C169" s="1" t="inlineStr">
         <is>
-          <t>ta</t>
+          <t>x</t>
         </is>
       </c>
       <c r="D169" s="1" t="inlineStr">
         <is>
-          <t>Cheklangan — shuning uchun urush sababi</t>
+          <t>Mashq vaqti shundan koʻp choʻzilmaydi</t>
         </is>
       </c>
     </row>
     <row r="170">
       <c r="A170" s="1" t="inlineStr">
         <is>
-          <t>Oazis bonusi</t>
-        </is>
-      </c>
-      <c r="B170" s="1" t="n">
-        <v>0.12</v>
-      </c>
-      <c r="C170" s="1" t="inlineStr">
-        <is>
-          <t>ulush</t>
-        </is>
-      </c>
-      <c r="D170" s="1" t="inlineStr">
-        <is>
-          <t>Egasiga doimiy ishlab chiqarish bonusi</t>
+          <t>Qurilish vaqti koeffitsientlari</t>
         </is>
       </c>
     </row>
     <row r="171">
       <c r="A171" s="1" t="inlineStr">
         <is>
-          <t>Oazis ushlab turish</t>
+          <t>Vaqt: Oziq gʻori</t>
         </is>
       </c>
       <c r="B171" s="1" t="n">
-        <v>24</v>
+        <v>1</v>
       </c>
       <c r="C171" s="1" t="inlineStr">
         <is>
-          <t>soat</t>
+          <t>x</t>
         </is>
       </c>
       <c r="D171" s="1" t="inlineStr">
         <is>
-          <t>Egallangandan keyin hujum qilib boʻlmaydi</t>
+          <t>Bazaviy qurilish vaqtiga nisbatan</t>
         </is>
       </c>
     </row>
     <row r="172">
       <c r="A172" s="1" t="inlineStr">
         <is>
-          <t>Bino askar sigʻimi</t>
+          <t>Vaqt: Ustaxona qoyasi</t>
+        </is>
+      </c>
+      <c r="B172" s="1" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="C172" s="1" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
+      <c r="D172" s="1" t="inlineStr">
+        <is>
+          <t>Asosiy iqtisod binosi — sekinroq</t>
         </is>
       </c>
     </row>
     <row r="173">
       <c r="A173" s="1" t="inlineStr">
         <is>
-          <t>Bazaviy askar sigʻimi</t>
+          <t>Vaqt: Razvedka qoyasi</t>
         </is>
       </c>
       <c r="B173" s="1" t="n">
-        <v>6</v>
+        <v>0.8</v>
       </c>
       <c r="C173" s="1" t="inlineStr">
         <is>
-          <t>ta</t>
+          <t>x</t>
         </is>
       </c>
       <c r="D173" s="1" t="inlineStr">
         <is>
-          <t>Bino 1-darajada nechta askar sigʻadi</t>
+          <t>Yengil qurilish</t>
         </is>
       </c>
     </row>
     <row r="174">
       <c r="A174" s="1" t="inlineStr">
         <is>
-          <t>Sigʻim oʻsish koeffitsienti</t>
+          <t>Vaqt: Jang maydoni</t>
         </is>
       </c>
       <c r="B174" s="1" t="n">
-        <v>1.2</v>
+        <v>1.3</v>
       </c>
       <c r="C174" s="1" t="inlineStr">
         <is>
@@ -20560,38 +20545,38 @@
       </c>
       <c r="D174" s="1" t="inlineStr">
         <is>
-          <t>Har bino darajasida koʻpaytiriladi</t>
+          <t>Eng sekin — asosiy PvP binosi</t>
         </is>
       </c>
     </row>
     <row r="175">
       <c r="A175" s="1" t="inlineStr">
         <is>
-          <t>Ortiqcha jazo darajasi</t>
+          <t>Vaqt: Himoya devori</t>
         </is>
       </c>
       <c r="B175" s="1" t="n">
-        <v>2</v>
+        <v>1.1</v>
       </c>
       <c r="C175" s="1" t="inlineStr">
         <is>
-          <t>daraja</t>
+          <t>x</t>
         </is>
       </c>
       <c r="D175" s="1" t="inlineStr">
         <is>
-          <t>Vaqt koeffitsienti = toʻlganlik ^ shu</t>
+          <t>Ogʻir qurilish</t>
         </is>
       </c>
     </row>
     <row r="176">
       <c r="A176" s="1" t="inlineStr">
         <is>
-          <t>Maksimal jazo</t>
+          <t>Vaqt: Ov soʻqmogʻi</t>
         </is>
       </c>
       <c r="B176" s="1" t="n">
-        <v>5</v>
+        <v>0.7</v>
       </c>
       <c r="C176" s="1" t="inlineStr">
         <is>
@@ -20600,21 +20585,34 @@
       </c>
       <c r="D176" s="1" t="inlineStr">
         <is>
-          <t>Mashq vaqti shundan koʻp choʻzilmaydi</t>
+          <t>Eng tez — boshidan kerak</t>
         </is>
       </c>
     </row>
     <row r="177">
       <c r="A177" s="1" t="inlineStr">
         <is>
-          <t>Qurilish vaqti koeffitsientlari</t>
+          <t>Vaqt: Shifo gʻori</t>
+        </is>
+      </c>
+      <c r="B177" s="1" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="C177" s="1" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
+      <c r="D177" s="1" t="inlineStr">
+        <is>
+          <t>Bazaviy qurilish vaqtiga nisbatan</t>
         </is>
       </c>
     </row>
     <row r="178">
       <c r="A178" s="1" t="inlineStr">
         <is>
-          <t>Vaqt: Oziq gʻori</t>
+          <t>Vaqt: Bozor</t>
         </is>
       </c>
       <c r="B178" s="1" t="n">
@@ -20634,385 +20632,372 @@
     <row r="179">
       <c r="A179" s="1" t="inlineStr">
         <is>
-          <t>Vaqt: Ustaxona qoyasi</t>
-        </is>
-      </c>
-      <c r="B179" s="1" t="n">
-        <v>1.2</v>
-      </c>
-      <c r="C179" s="1" t="inlineStr">
-        <is>
-          <t>x</t>
-        </is>
-      </c>
-      <c r="D179" s="1" t="inlineStr">
-        <is>
-          <t>Asosiy iqtisod binosi — sekinroq</t>
+          <t>Shifo gʻori</t>
         </is>
       </c>
     </row>
     <row r="180">
       <c r="A180" s="1" t="inlineStr">
         <is>
-          <t>Vaqt: Razvedka qoyasi</t>
+          <t>Shifo bazaviy sigʻimi</t>
         </is>
       </c>
       <c r="B180" s="1" t="n">
-        <v>0.8</v>
+        <v>2</v>
       </c>
       <c r="C180" s="1" t="inlineStr">
         <is>
-          <t>x</t>
+          <t>boʻri</t>
         </is>
       </c>
       <c r="D180" s="1" t="inlineStr">
         <is>
-          <t>Yengil qurilish</t>
+          <t>Bir vaqtda nechta jarohatlangan boʻri davolanadi</t>
         </is>
       </c>
     </row>
     <row r="181">
       <c r="A181" s="1" t="inlineStr">
         <is>
-          <t>Vaqt: Jang maydoni</t>
+          <t>Shifo sigʻim oʻsishi</t>
         </is>
       </c>
       <c r="B181" s="1" t="n">
-        <v>1.3</v>
+        <v>0.4</v>
       </c>
       <c r="C181" s="1" t="inlineStr">
         <is>
-          <t>x</t>
+          <t>boʻri/daraja</t>
         </is>
       </c>
       <c r="D181" s="1" t="inlineStr">
         <is>
-          <t>Eng sekin — asosiy PvP binosi</t>
+          <t>Har darajada</t>
         </is>
       </c>
     </row>
     <row r="182">
       <c r="A182" s="1" t="inlineStr">
         <is>
-          <t>Vaqt: Himoya devori</t>
+          <t>Bazaviy davolash vaqti</t>
         </is>
       </c>
       <c r="B182" s="1" t="n">
-        <v>1.1</v>
+        <v>60</v>
       </c>
       <c r="C182" s="1" t="inlineStr">
         <is>
-          <t>x</t>
+          <t>daqiqa</t>
         </is>
       </c>
       <c r="D182" s="1" t="inlineStr">
         <is>
-          <t>Ogʻir qurilish</t>
+          <t>Bitta boʻri, 1-darajada</t>
         </is>
       </c>
     </row>
     <row r="183">
       <c r="A183" s="1" t="inlineStr">
         <is>
-          <t>Vaqt: Ov soʻqmogʻi</t>
+          <t>Davolash tezligi oʻsishi</t>
         </is>
       </c>
       <c r="B183" s="1" t="n">
-        <v>0.7</v>
+        <v>0.05</v>
       </c>
       <c r="C183" s="1" t="inlineStr">
         <is>
-          <t>x</t>
+          <t>ulush/daraja</t>
         </is>
       </c>
       <c r="D183" s="1" t="inlineStr">
         <is>
-          <t>Eng tez — boshidan kerak</t>
+          <t>Vaqtni qisqartiradi</t>
         </is>
       </c>
     </row>
     <row r="184">
       <c r="A184" s="1" t="inlineStr">
         <is>
-          <t>Vaqt: Shifo gʻori</t>
+          <t>Shifo narxi: shox-shabba</t>
         </is>
       </c>
       <c r="B184" s="1" t="n">
-        <v>0.9</v>
+        <v>120</v>
       </c>
       <c r="C184" s="1" t="inlineStr">
         <is>
-          <t>x</t>
+          <t>birlik</t>
         </is>
       </c>
       <c r="D184" s="1" t="inlineStr">
         <is>
-          <t>Bazaviy qurilish vaqtiga nisbatan</t>
+          <t>1→2 daraja</t>
         </is>
       </c>
     </row>
     <row r="185">
       <c r="A185" s="1" t="inlineStr">
         <is>
-          <t>Vaqt: Bozor</t>
+          <t>Shifo narxi: teri</t>
         </is>
       </c>
       <c r="B185" s="1" t="n">
-        <v>1</v>
+        <v>100</v>
       </c>
       <c r="C185" s="1" t="inlineStr">
         <is>
-          <t>x</t>
+          <t>birlik</t>
         </is>
       </c>
       <c r="D185" s="1" t="inlineStr">
         <is>
-          <t>Bazaviy qurilish vaqtiga nisbatan</t>
+          <t>1→2 daraja</t>
         </is>
       </c>
     </row>
     <row r="186">
       <c r="A186" s="1" t="inlineStr">
         <is>
-          <t>Shifo gʻori</t>
+          <t>Shifo narxi: tosh</t>
+        </is>
+      </c>
+      <c r="B186" s="1" t="n">
+        <v>80</v>
+      </c>
+      <c r="C186" s="1" t="inlineStr">
+        <is>
+          <t>birlik</t>
+        </is>
+      </c>
+      <c r="D186" s="1" t="inlineStr">
+        <is>
+          <t>1→2 daraja</t>
         </is>
       </c>
     </row>
     <row r="187">
       <c r="A187" s="1" t="inlineStr">
         <is>
-          <t>Shifo bazaviy sigʻimi</t>
-        </is>
-      </c>
-      <c r="B187" s="1" t="n">
-        <v>2</v>
-      </c>
-      <c r="C187" s="1" t="inlineStr">
-        <is>
-          <t>boʻri</t>
-        </is>
-      </c>
-      <c r="D187" s="1" t="inlineStr">
-        <is>
-          <t>Bir vaqtda nechta jarohatlangan boʻri davolanadi</t>
+          <t>Bozor</t>
         </is>
       </c>
     </row>
     <row r="188">
       <c r="A188" s="1" t="inlineStr">
         <is>
-          <t>Shifo sigʻim oʻsishi</t>
+          <t>Bazaviy almashinuv kursi</t>
         </is>
       </c>
       <c r="B188" s="1" t="n">
-        <v>0.4</v>
+        <v>3</v>
       </c>
       <c r="C188" s="1" t="inlineStr">
         <is>
-          <t>boʻri/daraja</t>
+          <t>x</t>
         </is>
       </c>
       <c r="D188" s="1" t="inlineStr">
         <is>
-          <t>Har darajada</t>
+          <t>1-darajada 3 birlik berib 1 olasiz</t>
         </is>
       </c>
     </row>
     <row r="189">
       <c r="A189" s="1" t="inlineStr">
         <is>
-          <t>Bazaviy davolash vaqti</t>
+          <t>Kurs yaxshilanishi</t>
         </is>
       </c>
       <c r="B189" s="1" t="n">
-        <v>60</v>
+        <v>0.075</v>
       </c>
       <c r="C189" s="1" t="inlineStr">
         <is>
-          <t>daqiqa</t>
+          <t>x/daraja</t>
         </is>
       </c>
       <c r="D189" s="1" t="inlineStr">
         <is>
-          <t>Bitta boʻri, 1-darajada</t>
+          <t>Har darajada kurs yaxshilanadi</t>
         </is>
       </c>
     </row>
     <row r="190">
       <c r="A190" s="1" t="inlineStr">
         <is>
-          <t>Davolash tezligi oʻsishi</t>
+          <t>Bazaviy kunlik limit</t>
         </is>
       </c>
       <c r="B190" s="1" t="n">
-        <v>0.05</v>
+        <v>200</v>
       </c>
       <c r="C190" s="1" t="inlineStr">
         <is>
-          <t>ulush/daraja</t>
+          <t>birlik</t>
         </is>
       </c>
       <c r="D190" s="1" t="inlineStr">
         <is>
-          <t>Vaqtni qisqartiradi</t>
+          <t>Kuniga almashtirish mumkin boʻlgan miqdor</t>
         </is>
       </c>
     </row>
     <row r="191">
       <c r="A191" s="1" t="inlineStr">
         <is>
-          <t>Shifo narxi: shox-shabba</t>
+          <t>Limit oʻsishi</t>
         </is>
       </c>
       <c r="B191" s="1" t="n">
-        <v>120</v>
+        <v>1.2</v>
       </c>
       <c r="C191" s="1" t="inlineStr">
         <is>
-          <t>birlik</t>
+          <t>x</t>
         </is>
       </c>
       <c r="D191" s="1" t="inlineStr">
         <is>
-          <t>1→2 daraja</t>
+          <t>Har darajada</t>
         </is>
       </c>
     </row>
     <row r="192">
       <c r="A192" s="1" t="inlineStr">
         <is>
-          <t>Shifo narxi: goʻsht</t>
+          <t>Bazaviy soliq</t>
         </is>
       </c>
       <c r="B192" s="1" t="n">
-        <v>100</v>
+        <v>0.2</v>
       </c>
       <c r="C192" s="1" t="inlineStr">
         <is>
-          <t>kg</t>
+          <t>ulush</t>
         </is>
       </c>
       <c r="D192" s="1" t="inlineStr">
         <is>
-          <t>1→2 daraja</t>
+          <t>Almashinuvdan ushlanadi</t>
         </is>
       </c>
     </row>
     <row r="193">
       <c r="A193" s="1" t="inlineStr">
         <is>
-          <t>Shifo narxi: tosh</t>
+          <t>Soliq kamayishi</t>
         </is>
       </c>
       <c r="B193" s="1" t="n">
-        <v>80</v>
+        <v>0.006</v>
       </c>
       <c r="C193" s="1" t="inlineStr">
         <is>
-          <t>birlik</t>
+          <t>ulush/daraja</t>
         </is>
       </c>
       <c r="D193" s="1" t="inlineStr">
         <is>
-          <t>1→2 daraja</t>
+          <t>Har darajada</t>
         </is>
       </c>
     </row>
     <row r="194">
       <c r="A194" s="1" t="inlineStr">
         <is>
-          <t>Bozor</t>
+          <t>Bozor narxi: tosh</t>
+        </is>
+      </c>
+      <c r="B194" s="1" t="n">
+        <v>130</v>
+      </c>
+      <c r="C194" s="1" t="inlineStr">
+        <is>
+          <t>birlik</t>
+        </is>
+      </c>
+      <c r="D194" s="1" t="inlineStr">
+        <is>
+          <t>1→2 daraja</t>
         </is>
       </c>
     </row>
     <row r="195">
       <c r="A195" s="1" t="inlineStr">
         <is>
-          <t>Bazaviy almashinuv kursi</t>
+          <t>Bozor narxi: shox-shabba</t>
         </is>
       </c>
       <c r="B195" s="1" t="n">
-        <v>3</v>
+        <v>110</v>
       </c>
       <c r="C195" s="1" t="inlineStr">
         <is>
-          <t>x</t>
+          <t>birlik</t>
         </is>
       </c>
       <c r="D195" s="1" t="inlineStr">
         <is>
-          <t>1-darajada 3 birlik berib 1 olasiz</t>
+          <t>1→2 daraja</t>
         </is>
       </c>
     </row>
     <row r="196">
       <c r="A196" s="1" t="inlineStr">
         <is>
-          <t>Kurs yaxshilanishi</t>
-        </is>
-      </c>
-      <c r="B196" s="1" t="n">
-        <v>0.075</v>
-      </c>
-      <c r="C196" s="1" t="inlineStr">
-        <is>
-          <t>x/daraja</t>
-        </is>
-      </c>
-      <c r="D196" s="1" t="inlineStr">
-        <is>
-          <t>Har darajada kurs yaxshilanadi</t>
+          <t>Mukofot va mavsum</t>
         </is>
       </c>
     </row>
     <row r="197">
       <c r="A197" s="1" t="inlineStr">
         <is>
-          <t>Bazaviy kunlik limit</t>
+          <t>Faol oʻyinchi soni</t>
         </is>
       </c>
       <c r="B197" s="1" t="n">
-        <v>200</v>
+        <v>10000</v>
       </c>
       <c r="C197" s="1" t="inlineStr">
         <is>
-          <t>birlik</t>
+          <t>ta</t>
         </is>
       </c>
       <c r="D197" s="1" t="inlineStr">
         <is>
-          <t>Kuniga almashtirish mumkin boʻlgan miqdor</t>
+          <t>Kunlik faol oʻyinchi (DAU)</t>
         </is>
       </c>
     </row>
     <row r="198">
       <c r="A198" s="1" t="inlineStr">
         <is>
-          <t>Limit oʻsishi</t>
+          <t>Kunlik ARPU</t>
         </is>
       </c>
       <c r="B198" s="1" t="n">
-        <v>1.2</v>
+        <v>0.05</v>
       </c>
       <c r="C198" s="1" t="inlineStr">
         <is>
-          <t>x</t>
+          <t>$</t>
         </is>
       </c>
       <c r="D198" s="1" t="inlineStr">
         <is>
-          <t>Har darajada</t>
+          <t>Bitta oʻyinchidan kunlik daromad</t>
         </is>
       </c>
     </row>
     <row r="199">
       <c r="A199" s="1" t="inlineStr">
         <is>
-          <t>Bazaviy soliq</t>
+          <t>Jamgʻarma ulushi</t>
         </is>
       </c>
       <c r="B199" s="1" t="n">
-        <v>0.2</v>
+        <v>0.15</v>
       </c>
       <c r="C199" s="1" t="inlineStr">
         <is>
@@ -21021,165 +21006,165 @@
       </c>
       <c r="D199" s="1" t="inlineStr">
         <is>
-          <t>Almashinuvdan ushlanadi</t>
+          <t>Daromadning shuncha qismi sovrin fondiga</t>
         </is>
       </c>
     </row>
     <row r="200">
       <c r="A200" s="1" t="inlineStr">
         <is>
-          <t>Soliq kamayishi</t>
+          <t>Mavsum davomiyligi</t>
         </is>
       </c>
       <c r="B200" s="1" t="n">
-        <v>0.006</v>
+        <v>7</v>
       </c>
       <c r="C200" s="1" t="inlineStr">
         <is>
-          <t>ulush/daraja</t>
+          <t>kun</t>
         </is>
       </c>
       <c r="D200" s="1" t="inlineStr">
         <is>
-          <t>Har darajada</t>
+          <t>Reyting shundan keyin nolga tushadi</t>
         </is>
       </c>
     </row>
     <row r="201">
       <c r="A201" s="1" t="inlineStr">
         <is>
-          <t>Bozor narxi: tosh</t>
+          <t>Maksimal shaxsiy ulush</t>
         </is>
       </c>
       <c r="B201" s="1" t="n">
-        <v>130</v>
+        <v>0.05</v>
       </c>
       <c r="C201" s="1" t="inlineStr">
         <is>
-          <t>birlik</t>
+          <t>ulush</t>
         </is>
       </c>
       <c r="D201" s="1" t="inlineStr">
         <is>
-          <t>1→2 daraja</t>
+          <t>Bitta oʻyinchi fondning shuncha qismidan koʻp ololmaydi</t>
         </is>
       </c>
     </row>
     <row r="202">
       <c r="A202" s="1" t="inlineStr">
         <is>
-          <t>Bozor narxi: shox-shabba</t>
+          <t>Minimal haftalik janglar</t>
         </is>
       </c>
       <c r="B202" s="1" t="n">
-        <v>110</v>
+        <v>5</v>
       </c>
       <c r="C202" s="1" t="inlineStr">
         <is>
-          <t>birlik</t>
+          <t>ta</t>
         </is>
       </c>
       <c r="D202" s="1" t="inlineStr">
         <is>
-          <t>1→2 daraja</t>
+          <t>Shundan kam jang qilgan mukofot olmaydi</t>
         </is>
       </c>
     </row>
     <row r="203">
       <c r="A203" s="1" t="inlineStr">
         <is>
-          <t>Mukofot va mavsum</t>
+          <t>Yakuniy kunlar bonusi</t>
+        </is>
+      </c>
+      <c r="B203" s="1" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="C203" s="1" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
+      <c r="D203" s="1" t="inlineStr">
+        <is>
+          <t>Mavsumning oxirgi 3 kunida hissa</t>
         </is>
       </c>
     </row>
     <row r="204">
       <c r="A204" s="1" t="inlineStr">
         <is>
-          <t>Faol oʻyinchi soni</t>
+          <t>Tanga kursi</t>
         </is>
       </c>
       <c r="B204" s="1" t="n">
-        <v>10000</v>
+        <v>1000</v>
       </c>
       <c r="C204" s="1" t="inlineStr">
         <is>
-          <t>ta</t>
+          <t>tanga/$</t>
         </is>
       </c>
       <c r="D204" s="1" t="inlineStr">
         <is>
-          <t>Kunlik faol oʻyinchi (DAU)</t>
+          <t>Oʻyin ichidagi tanga qiymati</t>
         </is>
       </c>
     </row>
     <row r="205">
       <c r="A205" s="1" t="inlineStr">
         <is>
-          <t>Kunlik ARPU</t>
+          <t>Yangi akkaunt kutishi</t>
         </is>
       </c>
       <c r="B205" s="1" t="n">
-        <v>0.05</v>
+        <v>14</v>
       </c>
       <c r="C205" s="1" t="inlineStr">
         <is>
-          <t>$</t>
+          <t>kun</t>
         </is>
       </c>
       <c r="D205" s="1" t="inlineStr">
         <is>
-          <t>Bitta oʻyinchidan kunlik daromad</t>
+          <t>Shundan keyin mukofotga kira oladi</t>
         </is>
       </c>
     </row>
     <row r="206">
       <c r="A206" s="1" t="inlineStr">
         <is>
-          <t>Jamgʻarma ulushi</t>
-        </is>
-      </c>
-      <c r="B206" s="1" t="n">
-        <v>0.15</v>
-      </c>
-      <c r="C206" s="1" t="inlineStr">
-        <is>
-          <t>ulush</t>
-        </is>
-      </c>
-      <c r="D206" s="1" t="inlineStr">
-        <is>
-          <t>Daromadning shuncha qismi sovrin fondiga</t>
+          <t>Adolat nazorati</t>
         </is>
       </c>
     </row>
     <row r="207">
       <c r="A207" s="1" t="inlineStr">
         <is>
-          <t>Mavsum davomiyligi</t>
+          <t>Juftlik hissa chegarasi</t>
         </is>
       </c>
       <c r="B207" s="1" t="n">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="C207" s="1" t="inlineStr">
         <is>
-          <t>kun</t>
+          <t>jang</t>
         </is>
       </c>
       <c r="D207" s="1" t="inlineStr">
         <is>
-          <t>Reyting shundan keyin nolga tushadi</t>
+          <t>Bir juftlikning mavsumda hisobga olinadigan janglari</t>
         </is>
       </c>
     </row>
     <row r="208">
       <c r="A208" s="1" t="inlineStr">
         <is>
-          <t>Maksimal shaxsiy ulush</t>
+          <t>Yopiq guruh chegarasi</t>
         </is>
       </c>
       <c r="B208" s="1" t="n">
-        <v>0.05</v>
+        <v>0.6</v>
       </c>
       <c r="C208" s="1" t="inlineStr">
         <is>
@@ -21188,14 +21173,14 @@
       </c>
       <c r="D208" s="1" t="inlineStr">
         <is>
-          <t>Bitta oʻyinchi fondning shuncha qismidan koʻp ololmaydi</t>
+          <t>Janglarning shuncha qismi bir guruh ichida boʻlsa — bayroq</t>
         </is>
       </c>
     </row>
     <row r="209">
       <c r="A209" s="1" t="inlineStr">
         <is>
-          <t>Minimal haftalik janglar</t>
+          <t>Yopiq guruh hajmi</t>
         </is>
       </c>
       <c r="B209" s="1" t="n">
@@ -21203,130 +21188,143 @@
       </c>
       <c r="C209" s="1" t="inlineStr">
         <is>
-          <t>ta</t>
+          <t>oʻyinchi</t>
         </is>
       </c>
       <c r="D209" s="1" t="inlineStr">
         <is>
-          <t>Shundan kam jang qilgan mukofot olmaydi</t>
+          <t>Shuncha kishilik guruh tekshiriladi</t>
         </is>
       </c>
     </row>
     <row r="210">
       <c r="A210" s="1" t="inlineStr">
         <is>
-          <t>Yakuniy kunlar bonusi</t>
+          <t>Minimal himoya CP</t>
         </is>
       </c>
       <c r="B210" s="1" t="n">
-        <v>1.5</v>
+        <v>0.6</v>
       </c>
       <c r="C210" s="1" t="inlineStr">
         <is>
-          <t>x</t>
+          <t>ulush</t>
         </is>
       </c>
       <c r="D210" s="1" t="inlineStr">
         <is>
-          <t>Mavsumning oxirgi 3 kunida hissa</t>
+          <t>Himoyachi inida shuncha kuch turishi shart</t>
         </is>
       </c>
     </row>
     <row r="211">
       <c r="A211" s="1" t="inlineStr">
         <is>
-          <t>Tanga kursi</t>
+          <t>Minimal raund</t>
         </is>
       </c>
       <c r="B211" s="1" t="n">
-        <v>1000</v>
+        <v>3</v>
       </c>
       <c r="C211" s="1" t="inlineStr">
         <is>
-          <t>tanga/$</t>
+          <t>raund</t>
         </is>
       </c>
       <c r="D211" s="1" t="inlineStr">
         <is>
-          <t>Oʻyin ichidagi tanga qiymati</t>
+          <t>Jang shundan qisqa boʻlsa — hissa 0</t>
         </is>
       </c>
     </row>
     <row r="212">
       <c r="A212" s="1" t="inlineStr">
         <is>
-          <t>Yangi akkaunt kutishi</t>
+          <t>Minimal hujumchi yoʻqotishi</t>
         </is>
       </c>
       <c r="B212" s="1" t="n">
-        <v>14</v>
+        <v>0.15</v>
       </c>
       <c r="C212" s="1" t="inlineStr">
         <is>
-          <t>kun</t>
+          <t>ulush</t>
         </is>
       </c>
       <c r="D212" s="1" t="inlineStr">
         <is>
-          <t>Shundan keyin mukofotga kira oladi</t>
+          <t>Hujumchi shuncha askar yoʻqotishi kerak</t>
         </is>
       </c>
     </row>
     <row r="213">
       <c r="A213" s="1" t="inlineStr">
         <is>
-          <t>Adolat nazorati</t>
+          <t>Bir tomonlama nisbat</t>
+        </is>
+      </c>
+      <c r="B213" s="1" t="n">
+        <v>10</v>
+      </c>
+      <c r="C213" s="1" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
+      <c r="D213" s="1" t="inlineStr">
+        <is>
+          <t>Zarar nisbati shundan yuqori boʻlsa koeff. tushadi</t>
         </is>
       </c>
     </row>
     <row r="214">
       <c r="A214" s="1" t="inlineStr">
         <is>
-          <t>Juftlik chegarasi</t>
+          <t>Toʻda almashtirish bloki</t>
         </is>
       </c>
       <c r="B214" s="1" t="n">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="C214" s="1" t="inlineStr">
         <is>
-          <t>jang</t>
+          <t>kun</t>
         </is>
       </c>
       <c r="D214" s="1" t="inlineStr">
         <is>
-          <t>Bir raqib bilan mavsumda hisobga olinadigan janglar</t>
+          <t>Toʻda almashtirgan shu muddat mukofotsiz</t>
         </is>
       </c>
     </row>
     <row r="215">
       <c r="A215" s="1" t="inlineStr">
         <is>
-          <t>Yopiq guruh chegarasi</t>
+          <t>Toʻlov kutish vaqti</t>
         </is>
       </c>
       <c r="B215" s="1" t="n">
-        <v>0.6</v>
+        <v>48</v>
       </c>
       <c r="C215" s="1" t="inlineStr">
         <is>
-          <t>ulush</t>
+          <t>soat</t>
         </is>
       </c>
       <c r="D215" s="1" t="inlineStr">
         <is>
-          <t>Janglarning shuncha qismi bir guruh ichida boʻlsa — bayroq</t>
+          <t>Mavsum tugagach tekshiruv muddati</t>
         </is>
       </c>
     </row>
     <row r="216">
       <c r="A216" s="1" t="inlineStr">
         <is>
-          <t>Yopiq guruh hajmi</t>
+          <t>Qoʻlda tekshiruv</t>
         </is>
       </c>
       <c r="B216" s="1" t="n">
-        <v>5</v>
+        <v>100</v>
       </c>
       <c r="C216" s="1" t="inlineStr">
         <is>
@@ -21335,241 +21333,228 @@
       </c>
       <c r="D216" s="1" t="inlineStr">
         <is>
-          <t>Shuncha kishilik guruh tekshiriladi</t>
+          <t>Top shuncha profil qoʻlda koʻriladi</t>
         </is>
       </c>
     </row>
     <row r="217">
       <c r="A217" s="1" t="inlineStr">
         <is>
-          <t>Minimal himoya CP</t>
-        </is>
-      </c>
-      <c r="B217" s="1" t="n">
-        <v>0.6</v>
-      </c>
-      <c r="C217" s="1" t="inlineStr">
-        <is>
-          <t>ulush</t>
-        </is>
-      </c>
-      <c r="D217" s="1" t="inlineStr">
-        <is>
-          <t>Himoyachi inida shuncha kuch turishi shart</t>
+          <t>PvP oʻlja</t>
         </is>
       </c>
     </row>
     <row r="218">
       <c r="A218" s="1" t="inlineStr">
         <is>
-          <t>Minimal raund</t>
+          <t>Bazaviy yuk</t>
         </is>
       </c>
       <c r="B218" s="1" t="n">
-        <v>3</v>
+        <v>15</v>
       </c>
       <c r="C218" s="1" t="inlineStr">
         <is>
-          <t>raund</t>
+          <t>kg/hujumchi</t>
         </is>
       </c>
       <c r="D218" s="1" t="inlineStr">
         <is>
-          <t>Jang shundan qisqa boʻlsa — hissa 0</t>
+          <t>Bitta hujumchi olib keta oladigan miqdor</t>
         </is>
       </c>
     </row>
     <row r="219">
       <c r="A219" s="1" t="inlineStr">
         <is>
-          <t>Minimal hujumchi yoʻqotishi</t>
+          <t>Tier yuk bonusi</t>
         </is>
       </c>
       <c r="B219" s="1" t="n">
-        <v>0.15</v>
+        <v>0.2</v>
       </c>
       <c r="C219" s="1" t="inlineStr">
         <is>
-          <t>ulush</t>
+          <t>ulush/tier</t>
         </is>
       </c>
       <c r="D219" s="1" t="inlineStr">
         <is>
-          <t>Hujumchi shuncha askar yoʻqotishi kerak</t>
+          <t>Yuqori tier koʻproq olib ketadi</t>
         </is>
       </c>
     </row>
     <row r="220">
       <c r="A220" s="1" t="inlineStr">
         <is>
-          <t>Bir tomonlama nisbat</t>
+          <t>Oʻlja chegarasi</t>
         </is>
       </c>
       <c r="B220" s="1" t="n">
-        <v>10</v>
+        <v>0.5</v>
       </c>
       <c r="C220" s="1" t="inlineStr">
         <is>
-          <t>x</t>
+          <t>ulush</t>
         </is>
       </c>
       <c r="D220" s="1" t="inlineStr">
         <is>
-          <t>Zarar nisbati shundan yuqori boʻlsa koeff. tushadi</t>
+          <t>Reyd daromadi kunlik ovdan shuncha oshmasin</t>
         </is>
       </c>
     </row>
     <row r="221">
       <c r="A221" s="1" t="inlineStr">
         <is>
-          <t>Toʻda almashtirish bloki</t>
+          <t>Reyd koeffitsienti</t>
         </is>
       </c>
       <c r="B221" s="1" t="n">
-        <v>7</v>
+        <v>0.22</v>
       </c>
       <c r="C221" s="1" t="inlineStr">
         <is>
-          <t>kun</t>
+          <t>ulush</t>
         </is>
       </c>
       <c r="D221" s="1" t="inlineStr">
         <is>
-          <t>Toʻda almashtirgan shu muddat mukofotsiz</t>
+          <t>Himoyalanmagan zaxiradan olinadigan ulush</t>
         </is>
       </c>
     </row>
     <row r="222">
       <c r="A222" s="1" t="inlineStr">
         <is>
-          <t>Toʻlov kutish vaqti</t>
+          <t>Hujum oynasi: past</t>
         </is>
       </c>
       <c r="B222" s="1" t="n">
-        <v>48</v>
+        <v>1</v>
       </c>
       <c r="C222" s="1" t="inlineStr">
         <is>
-          <t>soat</t>
+          <t>daraja</t>
         </is>
       </c>
       <c r="D222" s="1" t="inlineStr">
         <is>
-          <t>Mavsum tugagach tekshiruv muddati</t>
+          <t>Shuncha past darajaga hujum qilish mumkin</t>
         </is>
       </c>
     </row>
     <row r="223">
       <c r="A223" s="1" t="inlineStr">
         <is>
-          <t>Qoʻlda tekshiruv</t>
+          <t>Hujum oynasi: yuqori</t>
         </is>
       </c>
       <c r="B223" s="1" t="n">
-        <v>100</v>
+        <v>1</v>
       </c>
       <c r="C223" s="1" t="inlineStr">
         <is>
-          <t>oʻyinchi</t>
+          <t>daraja</t>
         </is>
       </c>
       <c r="D223" s="1" t="inlineStr">
         <is>
-          <t>Top shuncha profil qoʻlda koʻriladi</t>
+          <t>Shuncha yuqori darajaga hujum qilish mumkin</t>
         </is>
       </c>
     </row>
     <row r="224">
       <c r="A224" s="1" t="inlineStr">
         <is>
-          <t>PvP oʻlja</t>
+          <t>Qalqon darajasi</t>
+        </is>
+      </c>
+      <c r="B224" s="1" t="n">
+        <v>6</v>
+      </c>
+      <c r="C224" s="1" t="inlineStr">
+        <is>
+          <t>daraja</t>
+        </is>
+      </c>
+      <c r="D224" s="1" t="inlineStr">
+        <is>
+          <t>Shu darajagacha umuman hujum qilib boʻlmaydi</t>
         </is>
       </c>
     </row>
     <row r="225">
       <c r="A225" s="1" t="inlineStr">
         <is>
-          <t>Bazaviy yuk</t>
+          <t>Kengayish kutish vaqti</t>
         </is>
       </c>
       <c r="B225" s="1" t="n">
-        <v>15</v>
+        <v>30</v>
       </c>
       <c r="C225" s="1" t="inlineStr">
         <is>
-          <t>kg/hujumchi</t>
+          <t>daqiqa</t>
         </is>
       </c>
       <c r="D225" s="1" t="inlineStr">
         <is>
-          <t>Bitta hujumchi olib keta oladigan miqdor</t>
+          <t>Mos raqib topilmasa, oyna shuncha vaqtdan keyin kengayadi</t>
         </is>
       </c>
     </row>
     <row r="226">
       <c r="A226" s="1" t="inlineStr">
         <is>
-          <t>Tier yuk bonusi</t>
+          <t>Maksimal oyna</t>
         </is>
       </c>
       <c r="B226" s="1" t="n">
-        <v>0.2</v>
+        <v>3</v>
       </c>
       <c r="C226" s="1" t="inlineStr">
         <is>
-          <t>ulush/tier</t>
+          <t>daraja</t>
         </is>
       </c>
       <c r="D226" s="1" t="inlineStr">
         <is>
-          <t>Yuqori tier koʻproq olib ketadi</t>
+          <t>Oyna eng koʻpi bilan shuncha kengayadi</t>
         </is>
       </c>
     </row>
     <row r="227">
       <c r="A227" s="1" t="inlineStr">
         <is>
-          <t>Oʻlja chegarasi</t>
+          <t>Minimal havza</t>
         </is>
       </c>
       <c r="B227" s="1" t="n">
-        <v>0.5</v>
+        <v>10</v>
       </c>
       <c r="C227" s="1" t="inlineStr">
         <is>
-          <t>ulush</t>
+          <t>oʻyinchi</t>
         </is>
       </c>
       <c r="D227" s="1" t="inlineStr">
         <is>
-          <t>Reyd daromadi kunlik ovdan shuncha oshmasin</t>
+          <t>Oynada shuncha faol raqib boʻlishi kerak</t>
         </is>
       </c>
     </row>
     <row r="228">
       <c r="A228" s="1" t="inlineStr">
         <is>
-          <t>Reyd koeffitsienti</t>
-        </is>
-      </c>
-      <c r="B228" s="1" t="n">
-        <v>0.22</v>
-      </c>
-      <c r="C228" s="1" t="inlineStr">
-        <is>
-          <t>ulush</t>
-        </is>
-      </c>
-      <c r="D228" s="1" t="inlineStr">
-        <is>
-          <t>Himoyalanmagan zaxiradan olinadigan ulush</t>
+          <t>Razvedka</t>
         </is>
       </c>
     </row>
     <row r="229">
       <c r="A229" s="1" t="inlineStr">
         <is>
-          <t>Hujum oynasi: past</t>
+          <t>Qisman chegara</t>
         </is>
       </c>
       <c r="B229" s="1" t="n">
@@ -21577,63 +21562,63 @@
       </c>
       <c r="C229" s="1" t="inlineStr">
         <is>
-          <t>daraja</t>
+          <t>x</t>
         </is>
       </c>
       <c r="D229" s="1" t="inlineStr">
         <is>
-          <t>Shuncha past darajaga hujum qilish mumkin</t>
+          <t>Shundan past — razvedka muvaffaqiyatsiz</t>
         </is>
       </c>
     </row>
     <row r="230">
       <c r="A230" s="1" t="inlineStr">
         <is>
-          <t>Hujum oynasi: yuqori</t>
+          <t>Toʻliq chegara</t>
         </is>
       </c>
       <c r="B230" s="1" t="n">
-        <v>1</v>
+        <v>1.5</v>
       </c>
       <c r="C230" s="1" t="inlineStr">
         <is>
-          <t>daraja</t>
+          <t>x</t>
         </is>
       </c>
       <c r="D230" s="1" t="inlineStr">
         <is>
-          <t>Shuncha yuqori darajaga hujum qilish mumkin</t>
+          <t>Askar soni va oʻlja koʻrinadi</t>
         </is>
       </c>
     </row>
     <row r="231">
       <c r="A231" s="1" t="inlineStr">
         <is>
-          <t>Qalqon darajasi</t>
+          <t>Aniq chegara</t>
         </is>
       </c>
       <c r="B231" s="1" t="n">
-        <v>6</v>
+        <v>2.5</v>
       </c>
       <c r="C231" s="1" t="inlineStr">
         <is>
-          <t>daraja</t>
+          <t>x</t>
         </is>
       </c>
       <c r="D231" s="1" t="inlineStr">
         <is>
-          <t>Shu darajagacha umuman hujum qilib boʻlmaydi</t>
+          <t>Aniq raqamlar va himoya foizi koʻrinadi</t>
         </is>
       </c>
     </row>
     <row r="232">
       <c r="A232" s="1" t="inlineStr">
         <is>
-          <t>Kengayish kutish vaqti</t>
+          <t>Razvedka kutish vaqti</t>
         </is>
       </c>
       <c r="B232" s="1" t="n">
-        <v>30</v>
+        <v>10</v>
       </c>
       <c r="C232" s="1" t="inlineStr">
         <is>
@@ -21642,233 +21627,1495 @@
       </c>
       <c r="D232" s="1" t="inlineStr">
         <is>
-          <t>Mos raqib topilmasa, oyna shuncha vaqtdan keyin kengayadi</t>
+          <t>Keyingi razvedkagacha</t>
         </is>
       </c>
     </row>
     <row r="233">
       <c r="A233" s="1" t="inlineStr">
         <is>
-          <t>Maksimal oyna</t>
+          <t>Maʼlumot muddati</t>
         </is>
       </c>
       <c r="B233" s="1" t="n">
-        <v>3</v>
+        <v>30</v>
       </c>
       <c r="C233" s="1" t="inlineStr">
         <is>
-          <t>daraja</t>
+          <t>daqiqa</t>
         </is>
       </c>
       <c r="D233" s="1" t="inlineStr">
         <is>
-          <t>Oyna eng koʻpi bilan shuncha kengayadi</t>
+          <t>Shundan keyin maʼlumot eskiradi</t>
         </is>
       </c>
     </row>
     <row r="234">
       <c r="A234" s="1" t="inlineStr">
         <is>
-          <t>Minimal havza</t>
+          <t>Muvaffaqiyatsiz jarohat</t>
         </is>
       </c>
       <c r="B234" s="1" t="n">
-        <v>10</v>
+        <v>0.1</v>
       </c>
       <c r="C234" s="1" t="inlineStr">
         <is>
-          <t>oʻyinchi</t>
+          <t>ulush</t>
         </is>
       </c>
       <c r="D234" s="1" t="inlineStr">
         <is>
-          <t>Oynada shuncha faol raqib boʻlishi kerak</t>
+          <t>Yoʻqotilgan razvedkachilar ulushi</t>
         </is>
       </c>
     </row>
     <row r="235">
       <c r="A235" s="1" t="inlineStr">
         <is>
-          <t>Razvedka</t>
+          <t>Oʻlja aniqligi</t>
+        </is>
+      </c>
+      <c r="B235" s="1" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="C235" s="1" t="inlineStr">
+        <is>
+          <t>ulush</t>
+        </is>
+      </c>
+      <c r="D235" s="1" t="inlineStr">
+        <is>
+          <t>Toʻliq bosqichda raqam ±shuncha xato koʻrsatiladi</t>
         </is>
       </c>
     </row>
     <row r="236">
       <c r="A236" s="1" t="inlineStr">
         <is>
-          <t>Qisman chegara</t>
+          <t>Qasos bonusi</t>
         </is>
       </c>
       <c r="B236" s="1" t="n">
-        <v>1</v>
+        <v>0.2</v>
       </c>
       <c r="C236" s="1" t="inlineStr">
         <is>
-          <t>x</t>
+          <t>ulush</t>
         </is>
       </c>
       <c r="D236" s="1" t="inlineStr">
         <is>
-          <t>Shundan past — razvedka muvaffaqiyatsiz</t>
+          <t>24 soat ichida qaytarilgan hujumga</t>
         </is>
       </c>
     </row>
     <row r="237">
       <c r="A237" s="1" t="inlineStr">
         <is>
-          <t>Toʻliq chegara</t>
-        </is>
-      </c>
-      <c r="B237" s="1" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="C237" s="1" t="inlineStr">
-        <is>
-          <t>x</t>
-        </is>
-      </c>
-      <c r="D237" s="1" t="inlineStr">
-        <is>
-          <t>Askar soni va oʻlja koʻrinadi</t>
+          <t>XP manbalari</t>
         </is>
       </c>
     </row>
     <row r="238">
       <c r="A238" s="1" t="inlineStr">
         <is>
-          <t>Aniq chegara</t>
+          <t>Ov XP</t>
         </is>
       </c>
       <c r="B238" s="1" t="n">
-        <v>2.5</v>
+        <v>0.5</v>
       </c>
       <c r="C238" s="1" t="inlineStr">
         <is>
-          <t>x</t>
+          <t>xp/kg</t>
         </is>
       </c>
       <c r="D238" s="1" t="inlineStr">
         <is>
-          <t>Aniq raqamlar va himoya foizi koʻrinadi</t>
+          <t>Oʻlja vazni × shu</t>
         </is>
       </c>
     </row>
     <row r="239">
       <c r="A239" s="1" t="inlineStr">
         <is>
-          <t>Razvedka kutish vaqti</t>
+          <t>Qurilish XP</t>
         </is>
       </c>
       <c r="B239" s="1" t="n">
-        <v>10</v>
+        <v>0.02</v>
       </c>
       <c r="C239" s="1" t="inlineStr">
         <is>
-          <t>daqiqa</t>
+          <t>xp/birlik</t>
         </is>
       </c>
       <c r="D239" s="1" t="inlineStr">
         <is>
-          <t>Keyingi razvedkagacha</t>
+          <t>Sarflangan qurilish resursi × shu</t>
         </is>
       </c>
     </row>
     <row r="240">
       <c r="A240" s="1" t="inlineStr">
         <is>
-          <t>Maʼlumot muddati</t>
+          <t>PvP XP</t>
         </is>
       </c>
       <c r="B240" s="1" t="n">
-        <v>30</v>
+        <v>0.03</v>
       </c>
       <c r="C240" s="1" t="inlineStr">
         <is>
-          <t>daqiqa</t>
+          <t>xp/EP</t>
         </is>
       </c>
       <c r="D240" s="1" t="inlineStr">
         <is>
-          <t>Shundan keyin maʼlumot eskiradi</t>
+          <t>Yetkazilgan EP zarar × shu × natija koeff.</t>
         </is>
       </c>
     </row>
     <row r="241">
       <c r="A241" s="1" t="inlineStr">
         <is>
-          <t>Muvaffaqiyatsiz jarohat</t>
+          <t>PvP XP: gʻalaba</t>
         </is>
       </c>
       <c r="B241" s="1" t="n">
-        <v>0.1</v>
+        <v>1.5</v>
       </c>
       <c r="C241" s="1" t="inlineStr">
         <is>
-          <t>ulush</t>
+          <t>x</t>
         </is>
       </c>
       <c r="D241" s="1" t="inlineStr">
         <is>
-          <t>Yoʻqotilgan razvedkachilar ulushi</t>
+          <t>Natija koeffitsienti</t>
         </is>
       </c>
     </row>
     <row r="242">
       <c r="A242" s="1" t="inlineStr">
         <is>
-          <t>Oʻlja aniqligi</t>
+          <t>PvP XP: durang</t>
         </is>
       </c>
       <c r="B242" s="1" t="n">
-        <v>0.2</v>
+        <v>1</v>
       </c>
       <c r="C242" s="1" t="inlineStr">
         <is>
-          <t>ulush</t>
+          <t>x</t>
         </is>
       </c>
       <c r="D242" s="1" t="inlineStr">
         <is>
-          <t>Toʻliq bosqichda raqam ±shuncha xato koʻrsatiladi</t>
+          <t>Natija koeffitsienti</t>
         </is>
       </c>
     </row>
     <row r="243">
       <c r="A243" s="1" t="inlineStr">
         <is>
-          <t>Qasos bonusi</t>
+          <t>PvP XP: magʻlubiyat</t>
         </is>
       </c>
       <c r="B243" s="1" t="n">
-        <v>0.2</v>
+        <v>0.5</v>
       </c>
       <c r="C243" s="1" t="inlineStr">
         <is>
-          <t>ulush</t>
+          <t>x</t>
         </is>
       </c>
       <c r="D243" s="1" t="inlineStr">
         <is>
-          <t>24 soat ichida qaytarilgan hujumga</t>
+          <t>Natija koeffitsienti</t>
         </is>
       </c>
     </row>
     <row r="244">
       <c r="A244" s="1" t="inlineStr">
         <is>
-          <t>Izoh: vazn ustuni haqiqiy zoologik maʼlumotlarga (oʻrtacha katta erkak boʻri vazni) asoslangan; mifologik boʻrilarda vazn yoʻq.</t>
+          <t>Vazifa XP ulushi</t>
+        </is>
+      </c>
+      <c r="B244" s="1" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="C244" s="1" t="inlineStr">
+        <is>
+          <t>ulush</t>
+        </is>
+      </c>
+      <c r="D244" s="1" t="inlineStr">
+        <is>
+          <t>Vazifa mukofot byudjetining shunchasi XP sifatida</t>
         </is>
       </c>
     </row>
     <row r="245">
       <c r="A245" s="1" t="inlineStr">
         <is>
-          <t>Barcha stat, XP, oziq va bino raqamlari shu varaqdagi kiritmalardan hisoblanadi — balansni faqat shu yerdan sozlang.</t>
+          <t>Catch-up maksimal qoʻshimcha</t>
+        </is>
+      </c>
+      <c r="B245" s="1" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="C245" s="1" t="inlineStr">
+        <is>
+          <t>ulush</t>
+        </is>
+      </c>
+      <c r="D245" s="1" t="inlineStr">
+        <is>
+          <t>+50% gacha</t>
         </is>
       </c>
     </row>
     <row r="246">
       <c r="A246" s="1" t="inlineStr">
+        <is>
+          <t>Catch-up koeffitsienti</t>
+        </is>
+      </c>
+      <c r="B246" s="1" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="C246" s="1" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
+      <c r="D246" s="1" t="inlineStr">
+        <is>
+          <t>(nisbat − chegara) × shu</t>
+        </is>
+      </c>
+    </row>
+    <row r="247">
+      <c r="A247" s="1" t="inlineStr">
+        <is>
+          <t>Catch-up chegarasi</t>
+        </is>
+      </c>
+      <c r="B247" s="1" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="C247" s="1" t="inlineStr">
+        <is>
+          <t>ulush</t>
+        </is>
+      </c>
+      <c r="D247" s="1" t="inlineStr">
+        <is>
+          <t>Shundan kam orqada qolganga bonus yoʻq</t>
+        </is>
+      </c>
+    </row>
+    <row r="248">
+      <c r="A248" s="1" t="inlineStr">
+        <is>
+          <t>Catch-up pasayish boshi</t>
+        </is>
+      </c>
+      <c r="B248" s="1" t="n">
+        <v>15</v>
+      </c>
+      <c r="C248" s="1" t="inlineStr">
+        <is>
+          <t>daraja</t>
+        </is>
+      </c>
+      <c r="D248" s="1" t="inlineStr">
+        <is>
+          <t>Bonus shu darajadan pasayadi</t>
+        </is>
+      </c>
+    </row>
+    <row r="249">
+      <c r="A249" s="1" t="inlineStr">
+        <is>
+          <t>Catch-up pasayish oxiri</t>
+        </is>
+      </c>
+      <c r="B249" s="1" t="n">
+        <v>20</v>
+      </c>
+      <c r="C249" s="1" t="inlineStr">
+        <is>
+          <t>daraja</t>
+        </is>
+      </c>
+      <c r="D249" s="1" t="inlineStr">
+        <is>
+          <t>Shu darajada bonus 0</t>
+        </is>
+      </c>
+    </row>
+    <row r="250">
+      <c r="A250" s="1" t="inlineStr">
+        <is>
+          <t>Ov</t>
+        </is>
+      </c>
+    </row>
+    <row r="251">
+      <c r="A251" s="1" t="inlineStr">
+        <is>
+          <t>Ovchi ochilish darajasi</t>
+        </is>
+      </c>
+      <c r="B251" s="1" t="n">
+        <v>3</v>
+      </c>
+      <c r="C251" s="1" t="inlineStr">
+        <is>
+          <t>daraja</t>
+        </is>
+      </c>
+      <c r="D251" s="1" t="inlineStr">
+        <is>
+          <t>Ov soʻqmogʻi bilan</t>
+        </is>
+      </c>
+    </row>
+    <row r="252">
+      <c r="A252" s="1" t="inlineStr">
+        <is>
+          <t>Yolgʻiz ov maksimal darajasi</t>
+        </is>
+      </c>
+      <c r="B252" s="1" t="n">
+        <v>3</v>
+      </c>
+      <c r="C252" s="1" t="inlineStr">
+        <is>
+          <t>daraja</t>
+        </is>
+      </c>
+      <c r="D252" s="1" t="inlineStr">
+        <is>
+          <t>1–3 darajada alfa oʻzi ovlaydi</t>
+        </is>
+      </c>
+    </row>
+    <row r="253">
+      <c r="A253" s="1" t="inlineStr">
+        <is>
+          <t>Yolgʻiz ov kutish vaqti</t>
+        </is>
+      </c>
+      <c r="B253" s="1" t="n">
+        <v>2</v>
+      </c>
+      <c r="C253" s="1" t="inlineStr">
+        <is>
+          <t>daqiqa</t>
+        </is>
+      </c>
+      <c r="D253" s="1" t="inlineStr">
+        <is>
+          <t>Bosishlar orasida</t>
+        </is>
+      </c>
+    </row>
+    <row r="254">
+      <c r="A254" s="1" t="inlineStr">
+        <is>
+          <t>Ov davomiyligi</t>
+        </is>
+      </c>
+      <c r="B254" s="1" t="n">
+        <v>60</v>
+      </c>
+      <c r="C254" s="1" t="inlineStr">
+        <is>
+          <t>daqiqa</t>
+        </is>
+      </c>
+      <c r="D254" s="1" t="inlineStr">
+        <is>
+          <t>Bitta ov yurishi</t>
+        </is>
+      </c>
+    </row>
+    <row r="255">
+      <c r="A255" s="1" t="inlineStr">
+        <is>
+          <t>Ovchi unumi koeffitsienti</t>
+        </is>
+      </c>
+      <c r="B255" s="1" t="n">
+        <v>5</v>
+      </c>
+      <c r="C255" s="1" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
+      <c r="D255" s="1" t="inlineStr">
+        <is>
+          <t>Ovchi unumi (kg/soat) = shu × bir askarning kunlik ehtiyoji</t>
+        </is>
+      </c>
+    </row>
+    <row r="256">
+      <c r="A256" s="1" t="inlineStr">
+        <is>
+          <t>Ovchi tier bonusi</t>
+        </is>
+      </c>
+      <c r="B256" s="1" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="C256" s="1" t="inlineStr">
+        <is>
+          <t>ulush/tier</t>
+        </is>
+      </c>
+      <c r="D256" s="1" t="inlineStr">
+        <is>
+          <t>Yuqori tier ovchi koʻproq ovlaydi</t>
+        </is>
+      </c>
+    </row>
+    <row r="257">
+      <c r="A257" s="1" t="inlineStr">
+        <is>
+          <t>Oʻlja toʻdasi boʻluvchisi</t>
+        </is>
+      </c>
+      <c r="B257" s="1" t="n">
+        <v>20</v>
+      </c>
+      <c r="C257" s="1" t="inlineStr">
+        <is>
+          <t>kg/boʻri</t>
+        </is>
+      </c>
+      <c r="D257" s="1" t="inlineStr">
+        <is>
+          <t>Minimal toʻda = oʻlja vazni ÷ shu (yuqoriga)</t>
+        </is>
+      </c>
+    </row>
+    <row r="258">
+      <c r="A258" s="1" t="inlineStr">
+        <is>
+          <t>Kichik oʻlja jazosi</t>
+        </is>
+      </c>
+      <c r="B258" s="1" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="C258" s="1" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
+      <c r="D258" s="1" t="inlineStr">
+        <is>
+          <t>Toʻda yetmasa ov natijasi × shu</t>
+        </is>
+      </c>
+    </row>
+    <row r="259">
+      <c r="A259" s="1" t="inlineStr">
+        <is>
+          <t>Ov guruhi bonusi</t>
+        </is>
+      </c>
+      <c r="B259" s="1" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="C259" s="1" t="inlineStr">
+        <is>
+          <t>ulush/oʻyinchi</t>
+        </is>
+      </c>
+      <c r="D259" s="1" t="inlineStr">
+        <is>
+          <t>Har qoʻshimcha oʻyinchi uchun</t>
+        </is>
+      </c>
+    </row>
+    <row r="260">
+      <c r="A260" s="1" t="inlineStr">
+        <is>
+          <t>Ov guruhi maksimal hajmi</t>
+        </is>
+      </c>
+      <c r="B260" s="1" t="n">
+        <v>4</v>
+      </c>
+      <c r="C260" s="1" t="inlineStr">
+        <is>
+          <t>oʻyinchi</t>
+        </is>
+      </c>
+      <c r="D260" s="1" t="inlineStr">
+        <is>
+          <t>2–4 oʻyinchi</t>
+        </is>
+      </c>
+    </row>
+    <row r="261">
+      <c r="A261" s="1" t="inlineStr">
+        <is>
+          <t>Ovdan shifobaxsh oʻt</t>
+        </is>
+      </c>
+      <c r="B261" s="1" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="C261" s="1" t="inlineStr">
+        <is>
+          <t>ulush</t>
+        </is>
+      </c>
+      <c r="D261" s="1" t="inlineStr">
+        <is>
+          <t>Ov natijasining shunchasi oʻt (birlik)</t>
+        </is>
+      </c>
+    </row>
+    <row r="262">
+      <c r="A262" s="1" t="inlineStr">
+        <is>
+          <t>Oy nuri va suv</t>
+        </is>
+      </c>
+    </row>
+    <row r="263">
+      <c r="A263" s="1" t="inlineStr">
+        <is>
+          <t>Oy nuri ehtiyoj darajasi</t>
+        </is>
+      </c>
+      <c r="B263" s="1" t="n">
+        <v>20</v>
+      </c>
+      <c r="C263" s="1" t="inlineStr">
+        <is>
+          <t>daraja</t>
+        </is>
+      </c>
+      <c r="D263" s="1" t="inlineStr">
+        <is>
+          <t>Shu darajadan oy nuri kerak</t>
+        </is>
+      </c>
+    </row>
+    <row r="264">
+      <c r="A264" s="1" t="inlineStr">
+        <is>
+          <t>Oy nuri passiv ishlab chiqarishi</t>
+        </is>
+      </c>
+      <c r="B264" s="1" t="n">
+        <v>0.006</v>
+      </c>
+      <c r="C264" s="1" t="inlineStr">
+        <is>
+          <t>birlik/askar/soat</t>
+        </is>
+      </c>
+      <c r="D264" s="1" t="inlineStr">
+        <is>
+          <t>Ehtiyojning 72%</t>
+        </is>
+      </c>
+    </row>
+    <row r="265">
+      <c r="A265" s="1" t="inlineStr">
+        <is>
+          <t>Oy mehrobi bonusi</t>
+        </is>
+      </c>
+      <c r="B265" s="1" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="C265" s="1" t="inlineStr">
+        <is>
+          <t>ulush</t>
+        </is>
+      </c>
+      <c r="D265" s="1" t="inlineStr">
+        <is>
+          <t>Passiv oy nuriga qoʻshiladi (72% → 100%)</t>
+        </is>
+      </c>
+    </row>
+    <row r="266">
+      <c r="A266" s="1" t="inlineStr">
+        <is>
+          <t>Oy nuri yetishmasligi CP jazosi</t>
+        </is>
+      </c>
+      <c r="B266" s="1" t="n">
+        <v>0.15</v>
+      </c>
+      <c r="C266" s="1" t="inlineStr">
+        <is>
+          <t>ulush</t>
+        </is>
+      </c>
+      <c r="D266" s="1" t="inlineStr">
+        <is>
+          <t>Goʻsht ochligidan alohida</t>
+        </is>
+      </c>
+    </row>
+    <row r="267">
+      <c r="A267" s="1" t="inlineStr">
+        <is>
+          <t>Bozor: oy nuri kurs koeffitsienti</t>
+        </is>
+      </c>
+      <c r="B267" s="1" t="n">
+        <v>2</v>
+      </c>
+      <c r="C267" s="1" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
+      <c r="D267" s="1" t="inlineStr">
+        <is>
+          <t>Oy nuri boshqa resursdan shuncha qimmat</t>
+        </is>
+      </c>
+    </row>
+    <row r="268">
+      <c r="A268" s="1" t="inlineStr">
+        <is>
+          <t>Suv yetishmasligi tezlik jazosi</t>
+        </is>
+      </c>
+      <c r="B268" s="1" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="C268" s="1" t="inlineStr">
+        <is>
+          <t>ulush</t>
+        </is>
+      </c>
+      <c r="D268" s="1" t="inlineStr">
+        <is>
+          <t>Yurish tezligi shuncha kamayadi</t>
+        </is>
+      </c>
+    </row>
+    <row r="269">
+      <c r="A269" s="1" t="inlineStr">
+        <is>
+          <t>Davolash</t>
+        </is>
+      </c>
+    </row>
+    <row r="270">
+      <c r="A270" s="1" t="inlineStr">
+        <is>
+          <t>Davolash narxi: oʻt</t>
+        </is>
+      </c>
+      <c r="B270" s="1" t="n">
+        <v>2</v>
+      </c>
+      <c r="C270" s="1" t="inlineStr">
+        <is>
+          <t>birlik/tier</t>
+        </is>
+      </c>
+      <c r="D270" s="1" t="inlineStr">
+        <is>
+          <t>Bir boʻri uchun</t>
+        </is>
+      </c>
+    </row>
+    <row r="271">
+      <c r="A271" s="1" t="inlineStr">
+        <is>
+          <t>Shifo gʻorisiz tuzalish vaqti</t>
+        </is>
+      </c>
+      <c r="B271" s="1" t="n">
+        <v>180</v>
+      </c>
+      <c r="C271" s="1" t="inlineStr">
+        <is>
+          <t>daqiqa</t>
+        </is>
+      </c>
+      <c r="D271" s="1" t="inlineStr">
+        <is>
+          <t>1–5 daraja: bepul, sekin</t>
+        </is>
+      </c>
+    </row>
+    <row r="272">
+      <c r="A272" s="1" t="inlineStr">
+        <is>
+          <t>Jang natijasi</t>
+        </is>
+      </c>
+    </row>
+    <row r="273">
+      <c r="A273" s="1" t="inlineStr">
+        <is>
+          <t>Toʻliq gʻalaba chegarasi</t>
+        </is>
+      </c>
+      <c r="B273" s="1" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="C273" s="1" t="inlineStr">
+        <is>
+          <t>R</t>
+        </is>
+      </c>
+      <c r="D273" s="1" t="inlineStr">
+        <is>
+          <t>R shundan katta yoki teng</t>
+        </is>
+      </c>
+    </row>
+    <row r="274">
+      <c r="A274" s="1" t="inlineStr">
+        <is>
+          <t>Gʻalaba chegarasi</t>
+        </is>
+      </c>
+      <c r="B274" s="1" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="C274" s="1" t="inlineStr">
+        <is>
+          <t>R</t>
+        </is>
+      </c>
+      <c r="D274" s="1" t="inlineStr">
+        <is>
+          <t>Qisman gʻalaba shundan</t>
+        </is>
+      </c>
+    </row>
+    <row r="275">
+      <c r="A275" s="1" t="inlineStr">
+        <is>
+          <t>Magʻlubiyat chegarasi</t>
+        </is>
+      </c>
+      <c r="B275" s="1" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="C275" s="1" t="inlineStr">
+        <is>
+          <t>R</t>
+        </is>
+      </c>
+      <c r="D275" s="1" t="inlineStr">
+        <is>
+          <t>R shundan kichik yoki teng — magʻlubiyat; oraliq — durang</t>
+        </is>
+      </c>
+    </row>
+    <row r="276">
+      <c r="A276" s="1" t="inlineStr">
+        <is>
+          <t>Tuzoq ehtimoli</t>
+        </is>
+      </c>
+      <c r="B276" s="1" t="n">
+        <v>0.15</v>
+      </c>
+      <c r="C276" s="1" t="inlineStr">
+        <is>
+          <t>ulush</t>
+        </is>
+      </c>
+      <c r="D276" s="1" t="inlineStr">
+        <is>
+          <t>Razvedkasiz hujumda</t>
+        </is>
+      </c>
+    </row>
+    <row r="277">
+      <c r="A277" s="1" t="inlineStr">
+        <is>
+          <t>Tuzoq zarari</t>
+        </is>
+      </c>
+      <c r="B277" s="1" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="C277" s="1" t="inlineStr">
+        <is>
+          <t>ulush</t>
+        </is>
+      </c>
+      <c r="D277" s="1" t="inlineStr">
+        <is>
+          <t>Hujumchi yoʻqotishiga qoʻshiladi</t>
+        </is>
+      </c>
+    </row>
+    <row r="278">
+      <c r="A278" s="1" t="inlineStr">
+        <is>
+          <t>Chekinish chegarasi</t>
+        </is>
+      </c>
+      <c r="B278" s="1" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="C278" s="1" t="inlineStr">
+        <is>
+          <t>ulush</t>
+        </is>
+      </c>
+      <c r="D278" s="1" t="inlineStr">
+        <is>
+          <t>Yoʻqotish shundan oshsa jang 4-raundda tugaydi</t>
+        </is>
+      </c>
+    </row>
+    <row r="279">
+      <c r="A279" s="1" t="inlineStr">
+        <is>
+          <t>Himoya devori bonusi</t>
+        </is>
+      </c>
+      <c r="B279" s="1" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="C279" s="1" t="inlineStr">
+        <is>
+          <t>ulush/daraja</t>
+        </is>
+      </c>
+      <c r="D279" s="1" t="inlineStr">
+        <is>
+          <t>Himoyachi EP si</t>
+        </is>
+      </c>
+    </row>
+    <row r="280">
+      <c r="A280" s="1" t="inlineStr">
+        <is>
+          <t>Bir raqibga kunlik hujum</t>
+        </is>
+      </c>
+      <c r="B280" s="1" t="n">
+        <v>3</v>
+      </c>
+      <c r="C280" s="1" t="inlineStr">
+        <is>
+          <t>ta</t>
+        </is>
+      </c>
+      <c r="D280" s="1" t="inlineStr">
+        <is>
+          <t>24 soat ichida</t>
+        </is>
+      </c>
+    </row>
+    <row r="281">
+      <c r="A281" s="1" t="inlineStr">
+        <is>
+          <t>Qisman gʻalaba oʻlja koeffitsienti</t>
+        </is>
+      </c>
+      <c r="B281" s="1" t="n">
+        <v>0.55</v>
+      </c>
+      <c r="C281" s="1" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
+      <c r="D281" s="1" t="inlineStr">
+        <is>
+          <t>Toʻliq gʻalaba — 1.00</t>
+        </is>
+      </c>
+    </row>
+    <row r="282">
+      <c r="A282" s="1" t="inlineStr">
+        <is>
+          <t>Takror hujum koeff. (2-hujum)</t>
+        </is>
+      </c>
+      <c r="B282" s="1" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="C282" s="1" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
+      <c r="D282" s="1" t="inlineStr">
+        <is>
+          <t>24 soat ichida</t>
+        </is>
+      </c>
+    </row>
+    <row r="283">
+      <c r="A283" s="1" t="inlineStr">
+        <is>
+          <t>Takror hujum koeff. (3-hujum)</t>
+        </is>
+      </c>
+      <c r="B283" s="1" t="n">
+        <v>0.25</v>
+      </c>
+      <c r="C283" s="1" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
+      <c r="D283" s="1" t="inlineStr">
+        <is>
+          <t>24 soat ichida</t>
+        </is>
+      </c>
+    </row>
+    <row r="284">
+      <c r="A284" s="1" t="inlineStr">
+        <is>
+          <t>Daraja oʻlja koeff. −1</t>
+        </is>
+      </c>
+      <c r="B284" s="1" t="n">
+        <v>0.7</v>
+      </c>
+      <c r="C284" s="1" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
+      <c r="D284" s="1" t="inlineStr">
+        <is>
+          <t>Pastga hujum</t>
+        </is>
+      </c>
+    </row>
+    <row r="285">
+      <c r="A285" s="1" t="inlineStr">
+        <is>
+          <t>Daraja oʻlja koeff. +1</t>
+        </is>
+      </c>
+      <c r="B285" s="1" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="C285" s="1" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
+      <c r="D285" s="1" t="inlineStr">
+        <is>
+          <t>Yuqoriga hujum</t>
+        </is>
+      </c>
+    </row>
+    <row r="286">
+      <c r="A286" s="1" t="inlineStr">
+        <is>
+          <t>Daraja oʻlja koeff. −2</t>
+        </is>
+      </c>
+      <c r="B286" s="1" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="C286" s="1" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
+      <c r="D286" s="1" t="inlineStr">
+        <is>
+          <t>Kengaygan oyna</t>
+        </is>
+      </c>
+    </row>
+    <row r="287">
+      <c r="A287" s="1" t="inlineStr">
+        <is>
+          <t>Daraja oʻlja koeff. +2</t>
+        </is>
+      </c>
+      <c r="B287" s="1" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="C287" s="1" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
+      <c r="D287" s="1" t="inlineStr">
+        <is>
+          <t>Kengaygan oyna</t>
+        </is>
+      </c>
+    </row>
+    <row r="288">
+      <c r="A288" s="1" t="inlineStr">
+        <is>
+          <t>Daraja oʻlja koeff. −3</t>
+        </is>
+      </c>
+      <c r="B288" s="1" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="C288" s="1" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
+      <c r="D288" s="1" t="inlineStr">
+        <is>
+          <t>Kengaygan oyna</t>
+        </is>
+      </c>
+    </row>
+    <row r="289">
+      <c r="A289" s="1" t="inlineStr">
+        <is>
+          <t>Daraja oʻlja koeff. +3</t>
+        </is>
+      </c>
+      <c r="B289" s="1" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="C289" s="1" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
+      <c r="D289" s="1" t="inlineStr">
+        <is>
+          <t>Kengaygan oyna</t>
+        </is>
+      </c>
+    </row>
+    <row r="290">
+      <c r="A290" s="1" t="inlineStr">
+        <is>
+          <t>Oflayn himoyachi oʻlja koeff.</t>
+        </is>
+      </c>
+      <c r="B290" s="1" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="C290" s="1" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
+      <c r="D290" s="1" t="inlineStr">
+        <is>
+          <t>Himoyachi 24+ soat oflayn boʻlsa</t>
+        </is>
+      </c>
+    </row>
+    <row r="291">
+      <c r="A291" s="1" t="inlineStr">
+        <is>
+          <t>Oflayn oʻlja chegarasi</t>
+        </is>
+      </c>
+      <c r="B291" s="1" t="n">
+        <v>24</v>
+      </c>
+      <c r="C291" s="1" t="inlineStr">
+        <is>
+          <t>soat</t>
+        </is>
+      </c>
+      <c r="D291" s="1" t="inlineStr">
+        <is>
+          <t>Shundan uzoq oflayn</t>
+        </is>
+      </c>
+    </row>
+    <row r="292">
+      <c r="A292" s="1" t="inlineStr">
+        <is>
+          <t>Yovvoyi toʻdalar (botlar)</t>
+        </is>
+      </c>
+    </row>
+    <row r="293">
+      <c r="A293" s="1" t="inlineStr">
+        <is>
+          <t>Botlar ochilish darajasi</t>
+        </is>
+      </c>
+      <c r="B293" s="1" t="n">
+        <v>4</v>
+      </c>
+      <c r="C293" s="1" t="inlineStr">
+        <is>
+          <t>daraja</t>
+        </is>
+      </c>
+      <c r="D293" s="1" t="inlineStr">
+        <is>
+          <t>4–6 darajada roʻyxat faqat botlardan</t>
+        </is>
+      </c>
+    </row>
+    <row r="294">
+      <c r="A294" s="1" t="inlineStr">
+        <is>
+          <t>Bot kuchi: kuchsiz</t>
+        </is>
+      </c>
+      <c r="B294" s="1" t="n">
+        <v>0.7</v>
+      </c>
+      <c r="C294" s="1" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
+      <c r="D294" s="1" t="inlineStr">
+        <is>
+          <t>Oʻyinchi EP siga nisbatan</t>
+        </is>
+      </c>
+    </row>
+    <row r="295">
+      <c r="A295" s="1" t="inlineStr">
+        <is>
+          <t>Bot kuchi: teng</t>
+        </is>
+      </c>
+      <c r="B295" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="C295" s="1" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
+      <c r="D295" s="1" t="inlineStr">
+        <is>
+          <t>Oʻyinchi EP siga nisbatan</t>
+        </is>
+      </c>
+    </row>
+    <row r="296">
+      <c r="A296" s="1" t="inlineStr">
+        <is>
+          <t>Bot kuchi: kuchli</t>
+        </is>
+      </c>
+      <c r="B296" s="1" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="C296" s="1" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
+      <c r="D296" s="1" t="inlineStr">
+        <is>
+          <t>Oʻyinchi EP siga nisbatan</t>
+        </is>
+      </c>
+    </row>
+    <row r="297">
+      <c r="A297" s="1" t="inlineStr">
+        <is>
+          <t>Bot tasodif oraligʻi</t>
+        </is>
+      </c>
+      <c r="B297" s="1" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="C297" s="1" t="inlineStr">
+        <is>
+          <t>ulush</t>
+        </is>
+      </c>
+      <c r="D297" s="1" t="inlineStr">
+        <is>
+          <t>±shuncha</t>
+        </is>
+      </c>
+    </row>
+    <row r="298">
+      <c r="A298" s="1" t="inlineStr">
+        <is>
+          <t>Navbat, qalqon va boshqalar</t>
+        </is>
+      </c>
+    </row>
+    <row r="299">
+      <c r="A299" s="1" t="inlineStr">
+        <is>
+          <t>Bekor qilishda qaytarish</t>
+        </is>
+      </c>
+      <c r="B299" s="1" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="C299" s="1" t="inlineStr">
+        <is>
+          <t>ulush</t>
+        </is>
+      </c>
+      <c r="D299" s="1" t="inlineStr">
+        <is>
+          <t>Navbat bekor qilinsa resursning shunchasi qaytadi</t>
+        </is>
+      </c>
+    </row>
+    <row r="300">
+      <c r="A300" s="1" t="inlineStr">
+        <is>
+          <t>Ikkinchi navbat bepul darajasi</t>
+        </is>
+      </c>
+      <c r="B300" s="1" t="n">
+        <v>10</v>
+      </c>
+      <c r="C300" s="1" t="inlineStr">
+        <is>
+          <t>daraja</t>
+        </is>
+      </c>
+      <c r="D300" s="1" t="inlineStr">
+        <is>
+          <t>Shu darajadan hammaga</t>
+        </is>
+      </c>
+    </row>
+    <row r="301">
+      <c r="A301" s="1" t="inlineStr">
+        <is>
+          <t>Oflayn ombor xaridi</t>
+        </is>
+      </c>
+      <c r="B301" s="1" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="C301" s="1" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
+      <c r="D301" s="1" t="inlineStr">
+        <is>
+          <t>Oflayn koeffitsientga qoʻshiladi (2.0 → 2.5)</t>
+        </is>
+      </c>
+    </row>
+    <row r="302">
+      <c r="A302" s="1" t="inlineStr">
+        <is>
+          <t>Oflayn chegarasi</t>
+        </is>
+      </c>
+      <c r="B302" s="1" t="n">
+        <v>5</v>
+      </c>
+      <c r="C302" s="1" t="inlineStr">
+        <is>
+          <t>daqiqa</t>
+        </is>
+      </c>
+      <c r="D302" s="1" t="inlineStr">
+        <is>
+          <t>Oxirgi soʻrovdan shuncha oʻtsa — oflayn</t>
+        </is>
+      </c>
+    </row>
+    <row r="303">
+      <c r="A303" s="1" t="inlineStr">
+        <is>
+          <t>In mashq tezlanishi</t>
+        </is>
+      </c>
+      <c r="B303" s="1" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="C303" s="1" t="inlineStr">
+        <is>
+          <t>ulush/daraja</t>
+        </is>
+      </c>
+      <c r="D303" s="1" t="inlineStr">
+        <is>
+          <t>In darajasi boshiga</t>
+        </is>
+      </c>
+    </row>
+    <row r="304">
+      <c r="A304" s="1" t="inlineStr">
+        <is>
+          <t>Lager ulushi tavani</t>
+        </is>
+      </c>
+      <c r="B304" s="1" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="C304" s="1" t="inlineStr">
+        <is>
+          <t>ulush</t>
+        </is>
+      </c>
+      <c r="D304" s="1" t="inlineStr">
+        <is>
+          <t>Ustaxona kunlik ishlab chiqarishiga nisbatan</t>
+        </is>
+      </c>
+    </row>
+    <row r="305">
+      <c r="A305" s="1" t="inlineStr">
+        <is>
+          <t>Reyd qalqoni: yoʻqotish chegarasi</t>
+        </is>
+      </c>
+      <c r="B305" s="1" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="C305" s="1" t="inlineStr">
+        <is>
+          <t>ulush</t>
+        </is>
+      </c>
+      <c r="D305" s="1" t="inlineStr">
+        <is>
+          <t>Shundan koʻp yoʻqotgan himoyachiga qalqon</t>
+        </is>
+      </c>
+    </row>
+    <row r="306">
+      <c r="A306" s="1" t="inlineStr">
+        <is>
+          <t>Reyd qalqoni</t>
+        </is>
+      </c>
+      <c r="B306" s="1" t="n">
+        <v>8</v>
+      </c>
+      <c r="C306" s="1" t="inlineStr">
+        <is>
+          <t>soat</t>
+        </is>
+      </c>
+      <c r="D306" s="1" t="inlineStr">
+        <is>
+          <t>30%+ yoʻqotgandan keyin</t>
+        </is>
+      </c>
+    </row>
+    <row r="307">
+      <c r="A307" s="1" t="inlineStr">
+        <is>
+          <t>Ketma-ket magʻlubiyat qalqoni</t>
+        </is>
+      </c>
+      <c r="B307" s="1" t="n">
+        <v>16</v>
+      </c>
+      <c r="C307" s="1" t="inlineStr">
+        <is>
+          <t>soat</t>
+        </is>
+      </c>
+      <c r="D307" s="1" t="inlineStr">
+        <is>
+          <t>Ketma-ket 2 magʻlubiyatdan keyin</t>
+        </is>
+      </c>
+    </row>
+    <row r="308">
+      <c r="A308" s="1" t="inlineStr">
+        <is>
+          <t>Tanishtiruv tezlashtirish uzunligi</t>
+        </is>
+      </c>
+      <c r="B308" s="1" t="n">
+        <v>60</v>
+      </c>
+      <c r="C308" s="1" t="inlineStr">
+        <is>
+          <t>daqiqa</t>
+        </is>
+      </c>
+      <c r="D308" s="1" t="inlineStr">
+        <is>
+          <t>Har bir bepul tezlashtirish</t>
+        </is>
+      </c>
+    </row>
+    <row r="309">
+      <c r="A309" s="1" t="inlineStr">
+        <is>
+          <t>Urushni rad etish jarimasi</t>
+        </is>
+      </c>
+      <c r="B309" s="1" t="n">
+        <v>50</v>
+      </c>
+      <c r="C309" s="1" t="inlineStr">
+        <is>
+          <t>reyting</t>
+        </is>
+      </c>
+      <c r="D309" s="1" t="inlineStr">
+        <is>
+          <t>Klan reytingidan</t>
+        </is>
+      </c>
+    </row>
+    <row r="310">
+      <c r="A310" s="1" t="inlineStr">
+        <is>
+          <t>Tungi reyd tezlik bonusi</t>
+        </is>
+      </c>
+      <c r="B310" s="1" t="n">
+        <v>0.25</v>
+      </c>
+      <c r="C310" s="1" t="inlineStr">
+        <is>
+          <t>ulush</t>
+        </is>
+      </c>
+      <c r="D310" s="1" t="inlineStr">
+        <is>
+          <t>22-darajadan, 22:00–06:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="311">
+      <c r="A311" s="1" t="inlineStr">
+        <is>
+          <t>Izoh: vazn ustuni haqiqiy zoologik maʼlumotlarga (oʻrtacha katta erkak boʻri vazni) asoslangan; mifologik boʻrilarda vazn yoʻq.</t>
+        </is>
+      </c>
+    </row>
+    <row r="312">
+      <c r="A312" s="1" t="inlineStr">
+        <is>
+          <t>Barcha stat, XP, oziq va bino raqamlari shu varaqdagi kiritmalardan hisoblanadi — balansni faqat shu yerdan sozlang.</t>
+        </is>
+      </c>
+    </row>
+    <row r="313">
+      <c r="A313" s="1" t="inlineStr">
         <is>
           <t>Bazaviy qiymatlar — test uchun taklif qilingan boshlangʻich raqamlar, haqiqiy oʻyin maʼlumotiga qarab oʻzgartiriladi.</t>
         </is>
@@ -21917,7 +23164,7 @@
     <row r="5">
       <c r="A5" s="1" t="inlineStr">
         <is>
-          <t>1. OZIQ GʻORI — goʻsht, suv, shifobaxsh oʻt saqlaydi</t>
+          <t>1. OZIQ GʻORI — goʻsht, suv, shifobaxsh oʻt va oy nuri saqlaydi (har biri alohida sigʻim)</t>
         </is>
       </c>
     </row>
@@ -21929,17 +23176,17 @@
       </c>
       <c r="B6" s="2" t="inlineStr">
         <is>
-          <t>Sigʻim (kg)</t>
+          <t>Sigʻim</t>
         </is>
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>Chirish vaqti (soat)</t>
+          <t>Passiv suv (soat)</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>Passiv suv (soat)</t>
+          <t>Oflayn sigʻim (2×)</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
@@ -21971,10 +23218,10 @@
         <v>40</v>
       </c>
       <c r="C7" s="1" t="n">
-        <v>12</v>
+        <v>0.2</v>
       </c>
       <c r="D7" s="1" t="n">
-        <v>5</v>
+        <v>80</v>
       </c>
       <c r="E7" s="1" t="n">
         <v>0.3</v>
@@ -21997,10 +23244,10 @@
         <v>49</v>
       </c>
       <c r="C8" s="1" t="n">
-        <v>13</v>
+        <v>0.3</v>
       </c>
       <c r="D8" s="1" t="n">
-        <v>6</v>
+        <v>98</v>
       </c>
       <c r="E8" s="1" t="n">
         <v>0.32</v>
@@ -22023,10 +23270,10 @@
         <v>60</v>
       </c>
       <c r="C9" s="1" t="n">
-        <v>15</v>
+        <v>0.4</v>
       </c>
       <c r="D9" s="1" t="n">
-        <v>7</v>
+        <v>120</v>
       </c>
       <c r="E9" s="1" t="n">
         <v>0.34</v>
@@ -22049,10 +23296,10 @@
         <v>73</v>
       </c>
       <c r="C10" s="1" t="n">
-        <v>16</v>
+        <v>0.5</v>
       </c>
       <c r="D10" s="1" t="n">
-        <v>9</v>
+        <v>146</v>
       </c>
       <c r="E10" s="1" t="n">
         <v>0.36</v>
@@ -22075,10 +23322,10 @@
         <v>89</v>
       </c>
       <c r="C11" s="1" t="n">
-        <v>18</v>
+        <v>0.6</v>
       </c>
       <c r="D11" s="1" t="n">
-        <v>10</v>
+        <v>178</v>
       </c>
       <c r="E11" s="1" t="n">
         <v>0.38</v>
@@ -22101,10 +23348,10 @@
         <v>108</v>
       </c>
       <c r="C12" s="1" t="n">
-        <v>19</v>
+        <v>0.8</v>
       </c>
       <c r="D12" s="1" t="n">
-        <v>12</v>
+        <v>216</v>
       </c>
       <c r="E12" s="1" t="n">
         <v>0.4</v>
@@ -22127,10 +23374,10 @@
         <v>132</v>
       </c>
       <c r="C13" s="1" t="n">
-        <v>21</v>
+        <v>1</v>
       </c>
       <c r="D13" s="1" t="n">
-        <v>15</v>
+        <v>264</v>
       </c>
       <c r="E13" s="1" t="n">
         <v>0.42</v>
@@ -22153,10 +23400,10 @@
         <v>161</v>
       </c>
       <c r="C14" s="1" t="n">
-        <v>22</v>
+        <v>1.2</v>
       </c>
       <c r="D14" s="1" t="n">
-        <v>18</v>
+        <v>322</v>
       </c>
       <c r="E14" s="1" t="n">
         <v>0.44</v>
@@ -22179,10 +23426,10 @@
         <v>196</v>
       </c>
       <c r="C15" s="1" t="n">
-        <v>24</v>
+        <v>1.5</v>
       </c>
       <c r="D15" s="1" t="n">
-        <v>21</v>
+        <v>392</v>
       </c>
       <c r="E15" s="1" t="n">
         <v>0.46</v>
@@ -22205,10 +23452,10 @@
         <v>239</v>
       </c>
       <c r="C16" s="1" t="n">
-        <v>25</v>
+        <v>1.9</v>
       </c>
       <c r="D16" s="1" t="n">
-        <v>26</v>
+        <v>478</v>
       </c>
       <c r="E16" s="1" t="n">
         <v>0.48</v>
@@ -22231,10 +23478,10 @@
         <v>292</v>
       </c>
       <c r="C17" s="1" t="n">
-        <v>26</v>
+        <v>2.3</v>
       </c>
       <c r="D17" s="1" t="n">
-        <v>31</v>
+        <v>584</v>
       </c>
       <c r="E17" s="1" t="n">
         <v>0.5</v>
@@ -22257,10 +23504,10 @@
         <v>356</v>
       </c>
       <c r="C18" s="1" t="n">
-        <v>28</v>
+        <v>2.9</v>
       </c>
       <c r="D18" s="1" t="n">
-        <v>37</v>
+        <v>712</v>
       </c>
       <c r="E18" s="1" t="n">
         <v>0.52</v>
@@ -22283,10 +23530,10 @@
         <v>435</v>
       </c>
       <c r="C19" s="1" t="n">
-        <v>29</v>
+        <v>3.6</v>
       </c>
       <c r="D19" s="1" t="n">
-        <v>45</v>
+        <v>870</v>
       </c>
       <c r="E19" s="1" t="n">
         <v>0.54</v>
@@ -22309,10 +23556,10 @@
         <v>531</v>
       </c>
       <c r="C20" s="1" t="n">
-        <v>31</v>
+        <v>4.5</v>
       </c>
       <c r="D20" s="1" t="n">
-        <v>53</v>
+        <v>1062</v>
       </c>
       <c r="E20" s="1" t="n">
         <v>0.5600000000000001</v>
@@ -22335,10 +23582,10 @@
         <v>647</v>
       </c>
       <c r="C21" s="1" t="n">
-        <v>32</v>
+        <v>5.7</v>
       </c>
       <c r="D21" s="1" t="n">
-        <v>64</v>
+        <v>1294</v>
       </c>
       <c r="E21" s="1" t="n">
         <v>0.58</v>
@@ -22361,10 +23608,10 @@
         <v>790</v>
       </c>
       <c r="C22" s="1" t="n">
-        <v>34</v>
+        <v>7.1</v>
       </c>
       <c r="D22" s="1" t="n">
-        <v>77</v>
+        <v>1580</v>
       </c>
       <c r="E22" s="1" t="n">
         <v>0.6</v>
@@ -22387,10 +23634,10 @@
         <v>963</v>
       </c>
       <c r="C23" s="1" t="n">
-        <v>35</v>
+        <v>8.9</v>
       </c>
       <c r="D23" s="1" t="n">
-        <v>92</v>
+        <v>1926</v>
       </c>
       <c r="E23" s="1" t="n">
         <v>0.62</v>
@@ -22413,10 +23660,10 @@
         <v>1175</v>
       </c>
       <c r="C24" s="1" t="n">
-        <v>36</v>
+        <v>11.1</v>
       </c>
       <c r="D24" s="1" t="n">
-        <v>111</v>
+        <v>2350</v>
       </c>
       <c r="E24" s="1" t="n">
         <v>0.64</v>
@@ -22439,10 +23686,10 @@
         <v>1434</v>
       </c>
       <c r="C25" s="1" t="n">
-        <v>38</v>
+        <v>13.9</v>
       </c>
       <c r="D25" s="1" t="n">
-        <v>133</v>
+        <v>2868</v>
       </c>
       <c r="E25" s="1" t="n">
         <v>0.66</v>
@@ -22465,10 +23712,10 @@
         <v>1749</v>
       </c>
       <c r="C26" s="1" t="n">
-        <v>39</v>
+        <v>17.3</v>
       </c>
       <c r="D26" s="1" t="n">
-        <v>160</v>
+        <v>3498</v>
       </c>
       <c r="E26" s="1" t="n">
         <v>0.68</v>
@@ -22491,10 +23738,10 @@
         <v>2134</v>
       </c>
       <c r="C27" s="1" t="n">
-        <v>41</v>
+        <v>21.7</v>
       </c>
       <c r="D27" s="1" t="n">
-        <v>192</v>
+        <v>4268</v>
       </c>
       <c r="E27" s="1" t="n">
         <v>0.7</v>
@@ -22517,10 +23764,10 @@
         <v>2604</v>
       </c>
       <c r="C28" s="1" t="n">
-        <v>42</v>
+        <v>27.1</v>
       </c>
       <c r="D28" s="1" t="n">
-        <v>230</v>
+        <v>5208</v>
       </c>
       <c r="E28" s="1" t="n">
         <v>0.72</v>
@@ -22543,10 +23790,10 @@
         <v>3177</v>
       </c>
       <c r="C29" s="1" t="n">
-        <v>44</v>
+        <v>33.9</v>
       </c>
       <c r="D29" s="1" t="n">
-        <v>276</v>
+        <v>6354</v>
       </c>
       <c r="E29" s="1" t="n">
         <v>0.74</v>
@@ -22569,10 +23816,10 @@
         <v>3876</v>
       </c>
       <c r="C30" s="1" t="n">
-        <v>45</v>
+        <v>42.4</v>
       </c>
       <c r="D30" s="1" t="n">
-        <v>331</v>
+        <v>7752</v>
       </c>
       <c r="E30" s="1" t="n">
         <v>0.76</v>
@@ -22595,10 +23842,10 @@
         <v>4728</v>
       </c>
       <c r="C31" s="1" t="n">
-        <v>47</v>
+        <v>52.9</v>
       </c>
       <c r="D31" s="1" t="n">
-        <v>397</v>
+        <v>9456</v>
       </c>
       <c r="E31" s="1" t="n">
         <v>0.78</v>
@@ -22638,12 +23885,12 @@
       </c>
       <c r="D33" s="2" t="inlineStr">
         <is>
-          <t>Sigʻim</t>
+          <t>Bufer (10 soat)</t>
         </is>
       </c>
       <c r="E33" s="2" t="inlineStr">
         <is>
-          <t>Yigʻuvchi slot</t>
+          <t>Oflayn bufer (2×)</t>
         </is>
       </c>
       <c r="F33" s="2" t="inlineStr">
@@ -22681,7 +23928,7 @@
         <v>200</v>
       </c>
       <c r="E34" s="1" t="n">
-        <v>2</v>
+        <v>400</v>
       </c>
       <c r="F34" s="1" t="n">
         <v>0</v>
@@ -22710,7 +23957,7 @@
         <v>240</v>
       </c>
       <c r="E35" s="1" t="n">
-        <v>2</v>
+        <v>480</v>
       </c>
       <c r="F35" s="1" t="n">
         <v>60</v>
@@ -22739,7 +23986,7 @@
         <v>300</v>
       </c>
       <c r="E36" s="1" t="n">
-        <v>3</v>
+        <v>600</v>
       </c>
       <c r="F36" s="1" t="n">
         <v>78</v>
@@ -22768,7 +24015,7 @@
         <v>360</v>
       </c>
       <c r="E37" s="1" t="n">
-        <v>3</v>
+        <v>720</v>
       </c>
       <c r="F37" s="1" t="n">
         <v>101</v>
@@ -22797,7 +24044,7 @@
         <v>440</v>
       </c>
       <c r="E38" s="1" t="n">
-        <v>3</v>
+        <v>880</v>
       </c>
       <c r="F38" s="1" t="n">
         <v>231</v>
@@ -22826,7 +24073,7 @@
         <v>540</v>
       </c>
       <c r="E39" s="1" t="n">
-        <v>4</v>
+        <v>1080</v>
       </c>
       <c r="F39" s="1" t="n">
         <v>300</v>
@@ -22855,7 +24102,7 @@
         <v>660</v>
       </c>
       <c r="E40" s="1" t="n">
-        <v>4</v>
+        <v>1320</v>
       </c>
       <c r="F40" s="1" t="n">
         <v>390</v>
@@ -22884,7 +24131,7 @@
         <v>800</v>
       </c>
       <c r="E41" s="1" t="n">
-        <v>4</v>
+        <v>1600</v>
       </c>
       <c r="F41" s="1" t="n">
         <v>507</v>
@@ -22913,7 +24160,7 @@
         <v>980</v>
       </c>
       <c r="E42" s="1" t="n">
-        <v>5</v>
+        <v>1960</v>
       </c>
       <c r="F42" s="1" t="n">
         <v>659</v>
@@ -22942,7 +24189,7 @@
         <v>1200</v>
       </c>
       <c r="E43" s="1" t="n">
-        <v>5</v>
+        <v>2400</v>
       </c>
       <c r="F43" s="1" t="n">
         <v>857</v>
@@ -22971,7 +24218,7 @@
         <v>1460</v>
       </c>
       <c r="E44" s="1" t="n">
-        <v>5</v>
+        <v>2920</v>
       </c>
       <c r="F44" s="1" t="n">
         <v>1591</v>
@@ -23000,7 +24247,7 @@
         <v>1780</v>
       </c>
       <c r="E45" s="1" t="n">
-        <v>6</v>
+        <v>3560</v>
       </c>
       <c r="F45" s="1" t="n">
         <v>2068</v>
@@ -23029,7 +24276,7 @@
         <v>2170</v>
       </c>
       <c r="E46" s="1" t="n">
-        <v>6</v>
+        <v>4340</v>
       </c>
       <c r="F46" s="1" t="n">
         <v>2688</v>
@@ -23058,7 +24305,7 @@
         <v>2650</v>
       </c>
       <c r="E47" s="1" t="n">
-        <v>6</v>
+        <v>5300</v>
       </c>
       <c r="F47" s="1" t="n">
         <v>3495</v>
@@ -23087,7 +24334,7 @@
         <v>3240</v>
       </c>
       <c r="E48" s="1" t="n">
-        <v>7</v>
+        <v>6480</v>
       </c>
       <c r="F48" s="1" t="n">
         <v>4543</v>
@@ -23116,7 +24363,7 @@
         <v>3950</v>
       </c>
       <c r="E49" s="1" t="n">
-        <v>7</v>
+        <v>7900</v>
       </c>
       <c r="F49" s="1" t="n">
         <v>7383</v>
@@ -23145,7 +24392,7 @@
         <v>4820</v>
       </c>
       <c r="E50" s="1" t="n">
-        <v>7</v>
+        <v>9640</v>
       </c>
       <c r="F50" s="1" t="n">
         <v>9597</v>
@@ -23174,7 +24421,7 @@
         <v>5880</v>
       </c>
       <c r="E51" s="1" t="n">
-        <v>8</v>
+        <v>11760</v>
       </c>
       <c r="F51" s="1" t="n">
         <v>12477</v>
@@ -23203,7 +24450,7 @@
         <v>7170</v>
       </c>
       <c r="E52" s="1" t="n">
-        <v>8</v>
+        <v>14340</v>
       </c>
       <c r="F52" s="1" t="n">
         <v>16220</v>
@@ -23232,7 +24479,7 @@
         <v>8750</v>
       </c>
       <c r="E53" s="1" t="n">
-        <v>8</v>
+        <v>17500</v>
       </c>
       <c r="F53" s="1" t="n">
         <v>21085</v>
@@ -23261,7 +24508,7 @@
         <v>10670</v>
       </c>
       <c r="E54" s="1" t="n">
-        <v>9</v>
+        <v>21340</v>
       </c>
       <c r="F54" s="1" t="n">
         <v>27411</v>
@@ -23290,7 +24537,7 @@
         <v>13020</v>
       </c>
       <c r="E55" s="1" t="n">
-        <v>9</v>
+        <v>26040</v>
       </c>
       <c r="F55" s="1" t="n">
         <v>35634</v>
@@ -23319,7 +24566,7 @@
         <v>15880</v>
       </c>
       <c r="E56" s="1" t="n">
-        <v>9</v>
+        <v>31760</v>
       </c>
       <c r="F56" s="1" t="n">
         <v>46325</v>
@@ -23348,7 +24595,7 @@
         <v>19380</v>
       </c>
       <c r="E57" s="1" t="n">
-        <v>10</v>
+        <v>38760</v>
       </c>
       <c r="F57" s="1" t="n">
         <v>60222</v>
@@ -23377,7 +24624,7 @@
         <v>23640</v>
       </c>
       <c r="E58" s="1" t="n">
-        <v>10</v>
+        <v>47280</v>
       </c>
       <c r="F58" s="1" t="n">
         <v>78289</v>
@@ -23432,7 +24679,7 @@
       </c>
       <c r="G60" s="2" t="inlineStr">
         <is>
-          <t>Narx: goʻsht</t>
+          <t>Narx: teri</t>
         </is>
       </c>
       <c r="H60" s="2" t="inlineStr">
@@ -23446,7 +24693,7 @@
         <v>1</v>
       </c>
       <c r="B61" s="1" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C61" s="1" t="n">
         <v>6</v>
@@ -23472,7 +24719,7 @@
         <v>2</v>
       </c>
       <c r="B62" s="1" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C62" s="1" t="n">
         <v>7</v>
@@ -23498,7 +24745,7 @@
         <v>3</v>
       </c>
       <c r="B63" s="1" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C63" s="1" t="n">
         <v>9</v>
@@ -24131,7 +25378,7 @@
       </c>
       <c r="G87" s="2" t="inlineStr">
         <is>
-          <t>Narx: goʻsht</t>
+          <t>Narx: teri</t>
         </is>
       </c>
       <c r="H87" s="2" t="inlineStr">
@@ -24145,7 +25392,7 @@
         <v>1</v>
       </c>
       <c r="B88" s="1" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C88" s="1" t="n">
         <v>6</v>
@@ -24171,7 +25418,7 @@
         <v>2</v>
       </c>
       <c r="B89" s="1" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C89" s="1" t="n">
         <v>7</v>
@@ -24197,7 +25444,7 @@
         <v>3</v>
       </c>
       <c r="B90" s="1" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C90" s="1" t="n">
         <v>9</v>
@@ -24830,7 +26077,7 @@
       </c>
       <c r="G114" s="2" t="inlineStr">
         <is>
-          <t>Narx: goʻsht</t>
+          <t>Narx: teri</t>
         </is>
       </c>
       <c r="H114" s="2" t="inlineStr">
@@ -24844,7 +26091,7 @@
         <v>1</v>
       </c>
       <c r="B115" s="1" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C115" s="1" t="n">
         <v>6</v>
@@ -24870,7 +26117,7 @@
         <v>2</v>
       </c>
       <c r="B116" s="1" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C116" s="1" t="n">
         <v>7</v>
@@ -24896,7 +26143,7 @@
         <v>3</v>
       </c>
       <c r="B117" s="1" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C117" s="1" t="n">
         <v>9</v>
@@ -25529,7 +26776,7 @@
       </c>
       <c r="G141" s="2" t="inlineStr">
         <is>
-          <t>Narx: goʻsht</t>
+          <t>Narx: teri</t>
         </is>
       </c>
       <c r="H141" s="2" t="inlineStr">
@@ -25543,7 +26790,7 @@
         <v>1</v>
       </c>
       <c r="B142" s="1" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C142" s="1" t="n">
         <v>6</v>
@@ -25569,7 +26816,7 @@
         <v>2</v>
       </c>
       <c r="B143" s="1" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C143" s="1" t="n">
         <v>7</v>
@@ -25595,7 +26842,7 @@
         <v>3</v>
       </c>
       <c r="B144" s="1" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C144" s="1" t="n">
         <v>9</v>
@@ -26218,7 +27465,7 @@
       </c>
       <c r="E168" s="2" t="inlineStr">
         <is>
-          <t>Narx: goʻsht</t>
+          <t>Narx: teri</t>
         </is>
       </c>
       <c r="F168" s="2" t="inlineStr">
@@ -27443,7 +28690,7 @@
     <row r="223">
       <c r="A223" s="1" t="inlineStr">
         <is>
-          <t>Ustaxona soatlik ishlab chiqarishini oʻyinchi 4 ta resurs orasida oʻzi taqsimlaydi; sigʻim toʻlsa ishlab chiqarish toʻxtaydi.</t>
+          <t>Ustaxona soatlik ishlab chiqarishini oʻyinchi 4 ta resurs orasida oʻzi taqsimlaydi. Ishlab chiqarish avval Ustaxona buferiga tushadi va “Yigʻib olish” bilan omborga oʻtadi; bufer toʻlsa ishlab chiqarish toʻxtaydi. Qurilish resurslari ombori cheklanmagan. Goʻsht bino narxiga kirmaydi.</t>
         </is>
       </c>
     </row>
@@ -27490,7 +28737,7 @@
     <row r="4">
       <c r="A4" s="1" t="inlineStr">
         <is>
-          <t>Har bir ustun boshqa varaqlardagi formulalardan avtomatik keladi. Sozlamalarni oʻzgartirsangiz, shu jadval ham oʻzgaradi.</t>
+          <t>Boshqa varaqlardan yigʻilgan qiymatlar. Faylda Excel formulalari yoʻq: sozlamani oʻzgartirgach qiymatlarni tools/blue_wolf_config.py tekshiruvi bilan solishtiring.</t>
         </is>
       </c>
     </row>
@@ -27562,7 +28809,7 @@
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>Yigʻuvchi slot</t>
+          <t>Kunlik ov (4 ov, kg)</t>
         </is>
       </c>
       <c r="O5" s="2" t="inlineStr">
@@ -27661,7 +28908,7 @@
         <v>1</v>
       </c>
       <c r="N6" s="1" t="n">
-        <v>2</v>
+        <v>12</v>
       </c>
       <c r="O6" s="1" t="inlineStr">
         <is>
@@ -27670,7 +28917,7 @@
       </c>
       <c r="P6" s="1" t="inlineStr">
         <is>
-          <t>Yolgʻiz ov: kemiruvchi va qush; birinchi in</t>
+          <t>Yolgʻiz ov (alfa): kemiruvchi va qush; In</t>
         </is>
       </c>
       <c r="Q6" s="1" t="n">
@@ -27689,7 +28936,7 @@
         <v>1</v>
       </c>
       <c r="V6" s="1" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="W6" s="1" t="n">
         <v>63</v>
@@ -27743,7 +28990,7 @@
         <v>1</v>
       </c>
       <c r="N7" s="1" t="n">
-        <v>2</v>
+        <v>14</v>
       </c>
       <c r="O7" s="1" t="inlineStr">
         <is>
@@ -27752,7 +28999,7 @@
       </c>
       <c r="P7" s="1" t="inlineStr">
         <is>
-          <t>Oziq gʻori va Ustaxona qoyasi ochiladi</t>
+          <t>Oziq gʻori va Ustaxona qoyasi</t>
         </is>
       </c>
       <c r="Q7" s="1" t="n">
@@ -27771,7 +29018,7 @@
         <v>1</v>
       </c>
       <c r="V7" s="1" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="W7" s="1" t="n">
         <v>65</v>
@@ -27825,7 +29072,7 @@
         <v>1</v>
       </c>
       <c r="N8" s="1" t="n">
-        <v>2</v>
+        <v>16</v>
       </c>
       <c r="O8" s="1" t="inlineStr">
         <is>
@@ -27834,7 +29081,7 @@
       </c>
       <c r="P8" s="1" t="inlineStr">
         <is>
-          <t>Yolgʻiz bosqichning soʻnggi darajasi; toʻdaga tayyorgarlik</t>
+          <t>Ov soʻqmogʻi, birinchi ovchi, quyon ovi</t>
         </is>
       </c>
       <c r="Q8" s="1" t="n">
@@ -27853,7 +29100,7 @@
         <v>1</v>
       </c>
       <c r="V8" s="1" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="W8" s="1" t="n">
         <v>66</v>
@@ -27907,7 +29154,7 @@
         <v>1</v>
       </c>
       <c r="N9" s="1" t="n">
-        <v>2</v>
+        <v>36</v>
       </c>
       <c r="O9" s="1" t="inlineStr">
         <is>
@@ -27916,7 +29163,7 @@
       </c>
       <c r="P9" s="1" t="inlineStr">
         <is>
-          <t>🔓 TOʻDA OCHILADI: toʻda bilan ov · toʻda (klan) yaratish yoki qoʻshilish · PvP arena · toʻda janglari</t>
+          <t>🔓 TOʻDA: qoʻshin 10 askar · Jang maydoni, Razvedka qoyasi, Himoya devori · yovvoyi toʻdalarga (bot) hujum · ov guruhi · klan va lager (v2)</t>
         </is>
       </c>
       <c r="Q9" s="1" t="n">
@@ -27989,7 +29236,7 @@
         <v>1</v>
       </c>
       <c r="N10" s="1" t="n">
-        <v>2</v>
+        <v>40</v>
       </c>
       <c r="O10" s="1" t="inlineStr">
         <is>
@@ -27998,7 +29245,7 @@
       </c>
       <c r="P10" s="1" t="inlineStr">
         <is>
-          <t>Toʻda ovi: yirik oʻlja · toʻda umumiy ombori</t>
+          <t>Yirik oʻlja — jayron (kamida 2 boʻri)</t>
         </is>
       </c>
       <c r="Q10" s="1" t="n">
@@ -28071,7 +29318,7 @@
         <v>1</v>
       </c>
       <c r="N11" s="1" t="n">
-        <v>2</v>
+        <v>44</v>
       </c>
       <c r="O11" s="1" t="inlineStr">
         <is>
@@ -28080,7 +29327,7 @@
       </c>
       <c r="P11" s="1" t="inlineStr">
         <is>
-          <t>Toʻda reydi: raqib omboriga hujum</t>
+          <t>🏥 Shifo gʻori · suv oazisi (v2)</t>
         </is>
       </c>
       <c r="Q11" s="1" t="n">
@@ -28153,7 +29400,7 @@
         <v>1</v>
       </c>
       <c r="N12" s="1" t="n">
-        <v>2</v>
+        <v>72</v>
       </c>
       <c r="O12" s="1" t="inlineStr">
         <is>
@@ -28162,7 +29409,7 @@
       </c>
       <c r="P12" s="1" t="inlineStr">
         <is>
-          <t>PvP reytingi va liga tizimi</t>
+          <t>🔓 Haqiqiy oʻyinchilarga hujum (qalqon tugaydi) · reyting va liga (v2)</t>
         </is>
       </c>
       <c r="Q12" s="1" t="n">
@@ -28235,7 +29482,7 @@
         <v>1</v>
       </c>
       <c r="N13" s="1" t="n">
-        <v>2</v>
+        <v>78</v>
       </c>
       <c r="O13" s="1" t="inlineStr">
         <is>
@@ -28244,7 +29491,7 @@
       </c>
       <c r="P13" s="1" t="inlineStr">
         <is>
-          <t>Toʻda urushi: toʻda vs toʻda sessiyasi</t>
+          <t>Toʻda urushi (v2) · oʻt oazisi (v2)</t>
         </is>
       </c>
       <c r="Q13" s="1" t="n">
@@ -28317,7 +29564,7 @@
         <v>1</v>
       </c>
       <c r="N14" s="1" t="n">
-        <v>2</v>
+        <v>112</v>
       </c>
       <c r="O14" s="1" t="inlineStr">
         <is>
@@ -28326,7 +29573,7 @@
       </c>
       <c r="P14" s="1" t="inlineStr">
         <is>
-          <t>Toʻda lavozimlari: alfa, beta, ovchi, qorovul</t>
+          <t>🛒 Bozor · toʻda lavozimlari (v2)</t>
         </is>
       </c>
       <c r="Q14" s="1" t="n">
@@ -28399,7 +29646,7 @@
         <v>1</v>
       </c>
       <c r="N15" s="1" t="n">
-        <v>2</v>
+        <v>150</v>
       </c>
       <c r="O15" s="1" t="inlineStr">
         <is>
@@ -28408,7 +29655,7 @@
       </c>
       <c r="P15" s="1" t="inlineStr">
         <is>
-          <t>Hudud egallash: dasht zonasi toʻda nomiga yoziladi</t>
+          <t>Ikkinchi qurilish navbati — hammaga bepul</t>
         </is>
       </c>
       <c r="Q15" s="1" t="n">
@@ -28481,7 +29728,7 @@
         <v>1</v>
       </c>
       <c r="N16" s="1" t="n">
-        <v>2</v>
+        <v>160</v>
       </c>
       <c r="O16" s="1" t="inlineStr">
         <is>
@@ -28490,7 +29737,7 @@
       </c>
       <c r="P16" s="1" t="inlineStr">
         <is>
-          <t>Toʻda birgalikda ovi (co-op boss: togʻ ayigʻi)</t>
+          <t>Co-op boss: togʻ ayigʻi (v3)</t>
         </is>
       </c>
       <c r="Q16" s="1" t="n">
@@ -28563,7 +29810,7 @@
         <v>1</v>
       </c>
       <c r="N17" s="1" t="n">
-        <v>2</v>
+        <v>204</v>
       </c>
       <c r="O17" s="1" t="inlineStr">
         <is>
@@ -28572,7 +29819,7 @@
       </c>
       <c r="P17" s="1" t="inlineStr">
         <is>
-          <t>Toʻda xazinasi va aʼzolarga ulush taqsimoti</t>
+          <t>Toʻda xazinasi (v2) · tosh koni (v2)</t>
         </is>
       </c>
       <c r="Q17" s="1" t="n">
@@ -28645,7 +29892,7 @@
         <v>1</v>
       </c>
       <c r="N18" s="1" t="n">
-        <v>2</v>
+        <v>288</v>
       </c>
       <c r="O18" s="1" t="inlineStr">
         <is>
@@ -28654,7 +29901,7 @@
       </c>
       <c r="P18" s="1" t="inlineStr">
         <is>
-          <t>Himoya urushi: inni toʻda bilan qoʻriqlash</t>
+          <t>Himoya urushi (v3)</t>
         </is>
       </c>
       <c r="Q18" s="1" t="n">
@@ -28727,7 +29974,7 @@
         <v>1</v>
       </c>
       <c r="N19" s="1" t="n">
-        <v>2</v>
+        <v>342</v>
       </c>
       <c r="O19" s="1" t="inlineStr">
         <is>
@@ -28736,7 +29983,7 @@
       </c>
       <c r="P19" s="1" t="inlineStr">
         <is>
-          <t>Mavsumiy PvP turniri (haftalik)</t>
+          <t>Haftalik turnir (v3)</t>
         </is>
       </c>
       <c r="Q19" s="1" t="n">
@@ -28809,7 +30056,7 @@
         <v>3</v>
       </c>
       <c r="N20" s="1" t="n">
-        <v>3</v>
+        <v>440</v>
       </c>
       <c r="O20" s="1" t="inlineStr">
         <is>
@@ -28818,7 +30065,7 @@
       </c>
       <c r="P20" s="1" t="inlineStr">
         <is>
-          <t>Toʻda taktikasi: qurshab olish, chekinish, tuzoq</t>
+          <t>Toʻda taktikasi (v3)</t>
         </is>
       </c>
       <c r="Q20" s="1" t="n">
@@ -28891,7 +30138,7 @@
         <v>5</v>
       </c>
       <c r="N21" s="1" t="n">
-        <v>3</v>
+        <v>546</v>
       </c>
       <c r="O21" s="1" t="inlineStr">
         <is>
@@ -28900,7 +30147,7 @@
       </c>
       <c r="P21" s="1" t="inlineStr">
         <is>
-          <t>Katta toʻda urushi: 20v20 xarita jangi</t>
+          <t>Suyak dalasi (v2) · 20v20 urush (v3)</t>
         </is>
       </c>
       <c r="Q21" s="1" t="n">
@@ -28973,7 +30220,7 @@
         <v>6</v>
       </c>
       <c r="N22" s="1" t="n">
-        <v>4</v>
+        <v>704</v>
       </c>
       <c r="O22" s="1" t="inlineStr">
         <is>
@@ -28982,7 +30229,7 @@
       </c>
       <c r="P22" s="1" t="inlineStr">
         <is>
-          <t>Toʻdalar ittifoqi (2–3 toʻda birlashuvi)</t>
+          <t>Toʻdalar ittifoqi (v3)</t>
         </is>
       </c>
       <c r="Q22" s="1" t="n">
@@ -29055,7 +30302,7 @@
         <v>7</v>
       </c>
       <c r="N23" s="1" t="n">
-        <v>4</v>
+        <v>874</v>
       </c>
       <c r="O23" s="1" t="inlineStr">
         <is>
@@ -29064,7 +30311,7 @@
       </c>
       <c r="P23" s="1" t="inlineStr">
         <is>
-          <t>Elite reyd: raqib hududini bosib olish</t>
+          <t>Elite reyd (v3)</t>
         </is>
       </c>
       <c r="Q23" s="1" t="n">
@@ -29137,7 +30384,7 @@
         <v>9</v>
       </c>
       <c r="N24" s="1" t="n">
-        <v>5</v>
+        <v>1104</v>
       </c>
       <c r="O24" s="1" t="inlineStr">
         <is>
@@ -29146,7 +30393,7 @@
       </c>
       <c r="P24" s="1" t="inlineStr">
         <is>
-          <t>Alfa unvoni: server reytingi va toʻda darajasi</t>
+          <t>Alfa unvoni, server reytingi (v2)</t>
         </is>
       </c>
       <c r="Q24" s="1" t="n">
@@ -29219,7 +30466,7 @@
         <v>10</v>
       </c>
       <c r="N25" s="1" t="n">
-        <v>5</v>
+        <v>1400</v>
       </c>
       <c r="O25" s="1" t="inlineStr">
         <is>
@@ -29228,7 +30475,7 @@
       </c>
       <c r="P25" s="1" t="inlineStr">
         <is>
-          <t>Muz davri zonasi · qadimgi toʻda janglari</t>
+          <t>🌙 Oy nuri ehtiyoji va passivi · Oy mehrobi (v2) · muz davri zonasi (v3)</t>
         </is>
       </c>
       <c r="Q25" s="1" t="n">
@@ -29301,7 +30548,7 @@
         <v>11</v>
       </c>
       <c r="N26" s="1" t="n">
-        <v>5</v>
+        <v>1716</v>
       </c>
       <c r="O26" s="1" t="inlineStr">
         <is>
@@ -29310,7 +30557,7 @@
       </c>
       <c r="P26" s="1" t="inlineStr">
         <is>
-          <t>Afsona darvozasi: toʻda bilan boss jangi</t>
+          <t>Afsona bossi (v3)</t>
         </is>
       </c>
       <c r="Q26" s="1" t="n">
@@ -29383,7 +30630,7 @@
         <v>14</v>
       </c>
       <c r="N27" s="1" t="n">
-        <v>6</v>
+        <v>2160</v>
       </c>
       <c r="O27" s="1" t="inlineStr">
         <is>
@@ -29392,7 +30639,7 @@
       </c>
       <c r="P27" s="1" t="inlineStr">
         <is>
-          <t>Tungi reyd: toʻda hujumi kuchi x2</t>
+          <t>Tungi reyd: 22:00–06:00 yurish tezligi +25%</t>
         </is>
       </c>
       <c r="Q27" s="1" t="n">
@@ -29465,7 +30712,7 @@
         <v>15</v>
       </c>
       <c r="N28" s="1" t="n">
-        <v>7</v>
+        <v>2688</v>
       </c>
       <c r="O28" s="1" t="inlineStr">
         <is>
@@ -29474,7 +30721,7 @@
       </c>
       <c r="P28" s="1" t="inlineStr">
         <is>
-          <t>Juft hujum: ikki toʻda bir vaqtda urishadi</t>
+          <t>Juft hujum (v3)</t>
         </is>
       </c>
       <c r="Q28" s="1" t="n">
@@ -29547,7 +30794,7 @@
         <v>17</v>
       </c>
       <c r="N29" s="1" t="n">
-        <v>7</v>
+        <v>3306</v>
       </c>
       <c r="O29" s="1" t="inlineStr">
         <is>
@@ -29556,7 +30803,7 @@
       </c>
       <c r="P29" s="1" t="inlineStr">
         <is>
-          <t>Zanjirni uzish: urushda toʻliq tiklanish</t>
+          <t>Zanjirni uzish: urushdan keyin jarohatlanganlar 2× tez davolanadi</t>
         </is>
       </c>
       <c r="Q29" s="1" t="n">
@@ -29629,7 +30876,7 @@
         <v>18</v>
       </c>
       <c r="N30" s="1" t="n">
-        <v>8</v>
+        <v>4140</v>
       </c>
       <c r="O30" s="1" t="inlineStr">
         <is>
@@ -29638,7 +30885,7 @@
       </c>
       <c r="P30" s="1" t="inlineStr">
         <is>
-          <t>Yakuniy daraja: butun ittifoqqa +10% doimiy bonus</t>
+          <t>Koʻk Boʻri unvoni · klanga +10% ishlab chiqarish (kuch emas)</t>
         </is>
       </c>
       <c r="Q30" s="1" t="n">
@@ -29779,7 +31026,7 @@
       </c>
       <c r="H6" s="1" t="inlineStr">
         <is>
-          <t>Ish unumi (kg/soat)</t>
+          <t>Ish unumi</t>
         </is>
       </c>
       <c r="I6" s="1" t="inlineStr">
@@ -29907,7 +31154,7 @@
       </c>
       <c r="B10" s="1" t="inlineStr">
         <is>
-          <t>Goʻsht va resurs yigʻish</t>
+          <t>Ov: goʻsht va shifobaxsh oʻt</t>
         </is>
       </c>
       <c r="C10" s="1" t="inlineStr">
@@ -29929,11 +31176,13 @@
       <c r="G10" s="1" t="n">
         <v>40</v>
       </c>
-      <c r="H10" s="1" t="n">
-        <v>12</v>
+      <c r="H10" s="1" t="inlineStr">
+        <is>
+          <t>5 × kunlik ehtiyoj kg/soat</t>
+        </is>
       </c>
       <c r="I10" s="1" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="11">
@@ -29971,17 +31220,17 @@
       </c>
       <c r="F12" s="1" t="inlineStr">
         <is>
-          <t>Mashq: goʻsht</t>
+          <t>Yangi askar: goʻsht</t>
         </is>
       </c>
       <c r="G12" s="1" t="inlineStr">
         <is>
-          <t>Mashq: suyak</t>
+          <t>Yangi askar: suyak</t>
         </is>
       </c>
       <c r="H12" s="1" t="inlineStr">
         <is>
-          <t>Mashq vaqti (soat)</t>
+          <t>Yangi askar: vaqt (daq)</t>
         </is>
       </c>
     </row>
@@ -29995,22 +31244,22 @@
         </is>
       </c>
       <c r="C13" s="1" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="D13" s="1" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="E13" s="1" t="n">
         <v>1</v>
       </c>
       <c r="F13" s="1" t="n">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="G13" s="1" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="H13" s="1" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
     </row>
     <row r="14">
@@ -30032,13 +31281,13 @@
         <v>1.45</v>
       </c>
       <c r="F14" s="1" t="n">
-        <v>200</v>
+        <v>42</v>
       </c>
       <c r="G14" s="1" t="n">
-        <v>80</v>
+        <v>17</v>
       </c>
       <c r="H14" s="1" t="n">
-        <v>2</v>
+        <v>5.8</v>
       </c>
     </row>
     <row r="15">
@@ -30060,13 +31309,13 @@
         <v>2.1025</v>
       </c>
       <c r="F15" s="1" t="n">
-        <v>440</v>
+        <v>89</v>
       </c>
       <c r="G15" s="1" t="n">
-        <v>176</v>
+        <v>35</v>
       </c>
       <c r="H15" s="1" t="n">
-        <v>4.4</v>
+        <v>8.4</v>
       </c>
     </row>
     <row r="16">
@@ -30088,13 +31337,13 @@
         <v>3.048625</v>
       </c>
       <c r="F16" s="1" t="n">
-        <v>968</v>
+        <v>187</v>
       </c>
       <c r="G16" s="1" t="n">
-        <v>387</v>
+        <v>75</v>
       </c>
       <c r="H16" s="1" t="n">
-        <v>9.699999999999999</v>
+        <v>12.2</v>
       </c>
     </row>
     <row r="17">
@@ -30116,13 +31365,13 @@
         <v>4.42050625</v>
       </c>
       <c r="F17" s="1" t="n">
-        <v>2130</v>
+        <v>393</v>
       </c>
       <c r="G17" s="1" t="n">
-        <v>852</v>
+        <v>157</v>
       </c>
       <c r="H17" s="1" t="n">
-        <v>21.3</v>
+        <v>17.8</v>
       </c>
     </row>
     <row r="18">
@@ -30144,13 +31393,13 @@
         <v>6.4097340625</v>
       </c>
       <c r="F18" s="1" t="n">
-        <v>4685</v>
+        <v>824</v>
       </c>
       <c r="G18" s="1" t="n">
-        <v>1874</v>
+        <v>330</v>
       </c>
       <c r="H18" s="1" t="n">
-        <v>46.9</v>
+        <v>25.7</v>
       </c>
     </row>
     <row r="19">
@@ -30458,14 +31707,14 @@
     <row r="36">
       <c r="A36" s="1" t="inlineStr">
         <is>
-          <t>Maks tier = MIN(alfa darajasi ÷ 4 ; SHU ROL binosi darajasi ÷ 4 ; 6). Binolar 25 darajagacha, lekin oʻyinchi darajasidan oshmaydi.</t>
+          <t>Maks tier = MAX(1; MIN(alfa darajasi ÷ 4 ; SHU ROL binosi darajasi ÷ 4 ; 6)). 1-tier rol binosi qurilgan zahoti ochiq. Binolar 25 darajagacha, lekin oʻyinchi darajasidan oshmaydi.</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" s="1" t="inlineStr">
         <is>
-          <t>Ovchi 1-darajadanoq mavjud (yolgʻiz bosqich), qolgan 3 rol toʻda ochilganda — 4-darajada keladi.</t>
+          <t>Ovchi 3-darajadan (Ov soʻqmogʻi bilan), qolgan 3 rol 4-darajada keladi. 1–3 darajada alfa oʻzi yolgʻiz ovlaydi.</t>
         </is>
       </c>
     </row>
@@ -32361,7 +33610,7 @@
       </c>
       <c r="F32" s="1" t="inlineStr">
         <is>
-          <t>Toʻliq — hujum qilib boʻlmaydi</t>
+          <t>Toʻliq — faqat botlarga hujum qila oladi (4–6 daraja)</t>
         </is>
       </c>
     </row>
@@ -32537,7 +33786,7 @@
       </c>
       <c r="F36" s="1" t="inlineStr">
         <is>
-          <t>Oʻlmaydi — 30% jarohatlanadi, 1–3 soat davolanadi</t>
+          <t>Jangda oʻladi yoki jarohatlanadi (bo'lim 7 formulasi); oʻljaga aylanmaydi</t>
         </is>
       </c>
     </row>
@@ -32563,7 +33812,7 @@
       </c>
       <c r="F37" s="1" t="inlineStr">
         <is>
-          <t>Oy toshi, XP, binolar, boʻrilar</t>
+          <t>Oy toshi, XP, binolar, qurilish resurslari, boʻrilar (faqat goʻsht olinadi)</t>
         </is>
       </c>
       <c r="G37" s="1" t="inlineStr"/>
@@ -32729,17 +33978,11 @@
     <row r="47">
       <c r="A47" s="1" t="inlineStr">
         <is>
-          <t>Oʻlja = Ombordagi zaxira × (1 − Himoya%) × Reyd koeffitsienti × gʻalaba × daraja koeff. × takror koeff., lekin yuk sigʻimidan oshmaydi.</t>
-        </is>
-      </c>
-      <c r="B47" s="1" t="n">
-        <v>0.1</v>
-      </c>
-      <c r="C47" s="1" t="inlineStr">
-        <is>
-          <t>Takror talashga qarshi</t>
-        </is>
-      </c>
+          <t>Oʻlja = Ombordagi goʻsht × (1 − Himoya%) × Reyd koeffitsienti × gʻalaba × daraja koeff. × takror koeff. × oflayn koeff. (himoyachi 24+ soat oflayn — 0.5), lekin yuk sigʻimidan oshmaydi. 4-hujum juftlik chegarasi bilan taqiqlangan.</t>
+        </is>
+      </c>
+      <c r="B47" s="1" t="n"/>
+      <c r="C47" s="1" t="n"/>
     </row>
     <row r="48">
       <c r="A48" s="1" t="inlineStr">
@@ -32773,7 +34016,7 @@
     <row r="51">
       <c r="A51" s="1" t="inlineStr">
         <is>
-          <t>1–6 daraja qalqon ostida: ularga hujum qilib boʻlmaydi, shuning uchun 7-darajali oʻyinchining tanlovi faqat 7 va 8 — oyna tabiiy ravishda torroq.</t>
+          <t>1–6 daraja qalqon ostida: 4–6 darajada roʻyxat faqat botlardan iborat. 7-darajali oʻyinchining haqiqiy raqiblari faqat 7 va 8 — boʻsh joylar botlar bilan toʻldiriladi.</t>
         </is>
       </c>
     </row>
@@ -34508,7 +35751,7 @@
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>Lager ulushi</t>
+          <t>Lager ulushi (60% tavan)</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -34931,23 +36174,23 @@
         <v>2</v>
       </c>
       <c r="F16" s="1" t="n">
-        <v>289</v>
+        <v>263</v>
       </c>
       <c r="G16" s="1" t="n">
-        <v>2312</v>
+        <v>2104</v>
       </c>
       <c r="H16" s="1" t="n">
         <v>3506</v>
       </c>
       <c r="I16" s="1" t="n">
-        <v>0.659440958357102</v>
+        <v>0.6</v>
       </c>
       <c r="J16" s="1" t="n">
         <v>7</v>
       </c>
       <c r="K16" s="1" t="inlineStr">
         <is>
-          <t>⚠️ Lager juda foydali — in boʻshab qoladi</t>
+          <t>Tavan: xom ulush 66% → 60%</t>
         </is>
       </c>
     </row>
@@ -34970,23 +36213,23 @@
         <v>3</v>
       </c>
       <c r="F17" s="1" t="n">
-        <v>451</v>
+        <v>321</v>
       </c>
       <c r="G17" s="1" t="n">
-        <v>3608</v>
+        <v>2568</v>
       </c>
       <c r="H17" s="1" t="n">
         <v>4278</v>
       </c>
       <c r="I17" s="1" t="n">
-        <v>0.843384759233287</v>
+        <v>0.6</v>
       </c>
       <c r="J17" s="1" t="n">
         <v>9</v>
       </c>
       <c r="K17" s="1" t="inlineStr">
         <is>
-          <t>⚠️ Lager juda foydali — in boʻshab qoladi</t>
+          <t>Tavan: xom ulush 84% → 60%</t>
         </is>
       </c>
     </row>
@@ -35009,23 +36252,23 @@
         <v>3</v>
       </c>
       <c r="F18" s="1" t="n">
-        <v>650</v>
+        <v>391</v>
       </c>
       <c r="G18" s="1" t="n">
-        <v>5200</v>
+        <v>3128</v>
       </c>
       <c r="H18" s="1" t="n">
         <v>5219</v>
       </c>
       <c r="I18" s="1" t="n">
-        <v>0.996359455834451</v>
+        <v>0.6</v>
       </c>
       <c r="J18" s="1" t="n">
         <v>10</v>
       </c>
       <c r="K18" s="1" t="inlineStr">
         <is>
-          <t>⚠️ Lager juda foydali — in boʻshab qoladi</t>
+          <t>Tavan: xom ulush 100% → 60%</t>
         </is>
       </c>
     </row>
@@ -35048,23 +36291,23 @@
         <v>3</v>
       </c>
       <c r="F19" s="1" t="n">
-        <v>946</v>
+        <v>478</v>
       </c>
       <c r="G19" s="1" t="n">
-        <v>7568</v>
+        <v>3824</v>
       </c>
       <c r="H19" s="1" t="n">
         <v>6367</v>
       </c>
       <c r="I19" s="1" t="n">
-        <v>1.18862886759856</v>
+        <v>0.6</v>
       </c>
       <c r="J19" s="1" t="n">
         <v>12</v>
       </c>
       <c r="K19" s="1" t="inlineStr">
         <is>
-          <t>⚠️ Lager juda foydali — in boʻshab qoladi</t>
+          <t>Tavan: xom ulush 119% → 60%</t>
         </is>
       </c>
     </row>
@@ -35087,23 +36330,23 @@
         <v>3</v>
       </c>
       <c r="F20" s="1" t="n">
-        <v>1377</v>
+        <v>583</v>
       </c>
       <c r="G20" s="1" t="n">
-        <v>11016</v>
+        <v>4664</v>
       </c>
       <c r="H20" s="1" t="n">
         <v>7767</v>
       </c>
       <c r="I20" s="1" t="n">
-        <v>1.41830822711472</v>
+        <v>0.6</v>
       </c>
       <c r="J20" s="1" t="n">
         <v>15</v>
       </c>
       <c r="K20" s="1" t="inlineStr">
         <is>
-          <t>⚠️ Lager juda foydali — in boʻshab qoladi</t>
+          <t>Tavan: xom ulush 142% → 60%</t>
         </is>
       </c>
     </row>
@@ -35126,23 +36369,23 @@
         <v>4</v>
       </c>
       <c r="F21" s="1" t="n">
-        <v>2132</v>
+        <v>711</v>
       </c>
       <c r="G21" s="1" t="n">
-        <v>17056</v>
+        <v>5688</v>
       </c>
       <c r="H21" s="1" t="n">
         <v>9476</v>
       </c>
       <c r="I21" s="1" t="n">
-        <v>1.79991557619249</v>
+        <v>0.6</v>
       </c>
       <c r="J21" s="1" t="n">
         <v>18</v>
       </c>
       <c r="K21" s="1" t="inlineStr">
         <is>
-          <t>⚠️ Lager juda foydali — in boʻshab qoladi</t>
+          <t>Tavan: xom ulush 180% → 60%</t>
         </is>
       </c>
     </row>
@@ -35165,23 +36408,23 @@
         <v>4</v>
       </c>
       <c r="F22" s="1" t="n">
-        <v>3121</v>
+        <v>867</v>
       </c>
       <c r="G22" s="1" t="n">
-        <v>24968</v>
+        <v>6936</v>
       </c>
       <c r="H22" s="1" t="n">
         <v>11561</v>
       </c>
       <c r="I22" s="1" t="n">
-        <v>2.15967476861863</v>
+        <v>0.6</v>
       </c>
       <c r="J22" s="1" t="n">
         <v>21</v>
       </c>
       <c r="K22" s="1" t="inlineStr">
         <is>
-          <t>⚠️ Lager juda foydali — in boʻshab qoladi</t>
+          <t>Tavan: xom ulush 216% → 60%</t>
         </is>
       </c>
     </row>
@@ -35204,23 +36447,23 @@
         <v>4</v>
       </c>
       <c r="F23" s="1" t="n">
-        <v>4513</v>
+        <v>1058</v>
       </c>
       <c r="G23" s="1" t="n">
-        <v>36104</v>
+        <v>8464</v>
       </c>
       <c r="H23" s="1" t="n">
         <v>14105</v>
       </c>
       <c r="I23" s="1" t="n">
-        <v>2.55965969514357</v>
+        <v>0.6</v>
       </c>
       <c r="J23" s="1" t="n">
         <v>26</v>
       </c>
       <c r="K23" s="1" t="inlineStr">
         <is>
-          <t>⚠️ Lager juda foydali — in boʻshab qoladi</t>
+          <t>Tavan: xom ulush 256% → 60%</t>
         </is>
       </c>
     </row>
@@ -35243,23 +36486,23 @@
         <v>4</v>
       </c>
       <c r="F24" s="1" t="n">
-        <v>6625</v>
+        <v>1291</v>
       </c>
       <c r="G24" s="1" t="n">
-        <v>53000</v>
+        <v>10328</v>
       </c>
       <c r="H24" s="1" t="n">
         <v>17208</v>
       </c>
       <c r="I24" s="1" t="n">
-        <v>3.07996280799628</v>
+        <v>0.6</v>
       </c>
       <c r="J24" s="1" t="n">
         <v>31</v>
       </c>
       <c r="K24" s="1" t="inlineStr">
         <is>
-          <t>⚠️ Lager juda foydali — in boʻshab qoladi</t>
+          <t>Tavan: xom ulush 308% → 60%</t>
         </is>
       </c>
     </row>
@@ -35282,23 +36525,23 @@
         <v>5</v>
       </c>
       <c r="F25" s="1" t="n">
-        <v>10169</v>
+        <v>1574</v>
       </c>
       <c r="G25" s="1" t="n">
-        <v>81352</v>
+        <v>12592</v>
       </c>
       <c r="H25" s="1" t="n">
         <v>20993</v>
       </c>
       <c r="I25" s="1" t="n">
-        <v>3.87519649406945</v>
+        <v>0.6</v>
       </c>
       <c r="J25" s="1" t="n">
         <v>37</v>
       </c>
       <c r="K25" s="1" t="inlineStr">
         <is>
-          <t>⚠️ Lager juda foydali — in boʻshab qoladi</t>
+          <t>Tavan: xom ulush 388% → 60%</t>
         </is>
       </c>
     </row>
@@ -35321,23 +36564,23 @@
         <v>5</v>
       </c>
       <c r="F26" s="1" t="n">
-        <v>14807</v>
+        <v>1921</v>
       </c>
       <c r="G26" s="1" t="n">
-        <v>118456</v>
+        <v>15368</v>
       </c>
       <c r="H26" s="1" t="n">
         <v>25612</v>
       </c>
       <c r="I26" s="1" t="n">
-        <v>4.62501952209902</v>
+        <v>0.6</v>
       </c>
       <c r="J26" s="1" t="n">
         <v>44</v>
       </c>
       <c r="K26" s="1" t="inlineStr">
         <is>
-          <t>⚠️ Lager juda foydali — in boʻshab qoladi</t>
+          <t>Tavan: xom ulush 463% → 60%</t>
         </is>
       </c>
     </row>
@@ -35360,23 +36603,23 @@
         <v>5</v>
       </c>
       <c r="F27" s="1" t="n">
-        <v>21645</v>
+        <v>2343</v>
       </c>
       <c r="G27" s="1" t="n">
-        <v>173160</v>
+        <v>18744</v>
       </c>
       <c r="H27" s="1" t="n">
         <v>31246</v>
       </c>
       <c r="I27" s="1" t="n">
-        <v>5.54182935415733</v>
+        <v>0.6</v>
       </c>
       <c r="J27" s="1" t="n">
         <v>53</v>
       </c>
       <c r="K27" s="1" t="inlineStr">
         <is>
-          <t>⚠️ Lager juda foydali — in boʻshab qoladi</t>
+          <t>Tavan: xom ulush 554% → 60%</t>
         </is>
       </c>
     </row>
@@ -35399,23 +36642,23 @@
         <v>5</v>
       </c>
       <c r="F28" s="1" t="n">
-        <v>31767</v>
+        <v>2859</v>
       </c>
       <c r="G28" s="1" t="n">
-        <v>254136</v>
+        <v>22872</v>
       </c>
       <c r="H28" s="1" t="n">
         <v>38120</v>
       </c>
       <c r="I28" s="1" t="n">
-        <v>6.66673662119622</v>
+        <v>0.6</v>
       </c>
       <c r="J28" s="1" t="n">
         <v>64</v>
       </c>
       <c r="K28" s="1" t="inlineStr">
         <is>
-          <t>⚠️ Lager juda foydali — in boʻshab qoladi</t>
+          <t>Tavan: xom ulush 667% → 60%</t>
         </is>
       </c>
     </row>
@@ -35438,23 +36681,23 @@
         <v>6</v>
       </c>
       <c r="F29" s="1" t="n">
-        <v>48367</v>
+        <v>3488</v>
       </c>
       <c r="G29" s="1" t="n">
-        <v>386936</v>
+        <v>27904</v>
       </c>
       <c r="H29" s="1" t="n">
         <v>46507</v>
       </c>
       <c r="I29" s="1" t="n">
-        <v>8.319951835207601</v>
+        <v>0.6</v>
       </c>
       <c r="J29" s="1" t="n">
         <v>77</v>
       </c>
       <c r="K29" s="1" t="inlineStr">
         <is>
-          <t>⚠️ Lager juda foydali — in boʻshab qoladi</t>
+          <t>Tavan: xom ulush 832% → 60%</t>
         </is>
       </c>
     </row>
@@ -35477,23 +36720,23 @@
         <v>6</v>
       </c>
       <c r="F30" s="1" t="n">
-        <v>70687</v>
+        <v>4255</v>
       </c>
       <c r="G30" s="1" t="n">
-        <v>565496</v>
+        <v>34040</v>
       </c>
       <c r="H30" s="1" t="n">
         <v>56738</v>
       </c>
       <c r="I30" s="1" t="n">
-        <v>9.966794740738131</v>
+        <v>0.6</v>
       </c>
       <c r="J30" s="1" t="n">
         <v>92</v>
       </c>
       <c r="K30" s="1" t="inlineStr">
         <is>
-          <t>⚠️ Lager juda foydali — in boʻshab qoladi</t>
+          <t>Tavan: xom ulush 997% → 60%</t>
         </is>
       </c>
     </row>
@@ -35676,7 +36919,7 @@
       </c>
       <c r="E37" s="1" t="inlineStr">
         <is>
-          <t>Oy toshi kuniga +1</t>
+          <t>Oy nuri ishlab chiqarishi +40% (ehtiyojning 72% → 100%)</t>
         </is>
       </c>
       <c r="F37" s="1" t="n">
@@ -35725,7 +36968,7 @@
     <row r="41">
       <c r="A41" s="1" t="inlineStr">
         <is>
-          <t>Lager ulushi = 8 soatlik lager yigʻimi ÷ Ustaxona kunlik ishlab chiqarishi (ikkalasi ham oʻyinchi darajasida). 5–60% oraligʻi sogʻlom: lager foydali, lekin inni tashlab ketishga arzimaydi.</t>
+          <t>Lager ulushi = MIN(60%, 8 soatlik lager yigʻimi ÷ Ustaxona kunlik ishlab chiqarishi). Xom ulush faqat qoʻshin hajmi bilan oʻsadi (25-darajada 997%), shuning uchun 60% tavan qoʻyilgan — u 11-darajadan ishga tushadi.</t>
         </is>
       </c>
       <c r="B41" s="1" t="inlineStr"/>
@@ -35742,11 +36985,7 @@
       </c>
     </row>
     <row r="42">
-      <c r="A42" s="1" t="inlineStr">
-        <is>
-          <t>Ishlab chiqarish oʻsishi 1.38 dan 1.22 ga tushirildi — endi u narx oʻsishidan (1.30) past, shuning uchun resurs har darajada qadrliroq boʻlib boradi.</t>
-        </is>
-      </c>
+      <c r="A42" s="1" t="n"/>
       <c r="B42" s="1" t="inlineStr"/>
       <c r="C42" s="1" t="inlineStr"/>
       <c r="D42" s="1" t="inlineStr">

--- a/docs/blue_wolf/blue_wolf_darajalar.xlsx
+++ b/docs/blue_wolf/blue_wolf_darajalar.xlsx
@@ -138,6 +138,7 @@
     <definedName function="false" hidden="false" name="hunt_mid_injury" vbProcedure="false">Sozlamalar!$B$321</definedName>
     <definedName function="false" hidden="false" name="hunt_small_party_penalty" vbProcedure="false">Sozlamalar!$B$260</definedName>
     <definedName function="false" hidden="false" name="hunt_speed_kmh" vbProcedure="false">Sozlamalar!$B$314</definedName>
+    <definedName function="false" hidden="false" name="login_gift_step" vbProcedure="false">Sozlamalar!$B$335</definedName>
     <definedName function="false" hidden="false" name="loot_cap_ratio" vbProcedure="false">Sozlamalar!$B$222</definedName>
     <definedName function="false" hidden="false" name="loot_carry_base" vbProcedure="false">Sozlamalar!$B$220</definedName>
     <definedName function="false" hidden="false" name="loot_carry_tier" vbProcedure="false">Sozlamalar!$B$221</definedName>
@@ -194,12 +195,21 @@
     <definedName function="false" hidden="false" name="promote_cost_share" vbProcedure="false">Sozlamalar!$B$46</definedName>
     <definedName function="false" hidden="false" name="promote_loss" vbProcedure="false">Sozlamalar!$B$45</definedName>
     <definedName function="false" hidden="false" name="promote_time_share" vbProcedure="false">Sozlamalar!$B$47</definedName>
+    <definedName function="false" hidden="false" name="quest_combo_max_days" vbProcedure="false">Sozlamalar!$B$332</definedName>
+    <definedName function="false" hidden="false" name="quest_combo_step" vbProcedure="false">Sozlamalar!$B$331</definedName>
     <definedName function="false" hidden="false" name="quest_daily_cap" vbProcedure="false">Sozlamalar!$B$36</definedName>
+    <definedName function="false" hidden="false" name="quest_daily_chest" vbProcedure="false">Sozlamalar!$B$330</definedName>
     <definedName function="false" hidden="false" name="quest_daily_count" vbProcedure="false">Sozlamalar!$B$34</definedName>
+    <definedName function="false" hidden="false" name="quest_meat_ratio" vbProcedure="false">Sozlamalar!$B$336</definedName>
     <definedName function="false" hidden="false" name="quest_milestone_cap" vbProcedure="false">Sozlamalar!$B$38</definedName>
+    <definedName function="false" hidden="false" name="quest_monthly_cap" vbProcedure="false">Sozlamalar!$B$329</definedName>
+    <definedName function="false" hidden="false" name="quest_monthly_chest" vbProcedure="false">Sozlamalar!$B$334</definedName>
+    <definedName function="false" hidden="false" name="quest_monthly_count" vbProcedure="false">Sozlamalar!$B$328</definedName>
     <definedName function="false" hidden="false" name="quest_safe_cap" vbProcedure="false">Sozlamalar!$B$40</definedName>
     <definedName function="false" hidden="false" name="quest_speedup_min" vbProcedure="false">Sozlamalar!$B$39</definedName>
+    <definedName function="false" hidden="false" name="quest_tz_offset_h" vbProcedure="false">Sozlamalar!$B$337</definedName>
     <definedName function="false" hidden="false" name="quest_weekly_cap" vbProcedure="false">Sozlamalar!$B$37</definedName>
+    <definedName function="false" hidden="false" name="quest_weekly_chest" vbProcedure="false">Sozlamalar!$B$333</definedName>
     <definedName function="false" hidden="false" name="quest_weekly_count" vbProcedure="false">Sozlamalar!$B$35</definedName>
     <definedName function="false" hidden="false" name="queue_cancel_refund" vbProcedure="false">Sozlamalar!$B$301</definedName>
     <definedName function="false" hidden="false" name="raid_coef" vbProcedure="false">Sozlamalar!$B$223</definedName>
@@ -328,7 +338,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2679" uniqueCount="1948">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2710" uniqueCount="1970">
   <si>
     <t xml:space="preserve">Blue Wolf — oʻyinchi darajalari (1–25)</t>
   </si>
@@ -6163,6 +6173,72 @@
   </si>
   <si>
     <t xml:space="preserve">… + tasodifiy 0–shu (kartaga qarab)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Vazifalar: oylik va mukofotlar</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Oylik vazifa soni</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Har oy (kalendar oy) 3 ta vazifa</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Oylik mukofot chegarasi</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Oylik vazifalar jami = kunlik ishlab chiqarish × shu</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Kun kombosi sandigʻi</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Kunning hamma vazifasi bajarilganda (× kombo koeff.)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Kombo qadami</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ulush/kun</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Ketma-ket har kun uchun sandiq +shu</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Kombo maksimal kuni</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Shundan keyin oʻsmaydi (maks ×1.6)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Haftalik sandiq</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Haftaning hamma vazifasi bajarilganda</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Oylik sandiq</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Oyning hamma vazifasi bajarilganda</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Kirish sovgʻasi qadami</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7 kunlik taqvim: n-kun = shu × n</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Vazifa goʻshti koeffitsienti</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Goʻsht mukofoti = ulush × shu × toʻdaning kunlik goʻsht ehtiyoji</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Vazifalar vaqt mintaqasi</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Kun/hafta/oy chegarasi: UTC+shu (Toshkent)</t>
   </si>
   <si>
     <t xml:space="preserve">Izoh: vazn ustuni haqiqiy zoologik maʼlumotlarga (oʻrtacha katta erkak boʻri vazni) asoslangan; mifologik boʻrilarda vazn yoʻq.</t>
@@ -22687,7 +22763,7 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A3:D330"/>
+  <dimension ref="A3:D341"/>
   <sheetFormatPr defaultColWidth="8.5390625" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="28"/>
@@ -26734,7 +26810,7 @@
         <v>1924</v>
       </c>
     </row>
-    <row r="316" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="316" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A316" s="2" t="s">
         <v>1925</v>
       </c>
@@ -26748,7 +26824,7 @@
         <v>1926</v>
       </c>
     </row>
-    <row r="317" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="317" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A317" s="2" t="s">
         <v>1927</v>
       </c>
@@ -26762,7 +26838,7 @@
         <v>1928</v>
       </c>
     </row>
-    <row r="318" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="318" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A318" s="2" t="s">
         <v>1929</v>
       </c>
@@ -26776,7 +26852,7 @@
         <v>1930</v>
       </c>
     </row>
-    <row r="319" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="319" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A319" s="2" t="s">
         <v>1931</v>
       </c>
@@ -26790,7 +26866,7 @@
         <v>1932</v>
       </c>
     </row>
-    <row r="320" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="320" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A320" s="2" t="s">
         <v>1933</v>
       </c>
@@ -26804,7 +26880,7 @@
         <v>1934</v>
       </c>
     </row>
-    <row r="321" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="321" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A321" s="2" t="s">
         <v>1935</v>
       </c>
@@ -26818,7 +26894,7 @@
         <v>1937</v>
       </c>
     </row>
-    <row r="322" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="322" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A322" s="2" t="s">
         <v>1938</v>
       </c>
@@ -26832,7 +26908,7 @@
         <v>1937</v>
       </c>
     </row>
-    <row r="323" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="323" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A323" s="2" t="s">
         <v>1939</v>
       </c>
@@ -26846,7 +26922,7 @@
         <v>1937</v>
       </c>
     </row>
-    <row r="324" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="324" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A324" s="2" t="s">
         <v>1940</v>
       </c>
@@ -26860,7 +26936,7 @@
         <v>1937</v>
       </c>
     </row>
-    <row r="325" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="325" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A325" s="2" t="s">
         <v>1941</v>
       </c>
@@ -26874,7 +26950,7 @@
         <v>1942</v>
       </c>
     </row>
-    <row r="326" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="326" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A326" s="2" t="s">
         <v>1943</v>
       </c>
@@ -26888,19 +26964,164 @@
         <v>1944</v>
       </c>
     </row>
-    <row r="328" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="327" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A327" s="2" t="s">
+        <v>1945</v>
+      </c>
+    </row>
+    <row r="328" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A328" s="2" t="s">
-        <v>1945</v>
-      </c>
-    </row>
-    <row r="329" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>1946</v>
+      </c>
+      <c r="B328" s="4" t="n">
+        <v>3</v>
+      </c>
+      <c r="C328" s="2" t="s">
+        <v>1409</v>
+      </c>
+      <c r="D328" s="2" t="s">
+        <v>1947</v>
+      </c>
+    </row>
+    <row r="329" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A329" s="2" t="s">
-        <v>1946</v>
-      </c>
-    </row>
-    <row r="330" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>1948</v>
+      </c>
+      <c r="B329" s="4" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="C329" s="2" t="s">
+        <v>1414</v>
+      </c>
+      <c r="D329" s="2" t="s">
+        <v>1949</v>
+      </c>
+    </row>
+    <row r="330" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A330" s="2" t="s">
-        <v>1947</v>
+        <v>1950</v>
+      </c>
+      <c r="B330" s="4" t="n">
+        <v>0.05</v>
+      </c>
+      <c r="C330" s="2" t="s">
+        <v>1414</v>
+      </c>
+      <c r="D330" s="2" t="s">
+        <v>1951</v>
+      </c>
+    </row>
+    <row r="331" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A331" s="2" t="s">
+        <v>1952</v>
+      </c>
+      <c r="B331" s="4" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="C331" s="2" t="s">
+        <v>1953</v>
+      </c>
+      <c r="D331" s="2" t="s">
+        <v>1954</v>
+      </c>
+    </row>
+    <row r="332" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A332" s="2" t="s">
+        <v>1955</v>
+      </c>
+      <c r="B332" s="4" t="n">
+        <v>7</v>
+      </c>
+      <c r="C332" s="2" t="s">
+        <v>1455</v>
+      </c>
+      <c r="D332" s="2" t="s">
+        <v>1956</v>
+      </c>
+    </row>
+    <row r="333" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A333" s="2" t="s">
+        <v>1957</v>
+      </c>
+      <c r="B333" s="4" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="C333" s="2" t="s">
+        <v>1414</v>
+      </c>
+      <c r="D333" s="2" t="s">
+        <v>1958</v>
+      </c>
+    </row>
+    <row r="334" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A334" s="2" t="s">
+        <v>1959</v>
+      </c>
+      <c r="B334" s="4" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="C334" s="2" t="s">
+        <v>1414</v>
+      </c>
+      <c r="D334" s="2" t="s">
+        <v>1960</v>
+      </c>
+    </row>
+    <row r="335" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A335" s="2" t="s">
+        <v>1961</v>
+      </c>
+      <c r="B335" s="4" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="C335" s="2" t="s">
+        <v>1953</v>
+      </c>
+      <c r="D335" s="2" t="s">
+        <v>1962</v>
+      </c>
+    </row>
+    <row r="336" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A336" s="2" t="s">
+        <v>1963</v>
+      </c>
+      <c r="B336" s="4" t="n">
+        <v>2</v>
+      </c>
+      <c r="C336" s="2" t="s">
+        <v>1356</v>
+      </c>
+      <c r="D336" s="2" t="s">
+        <v>1964</v>
+      </c>
+    </row>
+    <row r="337" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A337" s="2" t="s">
+        <v>1965</v>
+      </c>
+      <c r="B337" s="4" t="n">
+        <v>5</v>
+      </c>
+      <c r="C337" s="2" t="s">
+        <v>1461</v>
+      </c>
+      <c r="D337" s="2" t="s">
+        <v>1966</v>
+      </c>
+    </row>
+    <row r="339" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A339" s="1" t="s">
+        <v>1967</v>
+      </c>
+    </row>
+    <row r="340" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A340" s="1" t="s">
+        <v>1968</v>
+      </c>
+    </row>
+    <row r="341" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A341" s="1" t="s">
+        <v>1969</v>
       </c>
     </row>
   </sheetData>
